--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P113"/>
+  <dimension ref="A1:P118"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="4" min="2" max="4"/>
@@ -1620,22 +1620,22 @@
       </c>
     </row>
     <row r="64">
-      <c r="J64" t="inlineStr">
+      <c r="J64" s="0" t="inlineStr">
         <is>
           <t>enemyMaxHp</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
+      <c r="L64" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M64" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="N64" s="0" t="inlineStr">
         <is>
           <t>敌人最大血量</t>
         </is>
@@ -1914,128 +1914,128 @@
       </c>
     </row>
     <row r="81">
-      <c r="J81" s="0" t="inlineStr">
-        <is>
-          <t>prefab</t>
-        </is>
-      </c>
-      <c r="L81" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N81" s="0" t="inlineStr">
-        <is>
-          <t>预制体</t>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>maxStamina</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>最大体力</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Enemy</t>
-        </is>
-      </c>
-      <c r="G82" s="0" t="inlineStr">
-        <is>
-          <t>敌人属性</t>
-        </is>
-      </c>
-      <c r="I82" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>staminaRecoveryRate</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>体力恢复速率</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="J83" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L83" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N83" s="0" t="inlineStr">
-        <is>
-          <t>敌人ID</t>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>dodgeStaminaCost</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>闪避消耗体力</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="J84" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L84" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N84" s="0" t="inlineStr">
-        <is>
-          <t>名称</t>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>dodgeSpeed</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>闪避速度</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="J85" s="0" t="inlineStr">
-        <is>
-          <t>maxHp</t>
-        </is>
-      </c>
-      <c r="L85" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N85" s="0" t="inlineStr">
-        <is>
-          <t>最大血量</t>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>dodgeDuration</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>闪避持续时间</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="J86" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>prefab</t>
         </is>
       </c>
       <c r="L86" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N86" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>预制体</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="J87" s="0" t="inlineStr">
-        <is>
-          <t>rotationSpeed</t>
-        </is>
-      </c>
-      <c r="L87" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N87" s="0" t="inlineStr">
-        <is>
-          <t>旋转速度</t>
+      <c r="B87" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Enemy</t>
+        </is>
+      </c>
+      <c r="G87" s="0" t="inlineStr">
+        <is>
+          <t>敌人属性</t>
+        </is>
+      </c>
+      <c r="I87" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="J88" s="0" t="inlineStr">
         <is>
-          <t>attackDamage</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L88" s="0" t="inlineStr">
@@ -2045,82 +2045,82 @@
       </c>
       <c r="N88" s="0" t="inlineStr">
         <is>
-          <t>攻击伤害</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="J89" s="0" t="inlineStr">
         <is>
-          <t>attackRange</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L89" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N89" s="0" t="inlineStr">
         <is>
-          <t>攻击范围</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="J90" s="0" t="inlineStr">
         <is>
-          <t>attackInterval</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L90" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N90" s="0" t="inlineStr">
         <is>
-          <t>攻击间隔</t>
+          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="J91" s="0" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L91" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N91" s="0" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Wave</t>
-        </is>
-      </c>
-      <c r="G92" s="0" t="inlineStr">
-        <is>
-          <t>波次配置</t>
-        </is>
-      </c>
-      <c r="I92" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J92" s="0" t="inlineStr">
+        <is>
+          <t>rotationSpeed</t>
+        </is>
+      </c>
+      <c r="L92" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N92" s="0" t="inlineStr">
+        <is>
+          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="J93" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>attackDamage</t>
         </is>
       </c>
       <c r="L93" s="0" t="inlineStr">
@@ -2130,133 +2130,133 @@
       </c>
       <c r="N93" s="0" t="inlineStr">
         <is>
-          <t>波次ID</t>
+          <t>攻击伤害</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="J94" s="0" t="inlineStr">
         <is>
-          <t>levelId</t>
+          <t>attackRange</t>
         </is>
       </c>
       <c r="L94" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N94" s="0" t="inlineStr">
         <is>
-          <t>关卡ID</t>
+          <t>攻击范围</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="J95" s="0" t="inlineStr">
         <is>
-          <t>waveIndex</t>
+          <t>attackInterval</t>
         </is>
       </c>
       <c r="L95" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N95" s="0" t="inlineStr">
         <is>
-          <t>波次索引</t>
+          <t>攻击间隔</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="J96" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>prefab</t>
         </is>
       </c>
       <c r="L96" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N96" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>预制体</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="J97" s="0" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="L97" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N97" s="0" t="inlineStr">
-        <is>
-          <t>数量</t>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Wave</t>
+        </is>
+      </c>
+      <c r="G97" s="0" t="inlineStr">
+        <is>
+          <t>波次配置</t>
+        </is>
+      </c>
+      <c r="I97" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="J98" s="0" t="inlineStr">
         <is>
-          <t>spawnInterval</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L98" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N98" s="0" t="inlineStr">
         <is>
-          <t>刷新间隔</t>
+          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="J99" s="0" t="inlineStr">
         <is>
-          <t>spawnRadius</t>
+          <t>levelId</t>
         </is>
       </c>
       <c r="L99" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N99" s="0" t="inlineStr">
         <is>
-          <t>刷新半径</t>
+          <t>关卡ID</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Drop</t>
-        </is>
-      </c>
-      <c r="G100" s="0" t="inlineStr">
-        <is>
-          <t>掉落配置</t>
-        </is>
-      </c>
-      <c r="I100" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J100" s="0" t="inlineStr">
+        <is>
+          <t>waveIndex</t>
+        </is>
+      </c>
+      <c r="L100" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N100" s="0" t="inlineStr">
+        <is>
+          <t>波次索引</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="J101" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L101" s="0" t="inlineStr">
@@ -2266,14 +2266,14 @@
       </c>
       <c r="N101" s="0" t="inlineStr">
         <is>
-          <t>掉落ID</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="J102" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>count</t>
         </is>
       </c>
       <c r="L102" s="0" t="inlineStr">
@@ -2283,65 +2283,65 @@
       </c>
       <c r="N102" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="J103" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>spawnInterval</t>
         </is>
       </c>
       <c r="L103" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N103" s="0" t="inlineStr">
         <is>
-          <t>道具ID</t>
+          <t>刷新间隔</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="J104" s="0" t="inlineStr">
         <is>
-          <t>dropRate</t>
+          <t>spawnRadius</t>
         </is>
       </c>
       <c r="L104" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N104" s="0" t="inlineStr">
         <is>
-          <t>掉落概率(万分之一)</t>
+          <t>刷新半径</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="J105" s="0" t="inlineStr">
-        <is>
-          <t>minCount</t>
-        </is>
-      </c>
-      <c r="L105" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N105" s="0" t="inlineStr">
-        <is>
-          <t>最小数量</t>
+      <c r="B105" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Drop</t>
+        </is>
+      </c>
+      <c r="G105" s="0" t="inlineStr">
+        <is>
+          <t>掉落配置</t>
+        </is>
+      </c>
+      <c r="I105" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="J106" s="0" t="inlineStr">
         <is>
-          <t>maxCount</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L106" s="0" t="inlineStr">
@@ -2351,31 +2351,31 @@
       </c>
       <c r="N106" s="0" t="inlineStr">
         <is>
-          <t>最大数量</t>
+          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Buff</t>
-        </is>
-      </c>
-      <c r="G107" s="0" t="inlineStr">
-        <is>
-          <t>Buff配置</t>
-        </is>
-      </c>
-      <c r="I107" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J107" s="0" t="inlineStr">
+        <is>
+          <t>enemyId</t>
+        </is>
+      </c>
+      <c r="L107" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N107" s="0" t="inlineStr">
+        <is>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="J108" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L108" s="0" t="inlineStr">
@@ -2385,48 +2385,48 @@
       </c>
       <c r="N108" s="0" t="inlineStr">
         <is>
-          <t>BuffID</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="J109" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>dropRate</t>
         </is>
       </c>
       <c r="L109" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N109" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>掉落概率(万分之一)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="J110" s="0" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>minCount</t>
         </is>
       </c>
       <c r="L110" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N110" s="0" t="inlineStr">
         <is>
-          <t>持续时间</t>
+          <t>最小数量</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="J111" s="0" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>maxCount</t>
         </is>
       </c>
       <c r="L111" s="0" t="inlineStr">
@@ -2436,39 +2436,124 @@
       </c>
       <c r="N111" s="0" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>最大数量</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="J112" s="0" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="L112" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N112" s="0" t="inlineStr">
-        <is>
-          <t>数值</t>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Buff</t>
+        </is>
+      </c>
+      <c r="G112" s="0" t="inlineStr">
+        <is>
+          <t>Buff配置</t>
+        </is>
+      </c>
+      <c r="I112" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="J113" s="0" t="inlineStr">
         <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L113" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N113" s="0" t="inlineStr">
+        <is>
+          <t>BuffID</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="J114" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L114" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N114" s="0" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="J115" s="0" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="L115" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N115" s="0" t="inlineStr">
+        <is>
+          <t>持续时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="J116" s="0" t="inlineStr">
+        <is>
+          <t>effectType</t>
+        </is>
+      </c>
+      <c r="L116" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N116" s="0" t="inlineStr">
+        <is>
+          <t>效果类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="J117" s="0" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L117" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N117" s="0" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="J118" s="0" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="L113" s="0" t="inlineStr">
+      <c r="L118" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N113" s="0" t="inlineStr">
+      <c r="N118" s="0" t="inlineStr">
         <is>
           <t>图标</t>
         </is>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P129"/>
+  <dimension ref="A1:P136"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -2389,128 +2389,128 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="0" t="inlineStr">
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>itemType</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>cfg.EItemType</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>道具类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>图标资源地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>stackLimit</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>堆叠上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="0" t="inlineStr">
         <is>
           <t>cfg.Player</t>
         </is>
       </c>
-      <c r="G75" s="0" t="inlineStr">
+      <c r="G78" s="0" t="inlineStr">
         <is>
           <t>玩家属性</t>
         </is>
       </c>
-      <c r="I75" s="0" t="inlineStr">
+      <c r="I78" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="J76" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L76" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N76" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="J77" s="0" t="inlineStr">
-        <is>
-          <t>maxHp</t>
-        </is>
-      </c>
-      <c r="L77" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N77" s="0" t="inlineStr">
-        <is>
-          <t>最大血量</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="J78" s="0" t="inlineStr">
-        <is>
-          <t>moveSpeed</t>
-        </is>
-      </c>
-      <c r="L78" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N78" s="0" t="inlineStr">
-        <is>
-          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="J79" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L79" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N79" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="J80" s="0" t="inlineStr">
         <is>
-          <t>colliderRadius</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L80" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N80" s="0" t="inlineStr">
         <is>
-          <t>碰撞体半径</t>
+          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="J81" s="0" t="inlineStr">
         <is>
-          <t>maxStamina</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L81" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N81" s="0" t="inlineStr">
         <is>
-          <t>最大体力</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="J82" s="0" t="inlineStr">
         <is>
-          <t>staminaRecoveryRate</t>
+          <t>rotationSpeed</t>
         </is>
       </c>
       <c r="L82" s="0" t="inlineStr">
@@ -2520,48 +2520,48 @@
       </c>
       <c r="N82" s="0" t="inlineStr">
         <is>
-          <t>体力恢复速率</t>
+          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="J83" s="0" t="inlineStr">
         <is>
-          <t>dodgeStaminaCost</t>
+          <t>colliderRadius</t>
         </is>
       </c>
       <c r="L83" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N83" s="0" t="inlineStr">
         <is>
-          <t>闪避消耗体力</t>
+          <t>碰撞体半径</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="J84" s="0" t="inlineStr">
         <is>
-          <t>dodgeSpeed</t>
+          <t>maxStamina</t>
         </is>
       </c>
       <c r="L84" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N84" s="0" t="inlineStr">
         <is>
-          <t>闪避速度</t>
+          <t>最大体力</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="J85" s="0" t="inlineStr">
         <is>
-          <t>dodgeDuration</t>
+          <t>staminaRecoveryRate</t>
         </is>
       </c>
       <c r="L85" s="0" t="inlineStr">
@@ -2571,65 +2571,65 @@
       </c>
       <c r="N85" s="0" t="inlineStr">
         <is>
-          <t>闪避持续时间</t>
+          <t>体力恢复速率</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="J86" s="0" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>dodgeStaminaCost</t>
         </is>
       </c>
       <c r="L86" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N86" s="0" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>闪避消耗体力</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Enemy</t>
-        </is>
-      </c>
-      <c r="G87" s="0" t="inlineStr">
-        <is>
-          <t>敌人属性</t>
-        </is>
-      </c>
-      <c r="I87" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J87" s="0" t="inlineStr">
+        <is>
+          <t>dodgeSpeed</t>
+        </is>
+      </c>
+      <c r="L87" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N87" s="0" t="inlineStr">
+        <is>
+          <t>闪避速度</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="J88" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>dodgeDuration</t>
         </is>
       </c>
       <c r="L88" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N88" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>闪避持续时间</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="J89" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>prefab</t>
         </is>
       </c>
       <c r="L89" s="0" t="inlineStr">
@@ -2639,65 +2639,65 @@
       </c>
       <c r="N89" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>预制体</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="J90" s="0" t="inlineStr">
-        <is>
-          <t>maxHp</t>
-        </is>
-      </c>
-      <c r="L90" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N90" s="0" t="inlineStr">
-        <is>
-          <t>最大血量</t>
+      <c r="B90" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Enemy</t>
+        </is>
+      </c>
+      <c r="G90" s="0" t="inlineStr">
+        <is>
+          <t>敌人属性</t>
+        </is>
+      </c>
+      <c r="I90" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="J91" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L91" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N91" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="J92" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L92" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N92" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="J93" s="0" t="inlineStr">
         <is>
-          <t>attackDamage</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L93" s="0" t="inlineStr">
@@ -2707,14 +2707,14 @@
       </c>
       <c r="N93" s="0" t="inlineStr">
         <is>
-          <t>攻击伤害</t>
+          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="J94" s="0" t="inlineStr">
         <is>
-          <t>attackRange</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L94" s="0" t="inlineStr">
@@ -2724,14 +2724,14 @@
       </c>
       <c r="N94" s="0" t="inlineStr">
         <is>
-          <t>攻击范围</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="J95" s="0" t="inlineStr">
         <is>
-          <t>attackInterval</t>
+          <t>rotationSpeed</t>
         </is>
       </c>
       <c r="L95" s="0" t="inlineStr">
@@ -2741,99 +2741,99 @@
       </c>
       <c r="N95" s="0" t="inlineStr">
         <is>
-          <t>攻击间隔</t>
+          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="J96" s="0" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>attackDamage</t>
         </is>
       </c>
       <c r="L96" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N96" s="0" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>攻击伤害</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Wave</t>
-        </is>
-      </c>
-      <c r="G97" s="0" t="inlineStr">
-        <is>
-          <t>波次配置</t>
-        </is>
-      </c>
-      <c r="I97" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J97" s="0" t="inlineStr">
+        <is>
+          <t>attackRange</t>
+        </is>
+      </c>
+      <c r="L97" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N97" s="0" t="inlineStr">
+        <is>
+          <t>攻击范围</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="J98" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>attackInterval</t>
         </is>
       </c>
       <c r="L98" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N98" s="0" t="inlineStr">
         <is>
-          <t>波次ID</t>
+          <t>攻击间隔</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="J99" s="0" t="inlineStr">
         <is>
-          <t>levelId</t>
+          <t>prefab</t>
         </is>
       </c>
       <c r="L99" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N99" s="0" t="inlineStr">
         <is>
-          <t>关卡ID</t>
+          <t>预制体</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="J100" s="0" t="inlineStr">
-        <is>
-          <t>waveIndex</t>
-        </is>
-      </c>
-      <c r="L100" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N100" s="0" t="inlineStr">
-        <is>
-          <t>波次索引</t>
+      <c r="B100" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Wave</t>
+        </is>
+      </c>
+      <c r="G100" s="0" t="inlineStr">
+        <is>
+          <t>波次配置</t>
+        </is>
+      </c>
+      <c r="I100" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="J101" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L101" s="0" t="inlineStr">
@@ -2843,14 +2843,14 @@
       </c>
       <c r="N101" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="J102" s="0" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>levelId</t>
         </is>
       </c>
       <c r="L102" s="0" t="inlineStr">
@@ -2860,116 +2860,116 @@
       </c>
       <c r="N102" s="0" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>关卡ID</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="J103" s="0" t="inlineStr">
         <is>
-          <t>spawnInterval</t>
+          <t>waveIndex</t>
         </is>
       </c>
       <c r="L103" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N103" s="0" t="inlineStr">
         <is>
-          <t>刷新间隔</t>
+          <t>波次索引</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="J104" s="0" t="inlineStr">
         <is>
-          <t>spawnRadius</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L104" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N104" s="0" t="inlineStr">
         <is>
-          <t>刷新半径</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Drop</t>
-        </is>
-      </c>
-      <c r="G105" s="0" t="inlineStr">
-        <is>
-          <t>掉落配置</t>
-        </is>
-      </c>
-      <c r="I105" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J105" s="0" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="L105" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N105" s="0" t="inlineStr">
+        <is>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="J106" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>spawnInterval</t>
         </is>
       </c>
       <c r="L106" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N106" s="0" t="inlineStr">
         <is>
-          <t>掉落ID</t>
+          <t>刷新间隔</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="J107" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>spawnRadius</t>
         </is>
       </c>
       <c r="L107" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N107" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>刷新半径</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="J108" s="0" t="inlineStr">
-        <is>
-          <t>itemId</t>
-        </is>
-      </c>
-      <c r="L108" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N108" s="0" t="inlineStr">
-        <is>
-          <t>道具ID</t>
+      <c r="B108" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Drop</t>
+        </is>
+      </c>
+      <c r="G108" s="0" t="inlineStr">
+        <is>
+          <t>掉落配置</t>
+        </is>
+      </c>
+      <c r="I108" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="J109" s="0" t="inlineStr">
         <is>
-          <t>dropRate</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L109" s="0" t="inlineStr">
@@ -2979,14 +2979,14 @@
       </c>
       <c r="N109" s="0" t="inlineStr">
         <is>
-          <t>掉落概率(万分之一)</t>
+          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="J110" s="0" t="inlineStr">
         <is>
-          <t>minCount</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L110" s="0" t="inlineStr">
@@ -2996,14 +2996,14 @@
       </c>
       <c r="N110" s="0" t="inlineStr">
         <is>
-          <t>最小数量</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="J111" s="0" t="inlineStr">
         <is>
-          <t>maxCount</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L111" s="0" t="inlineStr">
@@ -3013,31 +3013,31 @@
       </c>
       <c r="N111" s="0" t="inlineStr">
         <is>
-          <t>最大数量</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="B112" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Buff</t>
-        </is>
-      </c>
-      <c r="G112" s="0" t="inlineStr">
-        <is>
-          <t>Buff配置</t>
-        </is>
-      </c>
-      <c r="I112" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J112" s="0" t="inlineStr">
+        <is>
+          <t>dropRate</t>
+        </is>
+      </c>
+      <c r="L112" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N112" s="0" t="inlineStr">
+        <is>
+          <t>掉落概率(万分之一)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="J113" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>minCount</t>
         </is>
       </c>
       <c r="L113" s="0" t="inlineStr">
@@ -3047,48 +3047,48 @@
       </c>
       <c r="N113" s="0" t="inlineStr">
         <is>
-          <t>BuffID</t>
+          <t>最小数量</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="J114" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>maxCount</t>
         </is>
       </c>
       <c r="L114" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N114" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>最大数量</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="J115" s="0" t="inlineStr">
-        <is>
-          <t>duration</t>
-        </is>
-      </c>
-      <c r="L115" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N115" s="0" t="inlineStr">
-        <is>
-          <t>持续时间</t>
+      <c r="B115" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Buff</t>
+        </is>
+      </c>
+      <c r="G115" s="0" t="inlineStr">
+        <is>
+          <t>Buff配置</t>
+        </is>
+      </c>
+      <c r="I115" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="J116" s="0" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L116" s="0" t="inlineStr">
@@ -3098,228 +3098,347 @@
       </c>
       <c r="N116" s="0" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>BuffID</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="J117" s="0" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L117" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N117" s="0" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="J118" s="0" t="inlineStr">
         <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="L118" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N118" s="0" t="inlineStr">
+        <is>
+          <t>持续时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="J119" s="0" t="inlineStr">
+        <is>
+          <t>effectType</t>
+        </is>
+      </c>
+      <c r="L119" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N119" s="0" t="inlineStr">
+        <is>
+          <t>效果类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="J120" s="0" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L120" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N120" s="0" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="J121" s="0" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="L118" s="0" t="inlineStr">
+      <c r="L121" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N118" s="0" t="inlineStr">
+      <c r="N121" s="0" t="inlineStr">
         <is>
           <t>图标</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="B119" t="inlineStr">
+    <row r="122">
+      <c r="B122" s="0" t="inlineStr">
         <is>
           <t>cfg.Portal</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G122" s="0" t="inlineStr">
         <is>
           <t>传送门配置</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="I122" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="J120" t="inlineStr">
+    <row r="123">
+      <c r="J123" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
+      <c r="L123" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N123" s="0" t="inlineStr">
         <is>
           <t>传送门ID</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="J121" t="inlineStr">
+    <row r="124">
+      <c r="J124" s="0" t="inlineStr">
         <is>
           <t>portalType</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="L124" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr">
+      <c r="N124" s="0" t="inlineStr">
         <is>
           <t>传送门类型</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="J122" t="inlineStr">
+    <row r="125">
+      <c r="J125" s="0" t="inlineStr">
         <is>
           <t>targetLevelId</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
+      <c r="L125" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N125" s="0" t="inlineStr">
         <is>
           <t>目标关卡ID</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="J123" t="inlineStr">
+    <row r="126">
+      <c r="J126" s="0" t="inlineStr">
         <is>
           <t>targetSceneName</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="L126" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr">
+      <c r="N126" s="0" t="inlineStr">
         <is>
           <t>目标场景名</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="J124" t="inlineStr">
+    <row r="127">
+      <c r="J127" s="0" t="inlineStr">
         <is>
           <t>spawnCondition</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="L127" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr">
+      <c r="N127" s="0" t="inlineStr">
         <is>
           <t>出现条件</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="J125" t="inlineStr">
+    <row r="128">
+      <c r="J128" s="0" t="inlineStr">
         <is>
           <t>conditionParam</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="L128" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr">
+      <c r="N128" s="0" t="inlineStr">
         <is>
           <t>条件参数</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="J126" t="inlineStr">
+    <row r="129">
+      <c r="J129" s="0" t="inlineStr">
         <is>
           <t>keepPlayerState</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="L129" s="0" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr">
+      <c r="N129" s="0" t="inlineStr">
         <is>
           <t>保留玩家状态</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="J127" t="inlineStr">
+    <row r="130">
+      <c r="J130" s="0" t="inlineStr">
         <is>
           <t>promptText</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="L130" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr">
+      <c r="N130" s="0" t="inlineStr">
         <is>
           <t>提示文本</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="J128" t="inlineStr">
+    <row r="131">
+      <c r="J131" s="0" t="inlineStr">
         <is>
           <t>transitionType</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="L131" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr">
+      <c r="N131" s="0" t="inlineStr">
         <is>
           <t>转场类型</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="J129" t="inlineStr">
+    <row r="132">
+      <c r="J132" s="0" t="inlineStr">
         <is>
           <t>transitionDuration</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr">
+      <c r="L132" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N132" s="0" t="inlineStr">
         <is>
           <t>转场时长</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>cfg.InventoryConfig</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>背包容量配置</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>tempBagCapacity</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>临时背包槽位</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>warehouseCapacity</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>仓库槽位</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P136"/>
+  <dimension ref="A1:P182"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -2389,51 +2389,51 @@
       </c>
     </row>
     <row r="75">
-      <c r="J75" t="inlineStr">
+      <c r="J75" s="0" t="inlineStr">
         <is>
           <t>itemType</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="L75" s="0" t="inlineStr">
         <is>
           <t>cfg.EItemType</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="N75" s="0" t="inlineStr">
         <is>
           <t>道具类型</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="J76" t="inlineStr">
+      <c r="J76" s="0" t="inlineStr">
         <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L76" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="N76" s="0" t="inlineStr">
         <is>
           <t>图标资源地址</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="J77" t="inlineStr">
+      <c r="J77" s="0" t="inlineStr">
         <is>
           <t>stackLimit</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
+      <c r="L77" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N77" s="0" t="inlineStr">
         <is>
           <t>堆叠上限</t>
         </is>
@@ -2644,111 +2644,111 @@
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="0" t="inlineStr">
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>idleAnim</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>待机动画名</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>moveAnim</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>移动动画名</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>dodgeAnim</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>闪避动画名</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>reloadAnim</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>换弹动画名</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>deadAnim</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>死亡动画名</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="0" t="inlineStr">
         <is>
           <t>cfg.Enemy</t>
         </is>
       </c>
-      <c r="G90" s="0" t="inlineStr">
+      <c r="G95" s="0" t="inlineStr">
         <is>
           <t>敌人属性</t>
         </is>
       </c>
-      <c r="I90" s="0" t="inlineStr">
+      <c r="I95" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="J91" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L91" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N91" s="0" t="inlineStr">
-        <is>
-          <t>敌人ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="J92" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L92" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N92" s="0" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="J93" s="0" t="inlineStr">
-        <is>
-          <t>maxHp</t>
-        </is>
-      </c>
-      <c r="L93" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N93" s="0" t="inlineStr">
-        <is>
-          <t>最大血量</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="J94" s="0" t="inlineStr">
-        <is>
-          <t>moveSpeed</t>
-        </is>
-      </c>
-      <c r="L94" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N94" s="0" t="inlineStr">
-        <is>
-          <t>移动速度</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="J95" s="0" t="inlineStr">
-        <is>
-          <t>rotationSpeed</t>
-        </is>
-      </c>
-      <c r="L95" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N95" s="0" t="inlineStr">
-        <is>
-          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="J96" s="0" t="inlineStr">
         <is>
-          <t>attackDamage</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L96" s="0" t="inlineStr">
@@ -2758,82 +2758,82 @@
       </c>
       <c r="N96" s="0" t="inlineStr">
         <is>
-          <t>攻击伤害</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="J97" s="0" t="inlineStr">
         <is>
-          <t>attackRange</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L97" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N97" s="0" t="inlineStr">
         <is>
-          <t>攻击范围</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="J98" s="0" t="inlineStr">
         <is>
-          <t>attackInterval</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L98" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N98" s="0" t="inlineStr">
         <is>
-          <t>攻击间隔</t>
+          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="J99" s="0" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L99" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N99" s="0" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Wave</t>
-        </is>
-      </c>
-      <c r="G100" s="0" t="inlineStr">
-        <is>
-          <t>波次配置</t>
-        </is>
-      </c>
-      <c r="I100" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J100" s="0" t="inlineStr">
+        <is>
+          <t>rotationSpeed</t>
+        </is>
+      </c>
+      <c r="L100" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N100" s="0" t="inlineStr">
+        <is>
+          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="J101" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>attackDamage</t>
         </is>
       </c>
       <c r="L101" s="0" t="inlineStr">
@@ -2843,133 +2843,133 @@
       </c>
       <c r="N101" s="0" t="inlineStr">
         <is>
-          <t>波次ID</t>
+          <t>攻击伤害</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="J102" s="0" t="inlineStr">
         <is>
-          <t>levelId</t>
+          <t>attackRange</t>
         </is>
       </c>
       <c r="L102" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N102" s="0" t="inlineStr">
         <is>
-          <t>关卡ID</t>
+          <t>攻击范围</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="J103" s="0" t="inlineStr">
         <is>
-          <t>waveIndex</t>
+          <t>attackInterval</t>
         </is>
       </c>
       <c r="L103" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N103" s="0" t="inlineStr">
         <is>
-          <t>波次索引</t>
+          <t>攻击间隔</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="J104" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>prefab</t>
         </is>
       </c>
       <c r="L104" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N104" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>预制体</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="J105" s="0" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="L105" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N105" s="0" t="inlineStr">
-        <is>
-          <t>数量</t>
+      <c r="B105" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Wave</t>
+        </is>
+      </c>
+      <c r="G105" s="0" t="inlineStr">
+        <is>
+          <t>波次配置</t>
+        </is>
+      </c>
+      <c r="I105" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="J106" s="0" t="inlineStr">
         <is>
-          <t>spawnInterval</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L106" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N106" s="0" t="inlineStr">
         <is>
-          <t>刷新间隔</t>
+          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="J107" s="0" t="inlineStr">
         <is>
-          <t>spawnRadius</t>
+          <t>levelId</t>
         </is>
       </c>
       <c r="L107" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N107" s="0" t="inlineStr">
         <is>
-          <t>刷新半径</t>
+          <t>关卡ID</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Drop</t>
-        </is>
-      </c>
-      <c r="G108" s="0" t="inlineStr">
-        <is>
-          <t>掉落配置</t>
-        </is>
-      </c>
-      <c r="I108" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J108" s="0" t="inlineStr">
+        <is>
+          <t>waveIndex</t>
+        </is>
+      </c>
+      <c r="L108" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N108" s="0" t="inlineStr">
+        <is>
+          <t>波次索引</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="J109" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L109" s="0" t="inlineStr">
@@ -2979,14 +2979,14 @@
       </c>
       <c r="N109" s="0" t="inlineStr">
         <is>
-          <t>掉落ID</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="J110" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>count</t>
         </is>
       </c>
       <c r="L110" s="0" t="inlineStr">
@@ -2996,65 +2996,65 @@
       </c>
       <c r="N110" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="J111" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>spawnInterval</t>
         </is>
       </c>
       <c r="L111" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N111" s="0" t="inlineStr">
         <is>
-          <t>道具ID</t>
+          <t>刷新间隔</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="J112" s="0" t="inlineStr">
         <is>
-          <t>dropRate</t>
+          <t>spawnRadius</t>
         </is>
       </c>
       <c r="L112" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N112" s="0" t="inlineStr">
         <is>
-          <t>掉落概率(万分之一)</t>
+          <t>刷新半径</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="J113" s="0" t="inlineStr">
-        <is>
-          <t>minCount</t>
-        </is>
-      </c>
-      <c r="L113" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N113" s="0" t="inlineStr">
-        <is>
-          <t>最小数量</t>
+      <c r="B113" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Drop</t>
+        </is>
+      </c>
+      <c r="G113" s="0" t="inlineStr">
+        <is>
+          <t>掉落配置</t>
+        </is>
+      </c>
+      <c r="I113" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="J114" s="0" t="inlineStr">
         <is>
-          <t>maxCount</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L114" s="0" t="inlineStr">
@@ -3064,31 +3064,31 @@
       </c>
       <c r="N114" s="0" t="inlineStr">
         <is>
-          <t>最大数量</t>
+          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="B115" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Buff</t>
-        </is>
-      </c>
-      <c r="G115" s="0" t="inlineStr">
-        <is>
-          <t>Buff配置</t>
-        </is>
-      </c>
-      <c r="I115" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J115" s="0" t="inlineStr">
+        <is>
+          <t>enemyId</t>
+        </is>
+      </c>
+      <c r="L115" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N115" s="0" t="inlineStr">
+        <is>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="J116" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L116" s="0" t="inlineStr">
@@ -3098,48 +3098,48 @@
       </c>
       <c r="N116" s="0" t="inlineStr">
         <is>
-          <t>BuffID</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="J117" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>dropRate</t>
         </is>
       </c>
       <c r="L117" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N117" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>掉落概率(万分之一)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="J118" s="0" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>minCount</t>
         </is>
       </c>
       <c r="L118" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N118" s="0" t="inlineStr">
         <is>
-          <t>持续时间</t>
+          <t>最小数量</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="J119" s="0" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>maxCount</t>
         </is>
       </c>
       <c r="L119" s="0" t="inlineStr">
@@ -3149,116 +3149,116 @@
       </c>
       <c r="N119" s="0" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>最大数量</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="J120" s="0" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="L120" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N120" s="0" t="inlineStr">
-        <is>
-          <t>数值</t>
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Buff</t>
+        </is>
+      </c>
+      <c r="G120" s="0" t="inlineStr">
+        <is>
+          <t>Buff配置</t>
+        </is>
+      </c>
+      <c r="I120" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="J121" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L121" s="0" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N121" s="0" t="inlineStr">
+        <is>
+          <t>BuffID</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="J122" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L122" s="0" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N121" s="0" t="inlineStr">
-        <is>
-          <t>图标</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="B122" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Portal</t>
-        </is>
-      </c>
-      <c r="G122" s="0" t="inlineStr">
-        <is>
-          <t>传送门配置</t>
-        </is>
-      </c>
-      <c r="I122" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="N122" s="0" t="inlineStr">
+        <is>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="J123" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="L123" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N123" s="0" t="inlineStr">
         <is>
-          <t>传送门ID</t>
+          <t>持续时间</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="J124" s="0" t="inlineStr">
         <is>
-          <t>portalType</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="L124" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N124" s="0" t="inlineStr">
         <is>
-          <t>传送门类型</t>
+          <t>效果类型</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="J125" s="0" t="inlineStr">
         <is>
-          <t>targetLevelId</t>
+          <t>value</t>
         </is>
       </c>
       <c r="L125" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N125" s="0" t="inlineStr">
         <is>
-          <t>目标关卡ID</t>
+          <t>数值</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="J126" s="0" t="inlineStr">
         <is>
-          <t>targetSceneName</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L126" s="0" t="inlineStr">
@@ -3268,82 +3268,82 @@
       </c>
       <c r="N126" s="0" t="inlineStr">
         <is>
-          <t>目标场景名</t>
+          <t>图标</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="J127" s="0" t="inlineStr">
-        <is>
-          <t>spawnCondition</t>
-        </is>
-      </c>
-      <c r="L127" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N127" s="0" t="inlineStr">
-        <is>
-          <t>出现条件</t>
+      <c r="B127" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Portal</t>
+        </is>
+      </c>
+      <c r="G127" s="0" t="inlineStr">
+        <is>
+          <t>传送门配置</t>
+        </is>
+      </c>
+      <c r="I127" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="J128" s="0" t="inlineStr">
         <is>
-          <t>conditionParam</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L128" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N128" s="0" t="inlineStr">
         <is>
-          <t>条件参数</t>
+          <t>传送门ID</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="J129" s="0" t="inlineStr">
         <is>
-          <t>keepPlayerState</t>
+          <t>portalType</t>
         </is>
       </c>
       <c r="L129" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N129" s="0" t="inlineStr">
         <is>
-          <t>保留玩家状态</t>
+          <t>传送门类型</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="J130" s="0" t="inlineStr">
         <is>
-          <t>promptText</t>
+          <t>targetLevelId</t>
         </is>
       </c>
       <c r="L130" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N130" s="0" t="inlineStr">
         <is>
-          <t>提示文本</t>
+          <t>目标关卡ID</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="J131" s="0" t="inlineStr">
         <is>
-          <t>transitionType</t>
+          <t>targetSceneName</t>
         </is>
       </c>
       <c r="L131" s="0" t="inlineStr">
@@ -3353,92 +3353,874 @@
       </c>
       <c r="N131" s="0" t="inlineStr">
         <is>
-          <t>转场类型</t>
+          <t>目标场景名</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="J132" s="0" t="inlineStr">
         <is>
+          <t>spawnCondition</t>
+        </is>
+      </c>
+      <c r="L132" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N132" s="0" t="inlineStr">
+        <is>
+          <t>出现条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="J133" s="0" t="inlineStr">
+        <is>
+          <t>conditionParam</t>
+        </is>
+      </c>
+      <c r="L133" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N133" s="0" t="inlineStr">
+        <is>
+          <t>条件参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="J134" s="0" t="inlineStr">
+        <is>
+          <t>keepPlayerState</t>
+        </is>
+      </c>
+      <c r="L134" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N134" s="0" t="inlineStr">
+        <is>
+          <t>保留玩家状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="J135" s="0" t="inlineStr">
+        <is>
+          <t>promptText</t>
+        </is>
+      </c>
+      <c r="L135" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N135" s="0" t="inlineStr">
+        <is>
+          <t>提示文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="J136" s="0" t="inlineStr">
+        <is>
+          <t>transitionType</t>
+        </is>
+      </c>
+      <c r="L136" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N136" s="0" t="inlineStr">
+        <is>
+          <t>转场类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="J137" s="0" t="inlineStr">
+        <is>
           <t>transitionDuration</t>
         </is>
       </c>
-      <c r="L132" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N132" s="0" t="inlineStr">
+      <c r="L137" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N137" s="0" t="inlineStr">
         <is>
           <t>转场时长</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="B133" t="inlineStr">
+    <row r="138">
+      <c r="B138" s="0" t="inlineStr">
         <is>
           <t>cfg.InventoryConfig</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G138" s="0" t="inlineStr">
         <is>
           <t>背包容量配置</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I138" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="J134" t="inlineStr">
+    <row r="139">
+      <c r="J139" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
+      <c r="L139" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N139" s="0" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="J135" t="inlineStr">
+    <row r="140">
+      <c r="J140" s="0" t="inlineStr">
         <is>
           <t>tempBagCapacity</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
+      <c r="L140" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N140" s="0" t="inlineStr">
         <is>
           <t>临时背包槽位</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="J136" t="inlineStr">
+    <row r="141">
+      <c r="J141" s="0" t="inlineStr">
         <is>
           <t>warehouseCapacity</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
+      <c r="L141" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N141" s="0" t="inlineStr">
         <is>
           <t>仓库槽位</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>cfg.Camera</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>相机配置</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>配置ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>smoothTime</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>相机平滑时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>defaultFov</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>默认FOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>fovSmoothTime</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>FOV平滑时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>shakeDamping</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>震动衰减速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>scopeRenderSize</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>狙击镜渲染纹理尺寸</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>scopeCameraFov</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>狙击镜相机FOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>defaultOrthographicSize</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>默认正交尺寸</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>cfg.Ballistic</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>弹道全局配置</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>配置ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>tracerRadius</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Tracer射线检测半径</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>tracerStartWidth</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Tracer起始宽度</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>tracerEndWidth</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Tracer结束宽度</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>tracerTailLength</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Tracer尾迹长度</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>maxActiveTracers</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>最大同时存在Tracer数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>hitLayers</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>默认命中层级</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>tracerStartColor</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Tracer起始颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>tracerEndColor</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Tracer结束颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>cfg.UiConfig</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>UI全局配置</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>配置ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>damageNumberPoolSize</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>伤害数字对象池大小</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>damageNumberFadeDuration</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>伤害数字渐隐时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>damageNumberMoveOffset</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>伤害数字上浮偏移</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>damageNumberNormalColor</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>普通伤害数字颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>damageNumberCriticalColor</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>暴击伤害数字颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>damageNumberNormalFontSize</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>普通伤害数字字体大小</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>damageNumberCriticalFontSize</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>暴击伤害数字字体大小</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>hitMarkerPoolSize</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>命中标记对象池大小</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>hitMarkerDuration</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>命中标记显示时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>hitMarkerSize</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>命中标记大小</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>hitMarkerNormalColor</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>普通命中标记颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>hitMarkerCriticalColor</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>暴击命中标记颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>indicatorFadeSpeed</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>受击指示器淡出速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>indicatorColor</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>受击指示器颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>loadingTextFormat</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>加载进度文本格式</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>cfg.Pickup</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>拾取物配置</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>配置ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>colliderRadius</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>拾取物碰撞体半径</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>visualScale</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>拾取物视觉缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>sortingOrder</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>拾取物渲染排序</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P182"/>
+  <dimension ref="A1:P244"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -2027,111 +2027,111 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Level</t>
-        </is>
-      </c>
-      <c r="G54" s="0" t="inlineStr">
-        <is>
-          <t>关卡配置</t>
-        </is>
-      </c>
-      <c r="I54" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J54" s="0" t="inlineStr">
+        <is>
+          <t>aimAssistRadius</t>
+        </is>
+      </c>
+      <c r="L54" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N54" s="0" t="inlineStr">
+        <is>
+          <t>辅助瞄准半径</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="J55" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>aimAssistMaxAngle</t>
         </is>
       </c>
       <c r="L55" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N55" s="0" t="inlineStr">
         <is>
-          <t>关卡ID</t>
+          <t>辅助瞄准最大角度</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>displayName</t>
+          <t>lockOnRange</t>
         </is>
       </c>
       <c r="L56" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N56" s="0" t="inlineStr">
         <is>
-          <t>显示名称</t>
+          <t>锁定范围</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="J57" s="0" t="inlineStr">
         <is>
-          <t>sceneName</t>
+          <t>lockOnAngle</t>
         </is>
       </c>
       <c r="L57" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N57" s="0" t="inlineStr">
         <is>
-          <t>场景名</t>
+          <t>锁定角度</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="J58" s="0" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>lockOnHoldTime</t>
         </is>
       </c>
       <c r="L58" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N58" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>锁定保持时间</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="J59" s="0" t="inlineStr">
-        <is>
-          <t>defaultWeaponIds</t>
-        </is>
-      </c>
-      <c r="L59" s="0" t="inlineStr">
-        <is>
-          <t>(array#sep=,),int</t>
-        </is>
-      </c>
-      <c r="N59" s="0" t="inlineStr">
-        <is>
-          <t>默认武器ID列表</t>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Level</t>
+        </is>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
+        <is>
+          <t>关卡配置</t>
+        </is>
+      </c>
+      <c r="I59" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="J60" s="0" t="inlineStr">
         <is>
-          <t>playerMaxHp</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L60" s="0" t="inlineStr">
@@ -2141,104 +2141,99 @@
       </c>
       <c r="N60" s="0" t="inlineStr">
         <is>
-          <t>玩家最大血量</t>
+          <t>关卡ID</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="J61" s="0" t="inlineStr">
         <is>
-          <t>enemyCount</t>
+          <t>displayName</t>
         </is>
       </c>
       <c r="L61" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N61" s="0" t="inlineStr">
         <is>
-          <t>敌人数量</t>
+          <t>显示名称</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>enemySpawnRadius</t>
+          <t>sceneName</t>
         </is>
       </c>
       <c r="L62" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N62" s="0" t="inlineStr">
         <is>
-          <t>敌人刷新半径</t>
+          <t>场景名</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="J63" s="0" t="inlineStr">
         <is>
-          <t>enemyConfigId</t>
+          <t>description</t>
         </is>
       </c>
       <c r="L63" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N63" s="0" t="inlineStr">
         <is>
-          <t>敌人配置ID</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="J64" s="0" t="inlineStr">
         <is>
-          <t>enemyMaxHp</t>
+          <t>defaultWeaponIds</t>
         </is>
       </c>
       <c r="L64" s="0" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M64" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+          <t>(array#sep=,),int</t>
         </is>
       </c>
       <c r="N64" s="0" t="inlineStr">
         <is>
-          <t>敌人最大血量</t>
+          <t>默认武器ID列表</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Item</t>
-        </is>
-      </c>
-      <c r="G65" s="0" t="inlineStr">
-        <is>
-          <t>道具配置</t>
-        </is>
-      </c>
-      <c r="I65" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J65" s="0" t="inlineStr">
+        <is>
+          <t>playerMaxHp</t>
+        </is>
+      </c>
+      <c r="L65" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N65" s="0" t="inlineStr">
+        <is>
+          <t>玩家最大血量</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>enemyCount</t>
         </is>
       </c>
       <c r="L66" s="0" t="inlineStr">
@@ -2248,48 +2243,48 @@
       </c>
       <c r="N66" s="0" t="inlineStr">
         <is>
-          <t>道具ID</t>
+          <t>敌人数量</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="J67" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>enemySpawnRadius</t>
         </is>
       </c>
       <c r="L67" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N67" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>敌人刷新半径</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="J68" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>enemyConfigId</t>
         </is>
       </c>
       <c r="L68" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N68" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>敌人配置ID</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="J69" s="0" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>enemyMaxHp</t>
         </is>
       </c>
       <c r="L69" s="0" t="inlineStr">
@@ -2297,33 +2292,38 @@
           <t>int</t>
         </is>
       </c>
+      <c r="M69" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
       <c r="N69" s="0" t="inlineStr">
         <is>
-          <t>价格</t>
+          <t>敌人最大血量</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="J70" s="0" t="inlineStr">
-        <is>
-          <t>quality</t>
-        </is>
-      </c>
-      <c r="L70" s="0" t="inlineStr">
-        <is>
-          <t>cfg.EQuality</t>
-        </is>
-      </c>
-      <c r="N70" s="0" t="inlineStr">
-        <is>
-          <t>品质</t>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Item</t>
+        </is>
+      </c>
+      <c r="G70" s="0" t="inlineStr">
+        <is>
+          <t>道具配置</t>
+        </is>
+      </c>
+      <c r="I70" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="J71" s="0" t="inlineStr">
         <is>
-          <t>upgradeToItemId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L71" s="0" t="inlineStr">
@@ -2333,218 +2333,218 @@
       </c>
       <c r="N71" s="0" t="inlineStr">
         <is>
-          <t>升级目标道具ID</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="J72" s="0" t="inlineStr">
         <is>
-          <t>expireTime</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L72" s="0" t="inlineStr">
         <is>
-          <t>datetime?</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N72" s="0" t="inlineStr">
         <is>
-          <t>过期时间</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="J73" s="0" t="inlineStr">
         <is>
-          <t>batchUseable</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L73" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N73" s="0" t="inlineStr">
         <is>
-          <t>是否可批量使用</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="J74" s="0" t="inlineStr">
         <is>
-          <t>exchangeList</t>
+          <t>price</t>
         </is>
       </c>
       <c r="L74" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N74" s="0" t="inlineStr">
         <is>
-          <t>兑换列表</t>
+          <t>价格</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="J75" s="0" t="inlineStr">
         <is>
-          <t>itemType</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="L75" s="0" t="inlineStr">
         <is>
-          <t>cfg.EItemType</t>
+          <t>cfg.EQuality</t>
         </is>
       </c>
       <c r="N75" s="0" t="inlineStr">
         <is>
-          <t>道具类型</t>
+          <t>品质</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="J76" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>upgradeToItemId</t>
         </is>
       </c>
       <c r="L76" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N76" s="0" t="inlineStr">
         <is>
-          <t>图标资源地址</t>
+          <t>升级目标道具ID</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="J77" s="0" t="inlineStr">
         <is>
-          <t>stackLimit</t>
+          <t>expireTime</t>
         </is>
       </c>
       <c r="L77" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>datetime?</t>
         </is>
       </c>
       <c r="N77" s="0" t="inlineStr">
         <is>
-          <t>堆叠上限</t>
+          <t>过期时间</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Player</t>
-        </is>
-      </c>
-      <c r="G78" s="0" t="inlineStr">
-        <is>
-          <t>玩家属性</t>
-        </is>
-      </c>
-      <c r="I78" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J78" s="0" t="inlineStr">
+        <is>
+          <t>batchUseable</t>
+        </is>
+      </c>
+      <c r="L78" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N78" s="0" t="inlineStr">
+        <is>
+          <t>是否可批量使用</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="J79" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>exchangeList</t>
         </is>
       </c>
       <c r="L79" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N79" s="0" t="inlineStr">
         <is>
-          <t>配置ID</t>
+          <t>兑换列表</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="J80" s="0" t="inlineStr">
         <is>
-          <t>maxHp</t>
+          <t>itemType</t>
         </is>
       </c>
       <c r="L80" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.EItemType</t>
         </is>
       </c>
       <c r="N80" s="0" t="inlineStr">
         <is>
-          <t>最大血量</t>
+          <t>道具类型</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="J81" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L81" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N81" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>图标资源地址</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="J82" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>stackLimit</t>
         </is>
       </c>
       <c r="L82" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N82" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>堆叠上限</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="J83" s="0" t="inlineStr">
-        <is>
-          <t>colliderRadius</t>
-        </is>
-      </c>
-      <c r="L83" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N83" s="0" t="inlineStr">
-        <is>
-          <t>碰撞体半径</t>
+      <c r="B83" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Player</t>
+        </is>
+      </c>
+      <c r="G83" s="0" t="inlineStr">
+        <is>
+          <t>玩家属性</t>
+        </is>
+      </c>
+      <c r="I83" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="J84" s="0" t="inlineStr">
         <is>
-          <t>maxStamina</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L84" s="0" t="inlineStr">
@@ -2554,48 +2554,48 @@
       </c>
       <c r="N84" s="0" t="inlineStr">
         <is>
-          <t>最大体力</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="J85" s="0" t="inlineStr">
         <is>
-          <t>staminaRecoveryRate</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L85" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N85" s="0" t="inlineStr">
         <is>
-          <t>体力恢复速率</t>
+          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="J86" s="0" t="inlineStr">
         <is>
-          <t>dodgeStaminaCost</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L86" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N86" s="0" t="inlineStr">
         <is>
-          <t>闪避消耗体力</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="J87" s="0" t="inlineStr">
         <is>
-          <t>dodgeSpeed</t>
+          <t>rotationSpeed</t>
         </is>
       </c>
       <c r="L87" s="0" t="inlineStr">
@@ -2605,14 +2605,14 @@
       </c>
       <c r="N87" s="0" t="inlineStr">
         <is>
-          <t>闪避速度</t>
+          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="J88" s="0" t="inlineStr">
         <is>
-          <t>dodgeDuration</t>
+          <t>colliderRadius</t>
         </is>
       </c>
       <c r="L88" s="0" t="inlineStr">
@@ -2622,150 +2622,150 @@
       </c>
       <c r="N88" s="0" t="inlineStr">
         <is>
-          <t>闪避持续时间</t>
+          <t>碰撞体半径</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="J89" s="0" t="inlineStr">
         <is>
+          <t>maxStamina</t>
+        </is>
+      </c>
+      <c r="L89" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N89" s="0" t="inlineStr">
+        <is>
+          <t>最大体力</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="J90" s="0" t="inlineStr">
+        <is>
+          <t>staminaRecoveryRate</t>
+        </is>
+      </c>
+      <c r="L90" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N90" s="0" t="inlineStr">
+        <is>
+          <t>体力恢复速率</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="J91" s="0" t="inlineStr">
+        <is>
+          <t>dodgeStaminaCost</t>
+        </is>
+      </c>
+      <c r="L91" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N91" s="0" t="inlineStr">
+        <is>
+          <t>闪避消耗体力</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="J92" s="0" t="inlineStr">
+        <is>
+          <t>dodgeSpeed</t>
+        </is>
+      </c>
+      <c r="L92" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N92" s="0" t="inlineStr">
+        <is>
+          <t>闪避速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="J93" s="0" t="inlineStr">
+        <is>
+          <t>dodgeDuration</t>
+        </is>
+      </c>
+      <c r="L93" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N93" s="0" t="inlineStr">
+        <is>
+          <t>闪避持续时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="J94" s="0" t="inlineStr">
+        <is>
           <t>prefab</t>
         </is>
       </c>
-      <c r="L89" s="0" t="inlineStr">
+      <c r="L94" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N89" s="0" t="inlineStr">
+      <c r="N94" s="0" t="inlineStr">
         <is>
           <t>预制体</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="J90" t="inlineStr">
+    <row r="95">
+      <c r="J95" s="0" t="inlineStr">
         <is>
           <t>idleAnim</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="L95" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="N95" s="0" t="inlineStr">
         <is>
           <t>待机动画名</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>moveAnim</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>移动动画名</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>dodgeAnim</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>闪避动画名</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>reloadAnim</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>换弹动画名</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>deadAnim</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>死亡动画名</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Enemy</t>
-        </is>
-      </c>
-      <c r="G95" s="0" t="inlineStr">
-        <is>
-          <t>敌人属性</t>
-        </is>
-      </c>
-      <c r="I95" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="J96" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>moveAnim</t>
         </is>
       </c>
       <c r="L96" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N96" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>移动动画名</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="J97" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>dodgeAnim</t>
         </is>
       </c>
       <c r="L97" s="0" t="inlineStr">
@@ -2775,31 +2775,31 @@
       </c>
       <c r="N97" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>闪避动画名</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="J98" s="0" t="inlineStr">
         <is>
-          <t>maxHp</t>
+          <t>reloadAnim</t>
         </is>
       </c>
       <c r="L98" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N98" s="0" t="inlineStr">
         <is>
-          <t>最大血量</t>
+          <t>换弹动画名</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="J99" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>weaponSwitchCooldown</t>
         </is>
       </c>
       <c r="L99" s="0" t="inlineStr">
@@ -2809,133 +2809,133 @@
       </c>
       <c r="N99" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>武器切换冷却</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="J100" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>deadAnim</t>
         </is>
       </c>
       <c r="L100" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N100" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>死亡动画名</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="J101" s="0" t="inlineStr">
-        <is>
-          <t>attackDamage</t>
-        </is>
-      </c>
-      <c r="L101" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N101" s="0" t="inlineStr">
-        <is>
-          <t>攻击伤害</t>
+      <c r="B101" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Enemy</t>
+        </is>
+      </c>
+      <c r="G101" s="0" t="inlineStr">
+        <is>
+          <t>敌人属性</t>
+        </is>
+      </c>
+      <c r="I101" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="J102" s="0" t="inlineStr">
         <is>
-          <t>attackRange</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L102" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N102" s="0" t="inlineStr">
         <is>
-          <t>攻击范围</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="J103" s="0" t="inlineStr">
         <is>
-          <t>attackInterval</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L103" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N103" s="0" t="inlineStr">
         <is>
-          <t>攻击间隔</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="J104" s="0" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L104" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N104" s="0" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Wave</t>
-        </is>
-      </c>
-      <c r="G105" s="0" t="inlineStr">
-        <is>
-          <t>波次配置</t>
-        </is>
-      </c>
-      <c r="I105" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J105" s="0" t="inlineStr">
+        <is>
+          <t>moveSpeed</t>
+        </is>
+      </c>
+      <c r="L105" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N105" s="0" t="inlineStr">
+        <is>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="J106" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>rotationSpeed</t>
         </is>
       </c>
       <c r="L106" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N106" s="0" t="inlineStr">
         <is>
-          <t>波次ID</t>
+          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="J107" s="0" t="inlineStr">
         <is>
-          <t>levelId</t>
+          <t>attackDamage</t>
         </is>
       </c>
       <c r="L107" s="0" t="inlineStr">
@@ -2945,116 +2945,116 @@
       </c>
       <c r="N107" s="0" t="inlineStr">
         <is>
-          <t>关卡ID</t>
+          <t>攻击伤害</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="J108" s="0" t="inlineStr">
         <is>
-          <t>waveIndex</t>
+          <t>attackRange</t>
         </is>
       </c>
       <c r="L108" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N108" s="0" t="inlineStr">
         <is>
-          <t>波次索引</t>
+          <t>攻击范围</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="J109" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>attackInterval</t>
         </is>
       </c>
       <c r="L109" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N109" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>攻击间隔</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="J110" s="0" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>pathRefreshInterval</t>
         </is>
       </c>
       <c r="L110" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N110" s="0" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>路径刷新间隔</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="J111" s="0" t="inlineStr">
         <is>
-          <t>spawnInterval</t>
+          <t>prefab</t>
         </is>
       </c>
       <c r="L111" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N111" s="0" t="inlineStr">
         <is>
-          <t>刷新间隔</t>
+          <t>预制体</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="J112" s="0" t="inlineStr">
-        <is>
-          <t>spawnRadius</t>
-        </is>
-      </c>
-      <c r="L112" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N112" s="0" t="inlineStr">
-        <is>
-          <t>刷新半径</t>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Wave</t>
+        </is>
+      </c>
+      <c r="G112" s="0" t="inlineStr">
+        <is>
+          <t>波次配置</t>
+        </is>
+      </c>
+      <c r="I112" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Drop</t>
-        </is>
-      </c>
-      <c r="G113" s="0" t="inlineStr">
-        <is>
-          <t>掉落配置</t>
-        </is>
-      </c>
-      <c r="I113" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J113" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L113" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N113" s="0" t="inlineStr">
+        <is>
+          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="J114" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>levelId</t>
         </is>
       </c>
       <c r="L114" s="0" t="inlineStr">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="N114" s="0" t="inlineStr">
         <is>
-          <t>掉落ID</t>
+          <t>关卡ID</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="J115" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>waveIndex</t>
         </is>
       </c>
       <c r="L115" s="0" t="inlineStr">
@@ -3081,14 +3081,14 @@
       </c>
       <c r="N115" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>波次索引</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="J116" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L116" s="0" t="inlineStr">
@@ -3098,14 +3098,14 @@
       </c>
       <c r="N116" s="0" t="inlineStr">
         <is>
-          <t>道具ID</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="J117" s="0" t="inlineStr">
         <is>
-          <t>dropRate</t>
+          <t>count</t>
         </is>
       </c>
       <c r="L117" s="0" t="inlineStr">
@@ -3115,53 +3115,53 @@
       </c>
       <c r="N117" s="0" t="inlineStr">
         <is>
-          <t>掉落概率(万分之一)</t>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="J118" s="0" t="inlineStr">
         <is>
-          <t>minCount</t>
+          <t>spawnInterval</t>
         </is>
       </c>
       <c r="L118" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N118" s="0" t="inlineStr">
         <is>
-          <t>最小数量</t>
+          <t>刷新间隔</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="J119" s="0" t="inlineStr">
         <is>
-          <t>maxCount</t>
+          <t>spawnRadius</t>
         </is>
       </c>
       <c r="L119" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N119" s="0" t="inlineStr">
         <is>
-          <t>最大数量</t>
+          <t>刷新半径</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>cfg.Buff</t>
+          <t>cfg.Drop</t>
         </is>
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>Buff配置</t>
+          <t>掉落配置</t>
         </is>
       </c>
       <c r="I120" s="0" t="inlineStr">
@@ -3183,48 +3183,48 @@
       </c>
       <c r="N121" s="0" t="inlineStr">
         <is>
-          <t>BuffID</t>
+          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="J122" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L122" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N122" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="J123" s="0" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L123" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N123" s="0" t="inlineStr">
         <is>
-          <t>持续时间</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="J124" s="0" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>dropRate</t>
         </is>
       </c>
       <c r="L124" s="0" t="inlineStr">
@@ -3234,53 +3234,53 @@
       </c>
       <c r="N124" s="0" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>掉落概率(万分之一)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="J125" s="0" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>minCount</t>
         </is>
       </c>
       <c r="L125" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N125" s="0" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>最小数量</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="J126" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>maxCount</t>
         </is>
       </c>
       <c r="L126" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N126" s="0" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>最大数量</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>cfg.Portal</t>
+          <t>cfg.Buff</t>
         </is>
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>传送门配置</t>
+          <t>Buff配置</t>
         </is>
       </c>
       <c r="I127" s="0" t="inlineStr">
@@ -3302,14 +3302,14 @@
       </c>
       <c r="N128" s="0" t="inlineStr">
         <is>
-          <t>传送门ID</t>
+          <t>BuffID</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="J129" s="0" t="inlineStr">
         <is>
-          <t>portalType</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L129" s="0" t="inlineStr">
@@ -3319,65 +3319,65 @@
       </c>
       <c r="N129" s="0" t="inlineStr">
         <is>
-          <t>传送门类型</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="J130" s="0" t="inlineStr">
         <is>
-          <t>targetLevelId</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="L130" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N130" s="0" t="inlineStr">
         <is>
-          <t>目标关卡ID</t>
+          <t>持续时间</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="J131" s="0" t="inlineStr">
         <is>
-          <t>targetSceneName</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="L131" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N131" s="0" t="inlineStr">
         <is>
-          <t>目标场景名</t>
+          <t>效果类型</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="J132" s="0" t="inlineStr">
         <is>
-          <t>spawnCondition</t>
+          <t>value</t>
         </is>
       </c>
       <c r="L132" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N132" s="0" t="inlineStr">
         <is>
-          <t>出现条件</t>
+          <t>数值</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="J133" s="0" t="inlineStr">
         <is>
-          <t>conditionParam</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L133" s="0" t="inlineStr">
@@ -3387,48 +3387,48 @@
       </c>
       <c r="N133" s="0" t="inlineStr">
         <is>
-          <t>条件参数</t>
+          <t>图标</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="J134" s="0" t="inlineStr">
-        <is>
-          <t>keepPlayerState</t>
-        </is>
-      </c>
-      <c r="L134" s="0" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="N134" s="0" t="inlineStr">
-        <is>
-          <t>保留玩家状态</t>
+      <c r="B134" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Portal</t>
+        </is>
+      </c>
+      <c r="G134" s="0" t="inlineStr">
+        <is>
+          <t>传送门配置</t>
+        </is>
+      </c>
+      <c r="I134" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="J135" s="0" t="inlineStr">
         <is>
-          <t>promptText</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L135" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N135" s="0" t="inlineStr">
         <is>
-          <t>提示文本</t>
+          <t>传送门ID</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="J136" s="0" t="inlineStr">
         <is>
-          <t>transitionType</t>
+          <t>portalType</t>
         </is>
       </c>
       <c r="L136" s="0" t="inlineStr">
@@ -3438,789 +3438,1843 @@
       </c>
       <c r="N136" s="0" t="inlineStr">
         <is>
-          <t>转场类型</t>
+          <t>传送门类型</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="J137" s="0" t="inlineStr">
         <is>
-          <t>transitionDuration</t>
+          <t>targetLevelId</t>
         </is>
       </c>
       <c r="L137" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N137" s="0" t="inlineStr">
         <is>
-          <t>转场时长</t>
+          <t>目标关卡ID</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="B138" s="0" t="inlineStr">
-        <is>
-          <t>cfg.InventoryConfig</t>
-        </is>
-      </c>
-      <c r="G138" s="0" t="inlineStr">
-        <is>
-          <t>背包容量配置</t>
-        </is>
-      </c>
-      <c r="I138" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J138" s="0" t="inlineStr">
+        <is>
+          <t>targetSceneName</t>
+        </is>
+      </c>
+      <c r="L138" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N138" s="0" t="inlineStr">
+        <is>
+          <t>目标场景名</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="J139" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>spawnCondition</t>
         </is>
       </c>
       <c r="L139" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N139" s="0" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>出现条件</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="J140" s="0" t="inlineStr">
         <is>
-          <t>tempBagCapacity</t>
+          <t>conditionParam</t>
         </is>
       </c>
       <c r="L140" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N140" s="0" t="inlineStr">
         <is>
-          <t>临时背包槽位</t>
+          <t>条件参数</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="J141" s="0" t="inlineStr">
         <is>
+          <t>keepPlayerState</t>
+        </is>
+      </c>
+      <c r="L141" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N141" s="0" t="inlineStr">
+        <is>
+          <t>保留玩家状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="J142" s="0" t="inlineStr">
+        <is>
+          <t>promptText</t>
+        </is>
+      </c>
+      <c r="L142" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N142" s="0" t="inlineStr">
+        <is>
+          <t>提示文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="J143" s="0" t="inlineStr">
+        <is>
+          <t>transitionType</t>
+        </is>
+      </c>
+      <c r="L143" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N143" s="0" t="inlineStr">
+        <is>
+          <t>转场类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="J144" s="0" t="inlineStr">
+        <is>
+          <t>transitionDuration</t>
+        </is>
+      </c>
+      <c r="L144" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N144" s="0" t="inlineStr">
+        <is>
+          <t>转场时长</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="0" t="inlineStr">
+        <is>
+          <t>cfg.InventoryConfig</t>
+        </is>
+      </c>
+      <c r="G145" s="0" t="inlineStr">
+        <is>
+          <t>背包容量配置</t>
+        </is>
+      </c>
+      <c r="I145" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="J146" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L146" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N146" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="J147" s="0" t="inlineStr">
+        <is>
+          <t>tempBagCapacity</t>
+        </is>
+      </c>
+      <c r="L147" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N147" s="0" t="inlineStr">
+        <is>
+          <t>临时背包槽位</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="J148" s="0" t="inlineStr">
+        <is>
           <t>warehouseCapacity</t>
         </is>
       </c>
-      <c r="L141" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N141" s="0" t="inlineStr">
+      <c r="L148" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N148" s="0" t="inlineStr">
         <is>
           <t>仓库槽位</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="B142" t="inlineStr">
+    <row r="149">
+      <c r="B149" s="0" t="inlineStr">
         <is>
           <t>cfg.Camera</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G149" s="0" t="inlineStr">
         <is>
           <t>相机配置</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H149" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="J143" t="inlineStr">
+    <row r="150">
+      <c r="J150" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr">
+      <c r="L150" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N150" s="0" t="inlineStr">
         <is>
           <t>配置ID</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="J144" t="inlineStr">
+    <row r="151">
+      <c r="J151" s="0" t="inlineStr">
         <is>
           <t>smoothTime</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr">
+      <c r="L151" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N151" s="0" t="inlineStr">
         <is>
           <t>相机平滑时间</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="J145" t="inlineStr">
+    <row r="152">
+      <c r="J152" s="0" t="inlineStr">
         <is>
           <t>defaultFov</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr">
+      <c r="L152" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N152" s="0" t="inlineStr">
         <is>
           <t>默认FOV</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="J146" t="inlineStr">
+    <row r="153">
+      <c r="J153" s="0" t="inlineStr">
         <is>
           <t>fovSmoothTime</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr">
+      <c r="L153" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N153" s="0" t="inlineStr">
         <is>
           <t>FOV平滑时间</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="J147" t="inlineStr">
+    <row r="154">
+      <c r="J154" s="0" t="inlineStr">
         <is>
           <t>shakeDamping</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr">
+      <c r="L154" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N154" s="0" t="inlineStr">
         <is>
           <t>震动衰减速度</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="J148" t="inlineStr">
+    <row r="155">
+      <c r="J155" s="0" t="inlineStr">
         <is>
           <t>scopeRenderSize</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
+      <c r="L155" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N155" s="0" t="inlineStr">
         <is>
           <t>狙击镜渲染纹理尺寸</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="J149" t="inlineStr">
+    <row r="156">
+      <c r="J156" s="0" t="inlineStr">
         <is>
           <t>scopeCameraFov</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
+      <c r="L156" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N156" s="0" t="inlineStr">
         <is>
           <t>狙击镜相机FOV</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="J150" t="inlineStr">
+    <row r="157">
+      <c r="J157" s="0" t="inlineStr">
         <is>
           <t>defaultOrthographicSize</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
+      <c r="L157" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N157" s="0" t="inlineStr">
         <is>
           <t>默认正交尺寸</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="B151" t="inlineStr">
+    <row r="158">
+      <c r="B158" s="0" t="inlineStr">
         <is>
           <t>cfg.Ballistic</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="G158" s="0" t="inlineStr">
         <is>
           <t>弹道全局配置</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="H158" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="J152" t="inlineStr">
+    <row r="159">
+      <c r="J159" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr">
+      <c r="L159" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N159" s="0" t="inlineStr">
         <is>
           <t>配置ID</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="J153" t="inlineStr">
+    <row r="160">
+      <c r="J160" s="0" t="inlineStr">
         <is>
           <t>tracerRadius</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr">
+      <c r="L160" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N160" s="0" t="inlineStr">
         <is>
           <t>Tracer射线检测半径</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="J154" t="inlineStr">
+    <row r="161">
+      <c r="J161" s="0" t="inlineStr">
         <is>
           <t>tracerStartWidth</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr">
+      <c r="L161" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N161" s="0" t="inlineStr">
         <is>
           <t>Tracer起始宽度</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="J155" t="inlineStr">
+    <row r="162">
+      <c r="J162" s="0" t="inlineStr">
         <is>
           <t>tracerEndWidth</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
+      <c r="L162" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N162" s="0" t="inlineStr">
         <is>
           <t>Tracer结束宽度</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="J156" t="inlineStr">
+    <row r="163">
+      <c r="J163" s="0" t="inlineStr">
         <is>
           <t>tracerTailLength</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr">
+      <c r="L163" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N163" s="0" t="inlineStr">
         <is>
           <t>Tracer尾迹长度</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="J157" t="inlineStr">
+    <row r="164">
+      <c r="J164" s="0" t="inlineStr">
         <is>
           <t>maxActiveTracers</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr">
+      <c r="L164" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N164" s="0" t="inlineStr">
         <is>
           <t>最大同时存在Tracer数量</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="J158" t="inlineStr">
+    <row r="165">
+      <c r="J165" s="0" t="inlineStr">
         <is>
           <t>hitLayers</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="L165" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr">
+      <c r="N165" s="0" t="inlineStr">
         <is>
           <t>默认命中层级</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="J159" t="inlineStr">
+    <row r="166">
+      <c r="J166" s="0" t="inlineStr">
         <is>
           <t>tracerStartColor</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="L166" s="0" t="inlineStr">
         <is>
           <t>cfg.Color#sep=,</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr">
+      <c r="N166" s="0" t="inlineStr">
         <is>
           <t>Tracer起始颜色</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="J160" t="inlineStr">
+    <row r="167">
+      <c r="J167" s="0" t="inlineStr">
         <is>
           <t>tracerEndColor</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
+      <c r="L167" s="0" t="inlineStr">
         <is>
           <t>cfg.Color#sep=,</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr">
+      <c r="N167" s="0" t="inlineStr">
         <is>
           <t>Tracer结束颜色</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="B161" t="inlineStr">
+    <row r="168">
+      <c r="B168" s="0" t="inlineStr">
         <is>
           <t>cfg.UiConfig</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="G168" s="0" t="inlineStr">
         <is>
           <t>UI全局配置</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="H168" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="J162" t="inlineStr">
+    <row r="169">
+      <c r="J169" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr">
+      <c r="L169" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N169" s="0" t="inlineStr">
         <is>
           <t>配置ID</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="J163" t="inlineStr">
+    <row r="170">
+      <c r="J170" s="0" t="inlineStr">
         <is>
           <t>damageNumberPoolSize</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr">
+      <c r="L170" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N170" s="0" t="inlineStr">
         <is>
           <t>伤害数字对象池大小</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="J164" t="inlineStr">
+    <row r="171">
+      <c r="J171" s="0" t="inlineStr">
         <is>
           <t>damageNumberFadeDuration</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr">
+      <c r="L171" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N171" s="0" t="inlineStr">
         <is>
           <t>伤害数字渐隐时间</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="J165" t="inlineStr">
+    <row r="172">
+      <c r="J172" s="0" t="inlineStr">
         <is>
           <t>damageNumberMoveOffset</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
+      <c r="L172" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N172" s="0" t="inlineStr">
         <is>
           <t>伤害数字上浮偏移</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="J166" t="inlineStr">
+    <row r="173">
+      <c r="J173" s="0" t="inlineStr">
         <is>
           <t>damageNumberNormalColor</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="L173" s="0" t="inlineStr">
         <is>
           <t>cfg.Color#sep=,</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr">
+      <c r="N173" s="0" t="inlineStr">
         <is>
           <t>普通伤害数字颜色</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="J167" t="inlineStr">
+    <row r="174">
+      <c r="J174" s="0" t="inlineStr">
         <is>
           <t>damageNumberCriticalColor</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="L174" s="0" t="inlineStr">
         <is>
           <t>cfg.Color#sep=,</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr">
+      <c r="N174" s="0" t="inlineStr">
         <is>
           <t>暴击伤害数字颜色</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="J168" t="inlineStr">
+    <row r="175">
+      <c r="J175" s="0" t="inlineStr">
         <is>
           <t>damageNumberNormalFontSize</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr">
+      <c r="L175" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N175" s="0" t="inlineStr">
         <is>
           <t>普通伤害数字字体大小</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="J169" t="inlineStr">
+    <row r="176">
+      <c r="J176" s="0" t="inlineStr">
         <is>
           <t>damageNumberCriticalFontSize</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
+      <c r="L176" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N176" s="0" t="inlineStr">
         <is>
           <t>暴击伤害数字字体大小</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="J170" t="inlineStr">
+    <row r="177">
+      <c r="J177" s="0" t="inlineStr">
         <is>
           <t>hitMarkerPoolSize</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
+      <c r="L177" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N177" s="0" t="inlineStr">
         <is>
           <t>命中标记对象池大小</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="J171" t="inlineStr">
+    <row r="178">
+      <c r="J178" s="0" t="inlineStr">
         <is>
           <t>hitMarkerDuration</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
+      <c r="L178" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N178" s="0" t="inlineStr">
         <is>
           <t>命中标记显示时间</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="J172" t="inlineStr">
+    <row r="179">
+      <c r="J179" s="0" t="inlineStr">
         <is>
           <t>hitMarkerSize</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
+      <c r="L179" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N179" s="0" t="inlineStr">
         <is>
           <t>命中标记大小</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="J173" t="inlineStr">
+    <row r="180">
+      <c r="J180" s="0" t="inlineStr">
         <is>
           <t>hitMarkerNormalColor</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
+      <c r="L180" s="0" t="inlineStr">
         <is>
           <t>cfg.Color#sep=,</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr">
+      <c r="N180" s="0" t="inlineStr">
         <is>
           <t>普通命中标记颜色</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="J174" t="inlineStr">
+    <row r="181">
+      <c r="J181" s="0" t="inlineStr">
         <is>
           <t>hitMarkerCriticalColor</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
+      <c r="L181" s="0" t="inlineStr">
         <is>
           <t>cfg.Color#sep=,</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr">
+      <c r="N181" s="0" t="inlineStr">
         <is>
           <t>暴击命中标记颜色</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="J175" t="inlineStr">
+    <row r="182">
+      <c r="J182" s="0" t="inlineStr">
         <is>
           <t>indicatorFadeSpeed</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr">
+      <c r="L182" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N182" s="0" t="inlineStr">
         <is>
           <t>受击指示器淡出速度</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="J176" t="inlineStr">
+    <row r="183">
+      <c r="J183" s="0" t="inlineStr">
         <is>
           <t>indicatorColor</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
+      <c r="L183" s="0" t="inlineStr">
         <is>
           <t>cfg.Color#sep=,</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr">
+      <c r="N183" s="0" t="inlineStr">
         <is>
           <t>受击指示器颜色</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="J177" t="inlineStr">
+    <row r="184">
+      <c r="J184" s="0" t="inlineStr">
         <is>
           <t>loadingTextFormat</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
+      <c r="L184" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr">
+      <c r="N184" s="0" t="inlineStr">
         <is>
           <t>加载进度文本格式</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="B178" t="inlineStr">
+    <row r="185">
+      <c r="B185" s="0" t="inlineStr">
         <is>
           <t>cfg.Pickup</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="G185" s="0" t="inlineStr">
         <is>
           <t>拾取物配置</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
+      <c r="H185" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="J179" t="inlineStr">
+    <row r="186">
+      <c r="J186" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr">
+      <c r="L186" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N186" s="0" t="inlineStr">
         <is>
           <t>配置ID</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="J180" t="inlineStr">
+    <row r="187">
+      <c r="J187" s="0" t="inlineStr">
         <is>
           <t>colliderRadius</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
+      <c r="L187" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N187" s="0" t="inlineStr">
         <is>
           <t>拾取物碰撞体半径</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="J181" t="inlineStr">
+    <row r="188">
+      <c r="J188" s="0" t="inlineStr">
         <is>
           <t>visualScale</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr">
+      <c r="L188" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N188" s="0" t="inlineStr">
         <is>
           <t>拾取物视觉缩放</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="J182" t="inlineStr">
+    <row r="189">
+      <c r="J189" s="0" t="inlineStr">
         <is>
           <t>sortingOrder</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr">
+      <c r="L189" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N189" s="0" t="inlineStr">
         <is>
           <t>拾取物渲染排序</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Building</t>
+        </is>
+      </c>
+      <c r="G190" s="0" t="inlineStr">
+        <is>
+          <t>建筑配置</t>
+        </is>
+      </c>
+      <c r="I190" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="J191" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L191" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N191" s="0" t="inlineStr">
+        <is>
+          <t>建筑ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="J192" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L192" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N192" s="0" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="J193" s="0" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="L193" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N193" s="0" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="J194" s="0" t="inlineStr">
+        <is>
+          <t>buildingType</t>
+        </is>
+      </c>
+      <c r="L194" s="0" t="inlineStr">
+        <is>
+          <t>cfg.EBuildingType</t>
+        </is>
+      </c>
+      <c r="N194" s="0" t="inlineStr">
+        <is>
+          <t>建筑类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="J195" s="0" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="L195" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N195" s="0" t="inlineStr">
+        <is>
+          <t>图标</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="J196" s="0" t="inlineStr">
+        <is>
+          <t>maxLevel</t>
+        </is>
+      </c>
+      <c r="L196" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N196" s="0" t="inlineStr">
+        <is>
+          <t>最大等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="J197" s="0" t="inlineStr">
+        <is>
+          <t>buildCostGold</t>
+        </is>
+      </c>
+      <c r="L197" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N197" s="0" t="inlineStr">
+        <is>
+          <t>建造金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="J198" s="0" t="inlineStr">
+        <is>
+          <t>buildCostItems</t>
+        </is>
+      </c>
+      <c r="L198" s="0" t="inlineStr">
+        <is>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+        </is>
+      </c>
+      <c r="N198" s="0" t="inlineStr">
+        <is>
+          <t>建造材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="J199" s="0" t="inlineStr">
+        <is>
+          <t>buildTime</t>
+        </is>
+      </c>
+      <c r="L199" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N199" s="0" t="inlineStr">
+        <is>
+          <t>建造耗时</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="J200" s="0" t="inlineStr">
+        <is>
+          <t>upgradeCostGold</t>
+        </is>
+      </c>
+      <c r="L200" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N200" s="0" t="inlineStr">
+        <is>
+          <t>升级金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="J201" s="0" t="inlineStr">
+        <is>
+          <t>upgradeCostItems</t>
+        </is>
+      </c>
+      <c r="L201" s="0" t="inlineStr">
+        <is>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+        </is>
+      </c>
+      <c r="N201" s="0" t="inlineStr">
+        <is>
+          <t>升级材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="J202" s="0" t="inlineStr">
+        <is>
+          <t>upgradeTime</t>
+        </is>
+      </c>
+      <c r="L202" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N202" s="0" t="inlineStr">
+        <is>
+          <t>升级耗时</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="J203" s="0" t="inlineStr">
+        <is>
+          <t>productionSlotCount</t>
+        </is>
+      </c>
+      <c r="L203" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N203" s="0" t="inlineStr">
+        <is>
+          <t>生产槽位</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="J204" s="0" t="inlineStr">
+        <is>
+          <t>unlockLevel</t>
+        </is>
+      </c>
+      <c r="L204" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N204" s="0" t="inlineStr">
+        <is>
+          <t>解锁等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Production</t>
+        </is>
+      </c>
+      <c r="G205" s="0" t="inlineStr">
+        <is>
+          <t>生产配方</t>
+        </is>
+      </c>
+      <c r="I205" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="J206" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L206" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N206" s="0" t="inlineStr">
+        <is>
+          <t>配方ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="J207" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L207" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N207" s="0" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="J208" s="0" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="L208" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N208" s="0" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="J209" s="0" t="inlineStr">
+        <is>
+          <t>buildingId</t>
+        </is>
+      </c>
+      <c r="L209" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N209" s="0" t="inlineStr">
+        <is>
+          <t>建筑ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="J210" s="0" t="inlineStr">
+        <is>
+          <t>levelRequired</t>
+        </is>
+      </c>
+      <c r="L210" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N210" s="0" t="inlineStr">
+        <is>
+          <t>等级要求</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="J211" s="0" t="inlineStr">
+        <is>
+          <t>inputItems</t>
+        </is>
+      </c>
+      <c r="L211" s="0" t="inlineStr">
+        <is>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+        </is>
+      </c>
+      <c r="N211" s="0" t="inlineStr">
+        <is>
+          <t>输入材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="J212" s="0" t="inlineStr">
+        <is>
+          <t>outputItemId</t>
+        </is>
+      </c>
+      <c r="L212" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N212" s="0" t="inlineStr">
+        <is>
+          <t>产出物品</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="J213" s="0" t="inlineStr">
+        <is>
+          <t>outputCount</t>
+        </is>
+      </c>
+      <c r="L213" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N213" s="0" t="inlineStr">
+        <is>
+          <t>产出数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="J214" s="0" t="inlineStr">
+        <is>
+          <t>productionTime</t>
+        </is>
+      </c>
+      <c r="L214" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N214" s="0" t="inlineStr">
+        <is>
+          <t>生产耗时</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="J215" s="0" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="L215" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N215" s="0" t="inlineStr">
+        <is>
+          <t>图标</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Order</t>
+        </is>
+      </c>
+      <c r="G216" s="0" t="inlineStr">
+        <is>
+          <t>订单配置</t>
+        </is>
+      </c>
+      <c r="I216" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="J217" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L217" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N217" s="0" t="inlineStr">
+        <is>
+          <t>订单ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="J218" s="0" t="inlineStr">
+        <is>
+          <t>requiredItems</t>
+        </is>
+      </c>
+      <c r="L218" s="0" t="inlineStr">
+        <is>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+        </is>
+      </c>
+      <c r="N218" s="0" t="inlineStr">
+        <is>
+          <t>需求物品</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="J219" s="0" t="inlineStr">
+        <is>
+          <t>rewardGold</t>
+        </is>
+      </c>
+      <c r="L219" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N219" s="0" t="inlineStr">
+        <is>
+          <t>奖励金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="J220" s="0" t="inlineStr">
+        <is>
+          <t>rewardItems</t>
+        </is>
+      </c>
+      <c r="L220" s="0" t="inlineStr">
+        <is>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+        </is>
+      </c>
+      <c r="N220" s="0" t="inlineStr">
+        <is>
+          <t>奖励物品</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="J221" s="0" t="inlineStr">
+        <is>
+          <t>rewardExp</t>
+        </is>
+      </c>
+      <c r="L221" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N221" s="0" t="inlineStr">
+        <is>
+          <t>奖励经验</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="J222" s="0" t="inlineStr">
+        <is>
+          <t>timeLimit</t>
+        </is>
+      </c>
+      <c r="L222" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N222" s="0" t="inlineStr">
+        <is>
+          <t>时限</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="J223" s="0" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L223" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N223" s="0" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="J224" s="0" t="inlineStr">
+        <is>
+          <t>minPlayerLevel</t>
+        </is>
+      </c>
+      <c r="L224" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N224" s="0" t="inlineStr">
+        <is>
+          <t>最低等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" s="0" t="inlineStr">
+        <is>
+          <t>cfg.SimTimeConfig</t>
+        </is>
+      </c>
+      <c r="G225" s="0" t="inlineStr">
+        <is>
+          <t>经营时间配置</t>
+        </is>
+      </c>
+      <c r="I225" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="J226" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L226" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N226" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="J227" s="0" t="inlineStr">
+        <is>
+          <t>baseSpeed</t>
+        </is>
+      </c>
+      <c r="L227" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N227" s="0" t="inlineStr">
+        <is>
+          <t>基础速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="J228" s="0" t="inlineStr">
+        <is>
+          <t>fastSpeed</t>
+        </is>
+      </c>
+      <c r="L228" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N228" s="0" t="inlineStr">
+        <is>
+          <t>加速速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="J229" s="0" t="inlineStr">
+        <is>
+          <t>maxSpeed</t>
+        </is>
+      </c>
+      <c r="L229" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N229" s="0" t="inlineStr">
+        <is>
+          <t>最大速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="J230" s="0" t="inlineStr">
+        <is>
+          <t>orderRefreshInterval</t>
+        </is>
+      </c>
+      <c r="L230" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N230" s="0" t="inlineStr">
+        <is>
+          <t>订单刷新间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="J231" s="0" t="inlineStr">
+        <is>
+          <t>maxOrderCount</t>
+        </is>
+      </c>
+      <c r="L231" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N231" s="0" t="inlineStr">
+        <is>
+          <t>最大订单数</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>cfg.Camera3D</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>3D摄像机配置</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>配置ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>pitchAngle</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>俯视角度</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>initialHeight</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>初始高度</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>initialDistance</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>初始距离</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>fov</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>视场角</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>minZoom</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>最小缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>maxZoom</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>最大缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>moveSpeed</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>移动速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>zoomSpeed</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>缩放速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>maxRotationAngle</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>最大旋转角度</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>rotationSpeed</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>旋转速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>followSmoothTime</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>跟随平滑时间</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P244"/>
+  <dimension ref="A1:P252"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -3018,43 +3018,43 @@
       </c>
     </row>
     <row r="112">
-      <c r="B112" s="0" t="inlineStr">
+      <c r="J112" s="0" t="inlineStr">
+        <is>
+          <t>chaseRange</t>
+        </is>
+      </c>
+      <c r="L112" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N112" s="0" t="inlineStr">
+        <is>
+          <t>仇恨范围（追击触发距离）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="0" t="inlineStr">
         <is>
           <t>cfg.Wave</t>
         </is>
       </c>
-      <c r="G112" s="0" t="inlineStr">
+      <c r="G113" s="0" t="inlineStr">
         <is>
           <t>波次配置</t>
         </is>
       </c>
-      <c r="I112" s="0" t="inlineStr">
+      <c r="I113" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="J113" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L113" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N113" s="0" t="inlineStr">
-        <is>
-          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="J114" s="0" t="inlineStr">
         <is>
-          <t>levelId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L114" s="0" t="inlineStr">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="N114" s="0" t="inlineStr">
         <is>
-          <t>关卡ID</t>
+          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="J115" s="0" t="inlineStr">
         <is>
-          <t>waveIndex</t>
+          <t>levelId</t>
         </is>
       </c>
       <c r="L115" s="0" t="inlineStr">
@@ -3081,14 +3081,14 @@
       </c>
       <c r="N115" s="0" t="inlineStr">
         <is>
-          <t>波次索引</t>
+          <t>关卡ID</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="J116" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>waveIndex</t>
         </is>
       </c>
       <c r="L116" s="0" t="inlineStr">
@@ -3098,14 +3098,14 @@
       </c>
       <c r="N116" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>波次索引</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="J117" s="0" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L117" s="0" t="inlineStr">
@@ -3115,82 +3115,82 @@
       </c>
       <c r="N117" s="0" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="J118" s="0" t="inlineStr">
         <is>
-          <t>spawnInterval</t>
+          <t>count</t>
         </is>
       </c>
       <c r="L118" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N118" s="0" t="inlineStr">
         <is>
-          <t>刷新间隔</t>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="J119" s="0" t="inlineStr">
         <is>
+          <t>spawnInterval</t>
+        </is>
+      </c>
+      <c r="L119" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N119" s="0" t="inlineStr">
+        <is>
+          <t>刷新间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="J120" s="0" t="inlineStr">
+        <is>
           <t>spawnRadius</t>
         </is>
       </c>
-      <c r="L119" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N119" s="0" t="inlineStr">
+      <c r="L120" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N120" s="0" t="inlineStr">
         <is>
           <t>刷新半径</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="B120" s="0" t="inlineStr">
+    <row r="121">
+      <c r="B121" s="0" t="inlineStr">
         <is>
           <t>cfg.Drop</t>
         </is>
       </c>
-      <c r="G120" s="0" t="inlineStr">
+      <c r="G121" s="0" t="inlineStr">
         <is>
           <t>掉落配置</t>
         </is>
       </c>
-      <c r="I120" s="0" t="inlineStr">
+      <c r="I121" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="J121" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L121" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N121" s="0" t="inlineStr">
-        <is>
-          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="J122" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L122" s="0" t="inlineStr">
@@ -3200,14 +3200,14 @@
       </c>
       <c r="N122" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="J123" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L123" s="0" t="inlineStr">
@@ -3217,14 +3217,14 @@
       </c>
       <c r="N123" s="0" t="inlineStr">
         <is>
-          <t>道具ID</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="J124" s="0" t="inlineStr">
         <is>
-          <t>dropRate</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L124" s="0" t="inlineStr">
@@ -3234,14 +3234,14 @@
       </c>
       <c r="N124" s="0" t="inlineStr">
         <is>
-          <t>掉落概率(万分之一)</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="J125" s="0" t="inlineStr">
         <is>
-          <t>minCount</t>
+          <t>dropRate</t>
         </is>
       </c>
       <c r="L125" s="0" t="inlineStr">
@@ -3251,235 +3251,235 @@
       </c>
       <c r="N125" s="0" t="inlineStr">
         <is>
-          <t>最小数量</t>
+          <t>掉落概率(万分之一)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="J126" s="0" t="inlineStr">
         <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="L126" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N126" s="0" t="inlineStr">
+        <is>
+          <t>最小数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="J127" s="0" t="inlineStr">
+        <is>
           <t>maxCount</t>
         </is>
       </c>
-      <c r="L126" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N126" s="0" t="inlineStr">
+      <c r="L127" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N127" s="0" t="inlineStr">
         <is>
           <t>最大数量</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="B127" s="0" t="inlineStr">
+    <row r="128">
+      <c r="B128" s="0" t="inlineStr">
         <is>
           <t>cfg.Buff</t>
         </is>
       </c>
-      <c r="G127" s="0" t="inlineStr">
+      <c r="G128" s="0" t="inlineStr">
         <is>
           <t>Buff配置</t>
         </is>
       </c>
-      <c r="I127" s="0" t="inlineStr">
+      <c r="I128" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="J128" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L128" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N128" s="0" t="inlineStr">
-        <is>
-          <t>BuffID</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="J129" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L129" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N129" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>BuffID</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="J130" s="0" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L130" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N130" s="0" t="inlineStr">
         <is>
-          <t>持续时间</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="J131" s="0" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="L131" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N131" s="0" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>持续时间</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="J132" s="0" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="L132" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N132" s="0" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>效果类型</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="J133" s="0" t="inlineStr">
         <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L133" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N133" s="0" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="J134" s="0" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="L133" s="0" t="inlineStr">
+      <c r="L134" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N133" s="0" t="inlineStr">
+      <c r="N134" s="0" t="inlineStr">
         <is>
           <t>图标</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="B134" s="0" t="inlineStr">
+    <row r="135">
+      <c r="B135" s="0" t="inlineStr">
         <is>
           <t>cfg.Portal</t>
         </is>
       </c>
-      <c r="G134" s="0" t="inlineStr">
+      <c r="G135" s="0" t="inlineStr">
         <is>
           <t>传送门配置</t>
         </is>
       </c>
-      <c r="I134" s="0" t="inlineStr">
+      <c r="I135" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="J135" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L135" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N135" s="0" t="inlineStr">
-        <is>
-          <t>传送门ID</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="J136" s="0" t="inlineStr">
         <is>
-          <t>portalType</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L136" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N136" s="0" t="inlineStr">
         <is>
-          <t>传送门类型</t>
+          <t>传送门ID</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="J137" s="0" t="inlineStr">
         <is>
-          <t>targetLevelId</t>
+          <t>portalType</t>
         </is>
       </c>
       <c r="L137" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N137" s="0" t="inlineStr">
         <is>
-          <t>目标关卡ID</t>
+          <t>传送门类型</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="J138" s="0" t="inlineStr">
         <is>
-          <t>targetSceneName</t>
+          <t>targetLevelId</t>
         </is>
       </c>
       <c r="L138" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N138" s="0" t="inlineStr">
         <is>
-          <t>目标场景名</t>
+          <t>目标关卡ID</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="J139" s="0" t="inlineStr">
         <is>
-          <t>spawnCondition</t>
+          <t>targetSceneName</t>
         </is>
       </c>
       <c r="L139" s="0" t="inlineStr">
@@ -3489,14 +3489,14 @@
       </c>
       <c r="N139" s="0" t="inlineStr">
         <is>
-          <t>出现条件</t>
+          <t>目标场景名</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="J140" s="0" t="inlineStr">
         <is>
-          <t>conditionParam</t>
+          <t>spawnCondition</t>
         </is>
       </c>
       <c r="L140" s="0" t="inlineStr">
@@ -3506,48 +3506,48 @@
       </c>
       <c r="N140" s="0" t="inlineStr">
         <is>
-          <t>条件参数</t>
+          <t>出现条件</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="J141" s="0" t="inlineStr">
         <is>
-          <t>keepPlayerState</t>
+          <t>conditionParam</t>
         </is>
       </c>
       <c r="L141" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N141" s="0" t="inlineStr">
         <is>
-          <t>保留玩家状态</t>
+          <t>条件参数</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="J142" s="0" t="inlineStr">
         <is>
-          <t>promptText</t>
+          <t>keepPlayerState</t>
         </is>
       </c>
       <c r="L142" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="N142" s="0" t="inlineStr">
         <is>
-          <t>提示文本</t>
+          <t>保留玩家状态</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="J143" s="0" t="inlineStr">
         <is>
-          <t>transitionType</t>
+          <t>promptText</t>
         </is>
       </c>
       <c r="L143" s="0" t="inlineStr">
@@ -3557,65 +3557,65 @@
       </c>
       <c r="N143" s="0" t="inlineStr">
         <is>
-          <t>转场类型</t>
+          <t>提示文本</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="J144" s="0" t="inlineStr">
         <is>
+          <t>transitionType</t>
+        </is>
+      </c>
+      <c r="L144" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N144" s="0" t="inlineStr">
+        <is>
+          <t>转场类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="J145" s="0" t="inlineStr">
+        <is>
           <t>transitionDuration</t>
         </is>
       </c>
-      <c r="L144" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N144" s="0" t="inlineStr">
+      <c r="L145" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N145" s="0" t="inlineStr">
         <is>
           <t>转场时长</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="B145" s="0" t="inlineStr">
+    <row r="146">
+      <c r="B146" s="0" t="inlineStr">
         <is>
           <t>cfg.InventoryConfig</t>
         </is>
       </c>
-      <c r="G145" s="0" t="inlineStr">
+      <c r="G146" s="0" t="inlineStr">
         <is>
           <t>背包容量配置</t>
         </is>
       </c>
-      <c r="I145" s="0" t="inlineStr">
+      <c r="I146" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="J146" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L146" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N146" s="0" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="J147" s="0" t="inlineStr">
         <is>
-          <t>tempBagCapacity</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L147" s="0" t="inlineStr">
@@ -3625,82 +3625,82 @@
       </c>
       <c r="N147" s="0" t="inlineStr">
         <is>
-          <t>临时背包槽位</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="J148" s="0" t="inlineStr">
         <is>
+          <t>tempBagCapacity</t>
+        </is>
+      </c>
+      <c r="L148" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N148" s="0" t="inlineStr">
+        <is>
+          <t>临时背包槽位</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="J149" s="0" t="inlineStr">
+        <is>
           <t>warehouseCapacity</t>
         </is>
       </c>
-      <c r="L148" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N148" s="0" t="inlineStr">
+      <c r="L149" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N149" s="0" t="inlineStr">
         <is>
           <t>仓库槽位</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="B149" s="0" t="inlineStr">
+    <row r="150">
+      <c r="B150" s="0" t="inlineStr">
         <is>
           <t>cfg.Camera</t>
         </is>
       </c>
-      <c r="G149" s="0" t="inlineStr">
+      <c r="G150" s="0" t="inlineStr">
         <is>
           <t>相机配置</t>
         </is>
       </c>
-      <c r="H149" s="0" t="inlineStr">
+      <c r="H150" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="J150" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L150" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N150" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="J151" s="0" t="inlineStr">
         <is>
-          <t>smoothTime</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L151" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N151" s="0" t="inlineStr">
         <is>
-          <t>相机平滑时间</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="J152" s="0" t="inlineStr">
         <is>
-          <t>defaultFov</t>
+          <t>smoothTime</t>
         </is>
       </c>
       <c r="L152" s="0" t="inlineStr">
@@ -3710,14 +3710,14 @@
       </c>
       <c r="N152" s="0" t="inlineStr">
         <is>
-          <t>默认FOV</t>
+          <t>相机平滑时间</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="J153" s="0" t="inlineStr">
         <is>
-          <t>fovSmoothTime</t>
+          <t>defaultFov</t>
         </is>
       </c>
       <c r="L153" s="0" t="inlineStr">
@@ -3727,14 +3727,14 @@
       </c>
       <c r="N153" s="0" t="inlineStr">
         <is>
-          <t>FOV平滑时间</t>
+          <t>默认FOV</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="J154" s="0" t="inlineStr">
         <is>
-          <t>shakeDamping</t>
+          <t>fovSmoothTime</t>
         </is>
       </c>
       <c r="L154" s="0" t="inlineStr">
@@ -3744,116 +3744,116 @@
       </c>
       <c r="N154" s="0" t="inlineStr">
         <is>
-          <t>震动衰减速度</t>
+          <t>FOV平滑时间</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="J155" s="0" t="inlineStr">
         <is>
-          <t>scopeRenderSize</t>
+          <t>shakeDamping</t>
         </is>
       </c>
       <c r="L155" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N155" s="0" t="inlineStr">
         <is>
-          <t>狙击镜渲染纹理尺寸</t>
+          <t>震动衰减速度</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="J156" s="0" t="inlineStr">
         <is>
-          <t>scopeCameraFov</t>
+          <t>scopeRenderSize</t>
         </is>
       </c>
       <c r="L156" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N156" s="0" t="inlineStr">
         <is>
-          <t>狙击镜相机FOV</t>
+          <t>狙击镜渲染纹理尺寸</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="J157" s="0" t="inlineStr">
         <is>
+          <t>scopeCameraFov</t>
+        </is>
+      </c>
+      <c r="L157" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N157" s="0" t="inlineStr">
+        <is>
+          <t>狙击镜相机FOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="J158" s="0" t="inlineStr">
+        <is>
           <t>defaultOrthographicSize</t>
         </is>
       </c>
-      <c r="L157" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N157" s="0" t="inlineStr">
+      <c r="L158" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N158" s="0" t="inlineStr">
         <is>
           <t>默认正交尺寸</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="B158" s="0" t="inlineStr">
+    <row r="159">
+      <c r="B159" s="0" t="inlineStr">
         <is>
           <t>cfg.Ballistic</t>
         </is>
       </c>
-      <c r="G158" s="0" t="inlineStr">
+      <c r="G159" s="0" t="inlineStr">
         <is>
           <t>弹道全局配置</t>
         </is>
       </c>
-      <c r="H158" s="0" t="inlineStr">
+      <c r="H159" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="J159" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L159" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N159" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="J160" s="0" t="inlineStr">
         <is>
-          <t>tracerRadius</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L160" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N160" s="0" t="inlineStr">
         <is>
-          <t>Tracer射线检测半径</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="J161" s="0" t="inlineStr">
         <is>
-          <t>tracerStartWidth</t>
+          <t>tracerRadius</t>
         </is>
       </c>
       <c r="L161" s="0" t="inlineStr">
@@ -3863,14 +3863,14 @@
       </c>
       <c r="N161" s="0" t="inlineStr">
         <is>
-          <t>Tracer起始宽度</t>
+          <t>Tracer射线检测半径</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="J162" s="0" t="inlineStr">
         <is>
-          <t>tracerEndWidth</t>
+          <t>tracerStartWidth</t>
         </is>
       </c>
       <c r="L162" s="0" t="inlineStr">
@@ -3880,14 +3880,14 @@
       </c>
       <c r="N162" s="0" t="inlineStr">
         <is>
-          <t>Tracer结束宽度</t>
+          <t>Tracer起始宽度</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="J163" s="0" t="inlineStr">
         <is>
-          <t>tracerTailLength</t>
+          <t>tracerEndWidth</t>
         </is>
       </c>
       <c r="L163" s="0" t="inlineStr">
@@ -3897,116 +3897,116 @@
       </c>
       <c r="N163" s="0" t="inlineStr">
         <is>
-          <t>Tracer尾迹长度</t>
+          <t>Tracer结束宽度</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="J164" s="0" t="inlineStr">
         <is>
-          <t>maxActiveTracers</t>
+          <t>tracerTailLength</t>
         </is>
       </c>
       <c r="L164" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N164" s="0" t="inlineStr">
         <is>
-          <t>最大同时存在Tracer数量</t>
+          <t>Tracer尾迹长度</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="J165" s="0" t="inlineStr">
         <is>
-          <t>hitLayers</t>
+          <t>maxActiveTracers</t>
         </is>
       </c>
       <c r="L165" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N165" s="0" t="inlineStr">
         <is>
-          <t>默认命中层级</t>
+          <t>最大同时存在Tracer数量</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="J166" s="0" t="inlineStr">
         <is>
-          <t>tracerStartColor</t>
+          <t>hitLayers</t>
         </is>
       </c>
       <c r="L166" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N166" s="0" t="inlineStr">
         <is>
-          <t>Tracer起始颜色</t>
+          <t>默认命中层级</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="J167" s="0" t="inlineStr">
         <is>
+          <t>tracerStartColor</t>
+        </is>
+      </c>
+      <c r="L167" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N167" s="0" t="inlineStr">
+        <is>
+          <t>Tracer起始颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="J168" s="0" t="inlineStr">
+        <is>
           <t>tracerEndColor</t>
         </is>
       </c>
-      <c r="L167" s="0" t="inlineStr">
+      <c r="L168" s="0" t="inlineStr">
         <is>
           <t>cfg.Color#sep=,</t>
         </is>
       </c>
-      <c r="N167" s="0" t="inlineStr">
+      <c r="N168" s="0" t="inlineStr">
         <is>
           <t>Tracer结束颜色</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="B168" s="0" t="inlineStr">
+    <row r="169">
+      <c r="B169" s="0" t="inlineStr">
         <is>
           <t>cfg.UiConfig</t>
         </is>
       </c>
-      <c r="G168" s="0" t="inlineStr">
+      <c r="G169" s="0" t="inlineStr">
         <is>
           <t>UI全局配置</t>
         </is>
       </c>
-      <c r="H168" s="0" t="inlineStr">
+      <c r="H169" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="J169" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L169" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N169" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="J170" s="0" t="inlineStr">
         <is>
-          <t>damageNumberPoolSize</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L170" s="0" t="inlineStr">
@@ -4016,31 +4016,31 @@
       </c>
       <c r="N170" s="0" t="inlineStr">
         <is>
-          <t>伤害数字对象池大小</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="J171" s="0" t="inlineStr">
         <is>
-          <t>damageNumberFadeDuration</t>
+          <t>damageNumberPoolSize</t>
         </is>
       </c>
       <c r="L171" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N171" s="0" t="inlineStr">
         <is>
-          <t>伤害数字渐隐时间</t>
+          <t>伤害数字对象池大小</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="J172" s="0" t="inlineStr">
         <is>
-          <t>damageNumberMoveOffset</t>
+          <t>damageNumberFadeDuration</t>
         </is>
       </c>
       <c r="L172" s="0" t="inlineStr">
@@ -4050,31 +4050,31 @@
       </c>
       <c r="N172" s="0" t="inlineStr">
         <is>
-          <t>伤害数字上浮偏移</t>
+          <t>伤害数字渐隐时间</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="J173" s="0" t="inlineStr">
         <is>
-          <t>damageNumberNormalColor</t>
+          <t>damageNumberMoveOffset</t>
         </is>
       </c>
       <c r="L173" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N173" s="0" t="inlineStr">
         <is>
-          <t>普通伤害数字颜色</t>
+          <t>伤害数字上浮偏移</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="J174" s="0" t="inlineStr">
         <is>
-          <t>damageNumberCriticalColor</t>
+          <t>damageNumberNormalColor</t>
         </is>
       </c>
       <c r="L174" s="0" t="inlineStr">
@@ -4084,31 +4084,31 @@
       </c>
       <c r="N174" s="0" t="inlineStr">
         <is>
-          <t>暴击伤害数字颜色</t>
+          <t>普通伤害数字颜色</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="J175" s="0" t="inlineStr">
         <is>
-          <t>damageNumberNormalFontSize</t>
+          <t>damageNumberCriticalColor</t>
         </is>
       </c>
       <c r="L175" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N175" s="0" t="inlineStr">
         <is>
-          <t>普通伤害数字字体大小</t>
+          <t>暴击伤害数字颜色</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="J176" s="0" t="inlineStr">
         <is>
-          <t>damageNumberCriticalFontSize</t>
+          <t>damageNumberNormalFontSize</t>
         </is>
       </c>
       <c r="L176" s="0" t="inlineStr">
@@ -4118,14 +4118,14 @@
       </c>
       <c r="N176" s="0" t="inlineStr">
         <is>
-          <t>暴击伤害数字字体大小</t>
+          <t>普通伤害数字字体大小</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="J177" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerPoolSize</t>
+          <t>damageNumberCriticalFontSize</t>
         </is>
       </c>
       <c r="L177" s="0" t="inlineStr">
@@ -4135,31 +4135,31 @@
       </c>
       <c r="N177" s="0" t="inlineStr">
         <is>
-          <t>命中标记对象池大小</t>
+          <t>暴击伤害数字字体大小</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="J178" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerDuration</t>
+          <t>hitMarkerPoolSize</t>
         </is>
       </c>
       <c r="L178" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N178" s="0" t="inlineStr">
         <is>
-          <t>命中标记显示时间</t>
+          <t>命中标记对象池大小</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="J179" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerSize</t>
+          <t>hitMarkerDuration</t>
         </is>
       </c>
       <c r="L179" s="0" t="inlineStr">
@@ -4169,31 +4169,31 @@
       </c>
       <c r="N179" s="0" t="inlineStr">
         <is>
-          <t>命中标记大小</t>
+          <t>命中标记显示时间</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="J180" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerNormalColor</t>
+          <t>hitMarkerSize</t>
         </is>
       </c>
       <c r="L180" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N180" s="0" t="inlineStr">
         <is>
-          <t>普通命中标记颜色</t>
+          <t>命中标记大小</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="J181" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerCriticalColor</t>
+          <t>hitMarkerNormalColor</t>
         </is>
       </c>
       <c r="L181" s="0" t="inlineStr">
@@ -4203,116 +4203,116 @@
       </c>
       <c r="N181" s="0" t="inlineStr">
         <is>
-          <t>暴击命中标记颜色</t>
+          <t>普通命中标记颜色</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="J182" s="0" t="inlineStr">
         <is>
-          <t>indicatorFadeSpeed</t>
+          <t>hitMarkerCriticalColor</t>
         </is>
       </c>
       <c r="L182" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N182" s="0" t="inlineStr">
         <is>
-          <t>受击指示器淡出速度</t>
+          <t>暴击命中标记颜色</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="J183" s="0" t="inlineStr">
         <is>
-          <t>indicatorColor</t>
+          <t>indicatorFadeSpeed</t>
         </is>
       </c>
       <c r="L183" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N183" s="0" t="inlineStr">
         <is>
-          <t>受击指示器颜色</t>
+          <t>受击指示器淡出速度</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="J184" s="0" t="inlineStr">
         <is>
+          <t>indicatorColor</t>
+        </is>
+      </c>
+      <c r="L184" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N184" s="0" t="inlineStr">
+        <is>
+          <t>受击指示器颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="J185" s="0" t="inlineStr">
+        <is>
           <t>loadingTextFormat</t>
         </is>
       </c>
-      <c r="L184" s="0" t="inlineStr">
+      <c r="L185" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N184" s="0" t="inlineStr">
+      <c r="N185" s="0" t="inlineStr">
         <is>
           <t>加载进度文本格式</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="B185" s="0" t="inlineStr">
+    <row r="186">
+      <c r="B186" s="0" t="inlineStr">
         <is>
           <t>cfg.Pickup</t>
         </is>
       </c>
-      <c r="G185" s="0" t="inlineStr">
+      <c r="G186" s="0" t="inlineStr">
         <is>
           <t>拾取物配置</t>
         </is>
       </c>
-      <c r="H185" s="0" t="inlineStr">
+      <c r="H186" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="J186" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L186" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N186" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="J187" s="0" t="inlineStr">
         <is>
-          <t>colliderRadius</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L187" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N187" s="0" t="inlineStr">
         <is>
-          <t>拾取物碰撞体半径</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="J188" s="0" t="inlineStr">
         <is>
-          <t>visualScale</t>
+          <t>colliderRadius</t>
         </is>
       </c>
       <c r="L188" s="0" t="inlineStr">
@@ -4322,82 +4322,82 @@
       </c>
       <c r="N188" s="0" t="inlineStr">
         <is>
-          <t>拾取物视觉缩放</t>
+          <t>拾取物碰撞体半径</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="J189" s="0" t="inlineStr">
         <is>
+          <t>visualScale</t>
+        </is>
+      </c>
+      <c r="L189" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N189" s="0" t="inlineStr">
+        <is>
+          <t>拾取物视觉缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="J190" s="0" t="inlineStr">
+        <is>
           <t>sortingOrder</t>
         </is>
       </c>
-      <c r="L189" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N189" s="0" t="inlineStr">
+      <c r="L190" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N190" s="0" t="inlineStr">
         <is>
           <t>拾取物渲染排序</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="B190" s="0" t="inlineStr">
+    <row r="191">
+      <c r="B191" s="0" t="inlineStr">
         <is>
           <t>cfg.Building</t>
         </is>
       </c>
-      <c r="G190" s="0" t="inlineStr">
+      <c r="G191" s="0" t="inlineStr">
         <is>
           <t>建筑配置</t>
         </is>
       </c>
-      <c r="I190" s="0" t="inlineStr">
+      <c r="I191" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="J191" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L191" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N191" s="0" t="inlineStr">
-        <is>
-          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="J192" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L192" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N192" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="J193" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L193" s="0" t="inlineStr">
@@ -4407,65 +4407,65 @@
       </c>
       <c r="N193" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="J194" s="0" t="inlineStr">
         <is>
-          <t>buildingType</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L194" s="0" t="inlineStr">
         <is>
-          <t>cfg.EBuildingType</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N194" s="0" t="inlineStr">
         <is>
-          <t>建筑类型</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="J195" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>buildingType</t>
         </is>
       </c>
       <c r="L195" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>cfg.EBuildingType</t>
         </is>
       </c>
       <c r="N195" s="0" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>建筑类型</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="J196" s="0" t="inlineStr">
         <is>
-          <t>maxLevel</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L196" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N196" s="0" t="inlineStr">
         <is>
-          <t>最大等级</t>
+          <t>图标</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="J197" s="0" t="inlineStr">
         <is>
-          <t>buildCostGold</t>
+          <t>maxLevel</t>
         </is>
       </c>
       <c r="L197" s="0" t="inlineStr">
@@ -4475,150 +4475,150 @@
       </c>
       <c r="N197" s="0" t="inlineStr">
         <is>
-          <t>建造金币</t>
+          <t>最大等级</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="J198" s="0" t="inlineStr">
         <is>
-          <t>buildCostItems</t>
+          <t>buildCostGold</t>
         </is>
       </c>
       <c r="L198" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N198" s="0" t="inlineStr">
         <is>
-          <t>建造材料</t>
+          <t>建造金币</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="J199" s="0" t="inlineStr">
         <is>
-          <t>buildTime</t>
+          <t>buildCostItems</t>
         </is>
       </c>
       <c r="L199" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N199" s="0" t="inlineStr">
         <is>
-          <t>建造耗时</t>
+          <t>建造材料</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="J200" s="0" t="inlineStr">
         <is>
-          <t>upgradeCostGold</t>
+          <t>buildTime</t>
         </is>
       </c>
       <c r="L200" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N200" s="0" t="inlineStr">
         <is>
-          <t>升级金币</t>
+          <t>建造耗时</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="J201" s="0" t="inlineStr">
         <is>
-          <t>upgradeCostItems</t>
+          <t>upgradeCostGold</t>
         </is>
       </c>
       <c r="L201" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N201" s="0" t="inlineStr">
         <is>
-          <t>升级材料</t>
+          <t>升级金币</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="J202" s="0" t="inlineStr">
         <is>
-          <t>upgradeTime</t>
+          <t>upgradeCostItems</t>
         </is>
       </c>
       <c r="L202" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N202" s="0" t="inlineStr">
         <is>
-          <t>升级耗时</t>
+          <t>升级材料</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="J203" s="0" t="inlineStr">
         <is>
-          <t>productionSlotCount</t>
+          <t>upgradeTime</t>
         </is>
       </c>
       <c r="L203" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N203" s="0" t="inlineStr">
         <is>
-          <t>生产槽位</t>
+          <t>升级耗时</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="J204" s="0" t="inlineStr">
         <is>
+          <t>productionSlotCount</t>
+        </is>
+      </c>
+      <c r="L204" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N204" s="0" t="inlineStr">
+        <is>
+          <t>生产槽位</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="J205" s="0" t="inlineStr">
+        <is>
           <t>unlockLevel</t>
         </is>
       </c>
-      <c r="L204" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N204" s="0" t="inlineStr">
+      <c r="L205" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N205" s="0" t="inlineStr">
         <is>
           <t>解锁等级</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="B205" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Production</t>
-        </is>
-      </c>
-      <c r="G205" s="0" t="inlineStr">
-        <is>
-          <t>生产配方</t>
-        </is>
-      </c>
-      <c r="I205" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="J206" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>footprintX</t>
         </is>
       </c>
       <c r="L206" s="0" t="inlineStr">
@@ -4628,99 +4628,99 @@
       </c>
       <c r="N206" s="0" t="inlineStr">
         <is>
-          <t>配方ID</t>
+          <t>占地格数X(1m格)</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="J207" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L207" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N207" s="0" t="inlineStr">
-        <is>
-          <t>名称</t>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>maxCount</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>数量上限-基础值(默认1)</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="J208" s="0" t="inlineStr">
-        <is>
-          <t>desc</t>
-        </is>
-      </c>
-      <c r="L208" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N208" s="0" t="inlineStr">
-        <is>
-          <t>描述</t>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>maxCountPerPlayerLevel</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>数量上限-玩家等级解锁:玩家每升1级上限+N(默认0)</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="J209" s="0" t="inlineStr">
-        <is>
-          <t>buildingId</t>
-        </is>
-      </c>
-      <c r="L209" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N209" s="0" t="inlineStr">
-        <is>
-          <t>建筑ID</t>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>maxCountUpgradeLevel</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>数量上限-升级解锁(默认方式):同类建筑每有1座达到该等级上限+1,0=不启用</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="J210" s="0" t="inlineStr">
-        <is>
-          <t>levelRequired</t>
-        </is>
-      </c>
-      <c r="L210" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N210" s="0" t="inlineStr">
-        <is>
-          <t>等级要求</t>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>maxCountSlotBaseCost</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>数量上限-购买解锁:购买1个栏位的金币基础价,0=不可购买</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="J211" s="0" t="inlineStr">
-        <is>
-          <t>inputItems</t>
-        </is>
-      </c>
-      <c r="L211" s="0" t="inlineStr">
-        <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
-        </is>
-      </c>
-      <c r="N211" s="0" t="inlineStr">
-        <is>
-          <t>输入材料</t>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>maxCountSlotCostGrow</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>数量上限-购买解锁:每已购1个栏位价格+N(线性涨价)</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="J212" s="0" t="inlineStr">
         <is>
-          <t>outputItemId</t>
+          <t>footprintZ</t>
         </is>
       </c>
       <c r="L212" s="0" t="inlineStr">
@@ -4730,48 +4730,48 @@
       </c>
       <c r="N212" s="0" t="inlineStr">
         <is>
-          <t>产出物品</t>
+          <t>占地格数Z(1m格)</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="J213" s="0" t="inlineStr">
-        <is>
-          <t>outputCount</t>
-        </is>
-      </c>
-      <c r="L213" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N213" s="0" t="inlineStr">
-        <is>
-          <t>产出数量</t>
+      <c r="B213" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Production</t>
+        </is>
+      </c>
+      <c r="G213" s="0" t="inlineStr">
+        <is>
+          <t>生产配方</t>
+        </is>
+      </c>
+      <c r="I213" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="J214" s="0" t="inlineStr">
         <is>
-          <t>productionTime</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L214" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N214" s="0" t="inlineStr">
         <is>
-          <t>生产耗时</t>
+          <t>配方ID</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="J215" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L215" s="0" t="inlineStr">
@@ -4781,31 +4781,31 @@
       </c>
       <c r="N215" s="0" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="B216" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Order</t>
-        </is>
-      </c>
-      <c r="G216" s="0" t="inlineStr">
-        <is>
-          <t>订单配置</t>
-        </is>
-      </c>
-      <c r="I216" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J216" s="0" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="L216" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N216" s="0" t="inlineStr">
+        <is>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="J217" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>buildingId</t>
         </is>
       </c>
       <c r="L217" s="0" t="inlineStr">
@@ -4815,65 +4815,65 @@
       </c>
       <c r="N217" s="0" t="inlineStr">
         <is>
-          <t>订单ID</t>
+          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="J218" s="0" t="inlineStr">
         <is>
-          <t>requiredItems</t>
+          <t>levelRequired</t>
         </is>
       </c>
       <c r="L218" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N218" s="0" t="inlineStr">
         <is>
-          <t>需求物品</t>
+          <t>等级要求</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="J219" s="0" t="inlineStr">
         <is>
-          <t>rewardGold</t>
+          <t>inputItems</t>
         </is>
       </c>
       <c r="L219" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N219" s="0" t="inlineStr">
         <is>
-          <t>奖励金币</t>
+          <t>输入材料</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="J220" s="0" t="inlineStr">
         <is>
-          <t>rewardItems</t>
+          <t>outputItemId</t>
         </is>
       </c>
       <c r="L220" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N220" s="0" t="inlineStr">
         <is>
-          <t>奖励物品</t>
+          <t>产出物品</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="J221" s="0" t="inlineStr">
         <is>
-          <t>rewardExp</t>
+          <t>outputCount</t>
         </is>
       </c>
       <c r="L221" s="0" t="inlineStr">
@@ -4883,14 +4883,14 @@
       </c>
       <c r="N221" s="0" t="inlineStr">
         <is>
-          <t>奖励经验</t>
+          <t>产出数量</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="J222" s="0" t="inlineStr">
         <is>
-          <t>timeLimit</t>
+          <t>productionTime</t>
         </is>
       </c>
       <c r="L222" s="0" t="inlineStr">
@@ -4900,133 +4900,133 @@
       </c>
       <c r="N222" s="0" t="inlineStr">
         <is>
-          <t>时限</t>
+          <t>生产耗时</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="J223" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L223" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N223" s="0" t="inlineStr">
         <is>
-          <t>权重</t>
+          <t>图标</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="J224" s="0" t="inlineStr">
-        <is>
-          <t>minPlayerLevel</t>
-        </is>
-      </c>
-      <c r="L224" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N224" s="0" t="inlineStr">
-        <is>
-          <t>最低等级</t>
+      <c r="B224" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Order</t>
+        </is>
+      </c>
+      <c r="G224" s="0" t="inlineStr">
+        <is>
+          <t>订单配置</t>
+        </is>
+      </c>
+      <c r="I224" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="B225" s="0" t="inlineStr">
-        <is>
-          <t>cfg.SimTimeConfig</t>
-        </is>
-      </c>
-      <c r="G225" s="0" t="inlineStr">
-        <is>
-          <t>经营时间配置</t>
-        </is>
-      </c>
-      <c r="I225" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J225" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L225" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N225" s="0" t="inlineStr">
+        <is>
+          <t>订单ID</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="J226" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>requiredItems</t>
         </is>
       </c>
       <c r="L226" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N226" s="0" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>需求物品</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="J227" s="0" t="inlineStr">
         <is>
-          <t>baseSpeed</t>
+          <t>rewardGold</t>
         </is>
       </c>
       <c r="L227" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N227" s="0" t="inlineStr">
         <is>
-          <t>基础速度</t>
+          <t>奖励金币</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="J228" s="0" t="inlineStr">
         <is>
-          <t>fastSpeed</t>
+          <t>rewardItems</t>
         </is>
       </c>
       <c r="L228" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N228" s="0" t="inlineStr">
         <is>
-          <t>加速速度</t>
+          <t>奖励物品</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="J229" s="0" t="inlineStr">
         <is>
-          <t>maxSpeed</t>
+          <t>rewardExp</t>
         </is>
       </c>
       <c r="L229" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N229" s="0" t="inlineStr">
         <is>
-          <t>最大速度</t>
+          <t>奖励经验</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="J230" s="0" t="inlineStr">
         <is>
-          <t>orderRefreshInterval</t>
+          <t>timeLimit</t>
         </is>
       </c>
       <c r="L230" s="0" t="inlineStr">
@@ -5036,243 +5036,379 @@
       </c>
       <c r="N230" s="0" t="inlineStr">
         <is>
-          <t>订单刷新间隔</t>
+          <t>时限</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="J231" s="0" t="inlineStr">
         <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L231" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N231" s="0" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="J232" s="0" t="inlineStr">
+        <is>
+          <t>minPlayerLevel</t>
+        </is>
+      </c>
+      <c r="L232" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N232" s="0" t="inlineStr">
+        <is>
+          <t>最低等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" s="0" t="inlineStr">
+        <is>
+          <t>cfg.SimTimeConfig</t>
+        </is>
+      </c>
+      <c r="G233" s="0" t="inlineStr">
+        <is>
+          <t>经营时间配置</t>
+        </is>
+      </c>
+      <c r="I233" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="J234" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L234" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N234" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="J235" s="0" t="inlineStr">
+        <is>
+          <t>baseSpeed</t>
+        </is>
+      </c>
+      <c r="L235" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N235" s="0" t="inlineStr">
+        <is>
+          <t>基础速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="J236" s="0" t="inlineStr">
+        <is>
+          <t>fastSpeed</t>
+        </is>
+      </c>
+      <c r="L236" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N236" s="0" t="inlineStr">
+        <is>
+          <t>加速速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="J237" s="0" t="inlineStr">
+        <is>
+          <t>maxSpeed</t>
+        </is>
+      </c>
+      <c r="L237" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N237" s="0" t="inlineStr">
+        <is>
+          <t>最大速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="J238" s="0" t="inlineStr">
+        <is>
+          <t>orderRefreshInterval</t>
+        </is>
+      </c>
+      <c r="L238" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N238" s="0" t="inlineStr">
+        <is>
+          <t>订单刷新间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="J239" s="0" t="inlineStr">
+        <is>
           <t>maxOrderCount</t>
         </is>
       </c>
-      <c r="L231" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N231" s="0" t="inlineStr">
+      <c r="L239" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N239" s="0" t="inlineStr">
         <is>
           <t>最大订单数</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="B232" t="inlineStr">
+    <row r="240">
+      <c r="B240" s="0" t="inlineStr">
         <is>
           <t>cfg.Camera3D</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
+      <c r="G240" s="0" t="inlineStr">
         <is>
           <t>3D摄像机配置</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr">
+      <c r="I240" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="J233" t="inlineStr">
+    <row r="241">
+      <c r="J241" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N233" t="inlineStr">
+      <c r="L241" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N241" s="0" t="inlineStr">
         <is>
           <t>配置ID</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="J234" t="inlineStr">
+    <row r="242">
+      <c r="J242" s="0" t="inlineStr">
         <is>
           <t>pitchAngle</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr">
+      <c r="L242" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N242" s="0" t="inlineStr">
         <is>
           <t>俯视角度</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="J235" t="inlineStr">
+    <row r="243">
+      <c r="J243" s="0" t="inlineStr">
         <is>
           <t>initialHeight</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N235" t="inlineStr">
+      <c r="L243" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N243" s="0" t="inlineStr">
         <is>
           <t>初始高度</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="J236" t="inlineStr">
+    <row r="244">
+      <c r="J244" s="0" t="inlineStr">
         <is>
           <t>initialDistance</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr">
+      <c r="L244" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N244" s="0" t="inlineStr">
         <is>
           <t>初始距离</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="J237" t="inlineStr">
+    <row r="245">
+      <c r="J245" s="0" t="inlineStr">
         <is>
           <t>fov</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N237" t="inlineStr">
+      <c r="L245" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N245" s="0" t="inlineStr">
         <is>
           <t>视场角</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="J238" t="inlineStr">
+    <row r="246">
+      <c r="J246" s="0" t="inlineStr">
         <is>
           <t>minZoom</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N238" t="inlineStr">
+      <c r="L246" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N246" s="0" t="inlineStr">
         <is>
           <t>最小缩放</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="J239" t="inlineStr">
+    <row r="247">
+      <c r="J247" s="0" t="inlineStr">
         <is>
           <t>maxZoom</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr">
+      <c r="L247" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N247" s="0" t="inlineStr">
         <is>
           <t>最大缩放</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="J240" t="inlineStr">
+    <row r="248">
+      <c r="J248" s="0" t="inlineStr">
         <is>
           <t>moveSpeed</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N240" t="inlineStr">
+      <c r="L248" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N248" s="0" t="inlineStr">
         <is>
           <t>移动速度</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="J241" t="inlineStr">
+    <row r="249">
+      <c r="J249" s="0" t="inlineStr">
         <is>
           <t>zoomSpeed</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N241" t="inlineStr">
+      <c r="L249" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N249" s="0" t="inlineStr">
         <is>
           <t>缩放速度</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="J242" t="inlineStr">
+    <row r="250">
+      <c r="J250" s="0" t="inlineStr">
         <is>
           <t>maxRotationAngle</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N242" t="inlineStr">
+      <c r="L250" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N250" s="0" t="inlineStr">
         <is>
           <t>最大旋转角度</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="J243" t="inlineStr">
+    <row r="251">
+      <c r="J251" s="0" t="inlineStr">
         <is>
           <t>rotationSpeed</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N243" t="inlineStr">
+      <c r="L251" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N251" s="0" t="inlineStr">
         <is>
           <t>旋转速度</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="J244" t="inlineStr">
+    <row r="252">
+      <c r="J252" s="0" t="inlineStr">
         <is>
           <t>followSmoothTime</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N244" t="inlineStr">
+      <c r="L252" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N252" s="0" t="inlineStr">
         <is>
           <t>跟随平滑时间</t>
         </is>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P252"/>
+  <dimension ref="A1:P253"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -1636,60 +1636,60 @@
       </c>
     </row>
     <row r="31">
-      <c r="J31" s="0" t="inlineStr">
-        <is>
-          <t>aimSensitivityMultiplier</t>
-        </is>
-      </c>
-      <c r="L31" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N31" s="0" t="inlineStr">
-        <is>
-          <t>瞄准灵敏度系数</t>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>scopeFov</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>狙击镜FOV(0=无狙击镜)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>aimAssistEnabled</t>
+          <t>aimSensitivityMultiplier</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N32" s="0" t="inlineStr">
         <is>
-          <t>是否开启辅助瞄准</t>
+          <t>瞄准灵敏度系数</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t>tracerSpeed</t>
+          <t>aimAssistEnabled</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="N33" s="0" t="inlineStr">
         <is>
-          <t>曳光速度</t>
+          <t>是否开启辅助瞄准</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t>tracerDelay</t>
+          <t>tracerSpeed</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
@@ -1699,14 +1699,14 @@
       </c>
       <c r="N34" s="0" t="inlineStr">
         <is>
-          <t>曳光延迟</t>
+          <t>曳光速度</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t>projectileSpeed</t>
+          <t>tracerDelay</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
@@ -1716,14 +1716,14 @@
       </c>
       <c r="N35" s="0" t="inlineStr">
         <is>
-          <t>投掷物速度</t>
+          <t>曳光延迟</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t>projectileLifeTime</t>
+          <t>projectileSpeed</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
@@ -1733,48 +1733,48 @@
       </c>
       <c r="N36" s="0" t="inlineStr">
         <is>
-          <t>投掷物生命周期</t>
+          <t>投掷物速度</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t>projectilePrefab</t>
+          <t>projectileLifeTime</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N37" s="0" t="inlineStr">
         <is>
-          <t>投掷物Prefab</t>
+          <t>投掷物生命周期</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>explosionRadius</t>
+          <t>projectilePrefab</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N38" s="0" t="inlineStr">
         <is>
-          <t>爆炸半径</t>
+          <t>投掷物Prefab</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>explosionDamageFalloff</t>
+          <t>explosionRadius</t>
         </is>
       </c>
       <c r="L39" s="0" t="inlineStr">
@@ -1784,14 +1784,14 @@
       </c>
       <c r="N39" s="0" t="inlineStr">
         <is>
-          <t>爆炸伤害衰减</t>
+          <t>爆炸半径</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>recoilIntensity</t>
+          <t>explosionDamageFalloff</t>
         </is>
       </c>
       <c r="L40" s="0" t="inlineStr">
@@ -1801,14 +1801,14 @@
       </c>
       <c r="N40" s="0" t="inlineStr">
         <is>
-          <t>后坐力强度</t>
+          <t>爆炸伤害衰减</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>raycastRadius</t>
+          <t>recoilIntensity</t>
         </is>
       </c>
       <c r="L41" s="0" t="inlineStr">
@@ -1818,82 +1818,82 @@
       </c>
       <c r="N41" s="0" t="inlineStr">
         <is>
-          <t>射线检测半径</t>
+          <t>后坐力强度</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>hitLayers</t>
+          <t>raycastRadius</t>
         </is>
       </c>
       <c r="L42" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N42" s="0" t="inlineStr">
         <is>
-          <t>命中层级</t>
+          <t>射线检测半径</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>showDebugRay</t>
+          <t>hitLayers</t>
         </is>
       </c>
       <c r="L43" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N43" s="0" t="inlineStr">
         <is>
-          <t>显示Debug射线</t>
+          <t>命中层级</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>debugRayDuration</t>
+          <t>showDebugRay</t>
         </is>
       </c>
       <c r="L44" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="N44" s="0" t="inlineStr">
         <is>
-          <t>Debug射线持续时间</t>
+          <t>显示Debug射线</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="J45" s="0" t="inlineStr">
         <is>
-          <t>debugHitColor</t>
+          <t>debugRayDuration</t>
         </is>
       </c>
       <c r="L45" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N45" s="0" t="inlineStr">
         <is>
-          <t>Debug命中颜色</t>
+          <t>Debug射线持续时间</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="J46" s="0" t="inlineStr">
         <is>
-          <t>debugMissColor</t>
+          <t>debugHitColor</t>
         </is>
       </c>
       <c r="L46" s="0" t="inlineStr">
@@ -1903,65 +1903,65 @@
       </c>
       <c r="N46" s="0" t="inlineStr">
         <is>
-          <t>Debug未命中颜色</t>
+          <t>Debug命中颜色</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="J47" s="0" t="inlineStr">
         <is>
-          <t>trackingTime</t>
+          <t>debugMissColor</t>
         </is>
       </c>
       <c r="L47" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N47" s="0" t="inlineStr">
         <is>
-          <t>锁定时间</t>
+          <t>Debug未命中颜色</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="J48" s="0" t="inlineStr">
         <is>
-          <t>trackingLaserColor</t>
+          <t>trackingTime</t>
         </is>
       </c>
       <c r="L48" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N48" s="0" t="inlineStr">
         <is>
-          <t>锁定激光颜色</t>
+          <t>锁定时间</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="J49" s="0" t="inlineStr">
         <is>
-          <t>lockOnSound</t>
+          <t>trackingLaserColor</t>
         </is>
       </c>
       <c r="L49" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N49" s="0" t="inlineStr">
         <is>
-          <t>锁定音效</t>
+          <t>锁定激光颜色</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="J50" s="0" t="inlineStr">
         <is>
-          <t>muzzleEffect</t>
+          <t>lockOnSound</t>
         </is>
       </c>
       <c r="L50" s="0" t="inlineStr">
@@ -1971,14 +1971,14 @@
       </c>
       <c r="N50" s="0" t="inlineStr">
         <is>
-          <t>枪口特效</t>
+          <t>锁定音效</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="J51" s="0" t="inlineStr">
         <is>
-          <t>hitEffect</t>
+          <t>muzzleEffect</t>
         </is>
       </c>
       <c r="L51" s="0" t="inlineStr">
@@ -1988,14 +1988,14 @@
       </c>
       <c r="N51" s="0" t="inlineStr">
         <is>
-          <t>命中特效</t>
+          <t>枪口特效</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="J52" s="0" t="inlineStr">
         <is>
-          <t>fireSound</t>
+          <t>hitEffect</t>
         </is>
       </c>
       <c r="L52" s="0" t="inlineStr">
@@ -2005,14 +2005,14 @@
       </c>
       <c r="N52" s="0" t="inlineStr">
         <is>
-          <t>开火音效</t>
+          <t>命中特效</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="J53" s="0" t="inlineStr">
         <is>
-          <t>reloadSound</t>
+          <t>fireSound</t>
         </is>
       </c>
       <c r="L53" s="0" t="inlineStr">
@@ -2022,31 +2022,31 @@
       </c>
       <c r="N53" s="0" t="inlineStr">
         <is>
-          <t>换弹音效</t>
+          <t>开火音效</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="J54" s="0" t="inlineStr">
         <is>
-          <t>aimAssistRadius</t>
+          <t>reloadSound</t>
         </is>
       </c>
       <c r="L54" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N54" s="0" t="inlineStr">
         <is>
-          <t>辅助瞄准半径</t>
+          <t>换弹音效</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="J55" s="0" t="inlineStr">
         <is>
-          <t>aimAssistMaxAngle</t>
+          <t>aimAssistRadius</t>
         </is>
       </c>
       <c r="L55" s="0" t="inlineStr">
@@ -2056,14 +2056,14 @@
       </c>
       <c r="N55" s="0" t="inlineStr">
         <is>
-          <t>辅助瞄准最大角度</t>
+          <t>辅助瞄准半径</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>lockOnRange</t>
+          <t>aimAssistMaxAngle</t>
         </is>
       </c>
       <c r="L56" s="0" t="inlineStr">
@@ -2073,14 +2073,14 @@
       </c>
       <c r="N56" s="0" t="inlineStr">
         <is>
-          <t>锁定范围</t>
+          <t>辅助瞄准最大角度</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="J57" s="0" t="inlineStr">
         <is>
-          <t>lockOnAngle</t>
+          <t>lockOnRange</t>
         </is>
       </c>
       <c r="L57" s="0" t="inlineStr">
@@ -2090,82 +2090,82 @@
       </c>
       <c r="N57" s="0" t="inlineStr">
         <is>
-          <t>锁定角度</t>
+          <t>锁定范围</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="J58" s="0" t="inlineStr">
         <is>
+          <t>lockOnAngle</t>
+        </is>
+      </c>
+      <c r="L58" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N58" s="0" t="inlineStr">
+        <is>
+          <t>锁定角度</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="J59" s="0" t="inlineStr">
+        <is>
           <t>lockOnHoldTime</t>
         </is>
       </c>
-      <c r="L58" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N58" s="0" t="inlineStr">
+      <c r="L59" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N59" s="0" t="inlineStr">
         <is>
           <t>锁定保持时间</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="0" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>cfg.Level</t>
         </is>
       </c>
-      <c r="G59" s="0" t="inlineStr">
+      <c r="G60" s="0" t="inlineStr">
         <is>
           <t>关卡配置</t>
         </is>
       </c>
-      <c r="I59" s="0" t="inlineStr">
+      <c r="I60" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="J60" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L60" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N60" s="0" t="inlineStr">
-        <is>
-          <t>关卡ID</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="J61" s="0" t="inlineStr">
         <is>
-          <t>displayName</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L61" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N61" s="0" t="inlineStr">
         <is>
-          <t>显示名称</t>
+          <t>关卡ID</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>sceneName</t>
+          <t>displayName</t>
         </is>
       </c>
       <c r="L62" s="0" t="inlineStr">
@@ -2175,14 +2175,14 @@
       </c>
       <c r="N62" s="0" t="inlineStr">
         <is>
-          <t>场景名</t>
+          <t>显示名称</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="J63" s="0" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>sceneName</t>
         </is>
       </c>
       <c r="L63" s="0" t="inlineStr">
@@ -2192,48 +2192,48 @@
       </c>
       <c r="N63" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>场景名</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="J64" s="0" t="inlineStr">
         <is>
-          <t>defaultWeaponIds</t>
+          <t>description</t>
         </is>
       </c>
       <c r="L64" s="0" t="inlineStr">
         <is>
-          <t>(array#sep=,),int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N64" s="0" t="inlineStr">
         <is>
-          <t>默认武器ID列表</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="J65" s="0" t="inlineStr">
         <is>
-          <t>playerMaxHp</t>
+          <t>defaultWeaponIds</t>
         </is>
       </c>
       <c r="L65" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(array#sep=,),int</t>
         </is>
       </c>
       <c r="N65" s="0" t="inlineStr">
         <is>
-          <t>玩家最大血量</t>
+          <t>默认武器ID列表</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t>enemyCount</t>
+          <t>playerMaxHp</t>
         </is>
       </c>
       <c r="L66" s="0" t="inlineStr">
@@ -2243,121 +2243,121 @@
       </c>
       <c r="N66" s="0" t="inlineStr">
         <is>
-          <t>敌人数量</t>
+          <t>玩家最大血量</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="J67" s="0" t="inlineStr">
         <is>
-          <t>enemySpawnRadius</t>
+          <t>enemyCount</t>
         </is>
       </c>
       <c r="L67" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N67" s="0" t="inlineStr">
         <is>
-          <t>敌人刷新半径</t>
+          <t>敌人数量</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="J68" s="0" t="inlineStr">
         <is>
-          <t>enemyConfigId</t>
+          <t>enemySpawnRadius</t>
         </is>
       </c>
       <c r="L68" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N68" s="0" t="inlineStr">
         <is>
-          <t>敌人配置ID</t>
+          <t>敌人刷新半径</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="J69" s="0" t="inlineStr">
         <is>
+          <t>enemyConfigId</t>
+        </is>
+      </c>
+      <c r="L69" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N69" s="0" t="inlineStr">
+        <is>
+          <t>敌人配置ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="J70" s="0" t="inlineStr">
+        <is>
           <t>enemyMaxHp</t>
         </is>
       </c>
-      <c r="L69" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M69" s="0" t="inlineStr">
+      <c r="L70" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M70" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="N69" s="0" t="inlineStr">
+      <c r="N70" s="0" t="inlineStr">
         <is>
           <t>敌人最大血量</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="0" t="inlineStr">
+    <row r="71">
+      <c r="B71" s="0" t="inlineStr">
         <is>
           <t>cfg.Item</t>
         </is>
       </c>
-      <c r="G70" s="0" t="inlineStr">
+      <c r="G71" s="0" t="inlineStr">
         <is>
           <t>道具配置</t>
         </is>
       </c>
-      <c r="I70" s="0" t="inlineStr">
+      <c r="I71" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="J71" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L71" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N71" s="0" t="inlineStr">
-        <is>
-          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="J72" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L72" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N72" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="J73" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L73" s="0" t="inlineStr">
@@ -2367,201 +2367,201 @@
       </c>
       <c r="N73" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="J74" s="0" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L74" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N74" s="0" t="inlineStr">
         <is>
-          <t>价格</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="J75" s="0" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>price</t>
         </is>
       </c>
       <c r="L75" s="0" t="inlineStr">
         <is>
-          <t>cfg.EQuality</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N75" s="0" t="inlineStr">
         <is>
-          <t>品质</t>
+          <t>价格</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="J76" s="0" t="inlineStr">
         <is>
-          <t>upgradeToItemId</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="L76" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.EQuality</t>
         </is>
       </c>
       <c r="N76" s="0" t="inlineStr">
         <is>
-          <t>升级目标道具ID</t>
+          <t>品质</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="J77" s="0" t="inlineStr">
         <is>
-          <t>expireTime</t>
+          <t>upgradeToItemId</t>
         </is>
       </c>
       <c r="L77" s="0" t="inlineStr">
         <is>
-          <t>datetime?</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N77" s="0" t="inlineStr">
         <is>
-          <t>过期时间</t>
+          <t>升级目标道具ID</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="J78" s="0" t="inlineStr">
         <is>
-          <t>batchUseable</t>
+          <t>expireTime</t>
         </is>
       </c>
       <c r="L78" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>datetime?</t>
         </is>
       </c>
       <c r="N78" s="0" t="inlineStr">
         <is>
-          <t>是否可批量使用</t>
+          <t>过期时间</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="J79" s="0" t="inlineStr">
         <is>
-          <t>exchangeList</t>
+          <t>batchUseable</t>
         </is>
       </c>
       <c r="L79" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="N79" s="0" t="inlineStr">
         <is>
-          <t>兑换列表</t>
+          <t>是否可批量使用</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="J80" s="0" t="inlineStr">
         <is>
-          <t>itemType</t>
+          <t>exchangeList</t>
         </is>
       </c>
       <c r="L80" s="0" t="inlineStr">
         <is>
-          <t>cfg.EItemType</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N80" s="0" t="inlineStr">
         <is>
-          <t>道具类型</t>
+          <t>兑换列表</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="J81" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>itemType</t>
         </is>
       </c>
       <c r="L81" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>cfg.EItemType</t>
         </is>
       </c>
       <c r="N81" s="0" t="inlineStr">
         <is>
-          <t>图标资源地址</t>
+          <t>道具类型</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="J82" s="0" t="inlineStr">
         <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="L82" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N82" s="0" t="inlineStr">
+        <is>
+          <t>图标资源地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="J83" s="0" t="inlineStr">
+        <is>
           <t>stackLimit</t>
         </is>
       </c>
-      <c r="L82" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N82" s="0" t="inlineStr">
+      <c r="L83" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N83" s="0" t="inlineStr">
         <is>
           <t>堆叠上限</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="0" t="inlineStr">
+    <row r="84">
+      <c r="B84" s="0" t="inlineStr">
         <is>
           <t>cfg.Player</t>
         </is>
       </c>
-      <c r="G83" s="0" t="inlineStr">
+      <c r="G84" s="0" t="inlineStr">
         <is>
           <t>玩家属性</t>
         </is>
       </c>
-      <c r="I83" s="0" t="inlineStr">
+      <c r="I84" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="J84" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L84" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N84" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="J85" s="0" t="inlineStr">
         <is>
-          <t>maxHp</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L85" s="0" t="inlineStr">
@@ -2571,31 +2571,31 @@
       </c>
       <c r="N85" s="0" t="inlineStr">
         <is>
-          <t>最大血量</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="J86" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L86" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N86" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="J87" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L87" s="0" t="inlineStr">
@@ -2605,14 +2605,14 @@
       </c>
       <c r="N87" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="J88" s="0" t="inlineStr">
         <is>
-          <t>colliderRadius</t>
+          <t>rotationSpeed</t>
         </is>
       </c>
       <c r="L88" s="0" t="inlineStr">
@@ -2622,82 +2622,82 @@
       </c>
       <c r="N88" s="0" t="inlineStr">
         <is>
-          <t>碰撞体半径</t>
+          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="J89" s="0" t="inlineStr">
         <is>
-          <t>maxStamina</t>
+          <t>colliderRadius</t>
         </is>
       </c>
       <c r="L89" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N89" s="0" t="inlineStr">
         <is>
-          <t>最大体力</t>
+          <t>碰撞体半径</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="J90" s="0" t="inlineStr">
         <is>
-          <t>staminaRecoveryRate</t>
+          <t>maxStamina</t>
         </is>
       </c>
       <c r="L90" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N90" s="0" t="inlineStr">
         <is>
-          <t>体力恢复速率</t>
+          <t>最大体力</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="J91" s="0" t="inlineStr">
         <is>
-          <t>dodgeStaminaCost</t>
+          <t>staminaRecoveryRate</t>
         </is>
       </c>
       <c r="L91" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N91" s="0" t="inlineStr">
         <is>
-          <t>闪避消耗体力</t>
+          <t>体力恢复速率</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="J92" s="0" t="inlineStr">
         <is>
-          <t>dodgeSpeed</t>
+          <t>dodgeStaminaCost</t>
         </is>
       </c>
       <c r="L92" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N92" s="0" t="inlineStr">
         <is>
-          <t>闪避速度</t>
+          <t>闪避消耗体力</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="J93" s="0" t="inlineStr">
         <is>
-          <t>dodgeDuration</t>
+          <t>dodgeSpeed</t>
         </is>
       </c>
       <c r="L93" s="0" t="inlineStr">
@@ -2707,31 +2707,31 @@
       </c>
       <c r="N93" s="0" t="inlineStr">
         <is>
-          <t>闪避持续时间</t>
+          <t>闪避速度</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="J94" s="0" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>dodgeDuration</t>
         </is>
       </c>
       <c r="L94" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N94" s="0" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>闪避持续时间</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="J95" s="0" t="inlineStr">
         <is>
-          <t>idleAnim</t>
+          <t>prefab</t>
         </is>
       </c>
       <c r="L95" s="0" t="inlineStr">
@@ -2741,14 +2741,14 @@
       </c>
       <c r="N95" s="0" t="inlineStr">
         <is>
-          <t>待机动画名</t>
+          <t>预制体</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="J96" s="0" t="inlineStr">
         <is>
-          <t>moveAnim</t>
+          <t>idleAnim</t>
         </is>
       </c>
       <c r="L96" s="0" t="inlineStr">
@@ -2758,14 +2758,14 @@
       </c>
       <c r="N96" s="0" t="inlineStr">
         <is>
-          <t>移动动画名</t>
+          <t>待机动画名</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="J97" s="0" t="inlineStr">
         <is>
-          <t>dodgeAnim</t>
+          <t>moveAnim</t>
         </is>
       </c>
       <c r="L97" s="0" t="inlineStr">
@@ -2775,14 +2775,14 @@
       </c>
       <c r="N97" s="0" t="inlineStr">
         <is>
-          <t>闪避动画名</t>
+          <t>移动动画名</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="J98" s="0" t="inlineStr">
         <is>
-          <t>reloadAnim</t>
+          <t>dodgeAnim</t>
         </is>
       </c>
       <c r="L98" s="0" t="inlineStr">
@@ -2792,133 +2792,133 @@
       </c>
       <c r="N98" s="0" t="inlineStr">
         <is>
-          <t>换弹动画名</t>
+          <t>闪避动画名</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="J99" s="0" t="inlineStr">
         <is>
-          <t>weaponSwitchCooldown</t>
+          <t>reloadAnim</t>
         </is>
       </c>
       <c r="L99" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N99" s="0" t="inlineStr">
         <is>
-          <t>武器切换冷却</t>
+          <t>换弹动画名</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="J100" s="0" t="inlineStr">
         <is>
+          <t>weaponSwitchCooldown</t>
+        </is>
+      </c>
+      <c r="L100" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N100" s="0" t="inlineStr">
+        <is>
+          <t>武器切换冷却</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="J101" s="0" t="inlineStr">
+        <is>
           <t>deadAnim</t>
         </is>
       </c>
-      <c r="L100" s="0" t="inlineStr">
+      <c r="L101" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N100" s="0" t="inlineStr">
+      <c r="N101" s="0" t="inlineStr">
         <is>
           <t>死亡动画名</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" s="0" t="inlineStr">
+    <row r="102">
+      <c r="B102" s="0" t="inlineStr">
         <is>
           <t>cfg.Enemy</t>
         </is>
       </c>
-      <c r="G101" s="0" t="inlineStr">
+      <c r="G102" s="0" t="inlineStr">
         <is>
           <t>敌人属性</t>
         </is>
       </c>
-      <c r="I101" s="0" t="inlineStr">
+      <c r="I102" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="J102" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L102" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N102" s="0" t="inlineStr">
-        <is>
-          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="J103" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L103" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N103" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="J104" s="0" t="inlineStr">
         <is>
-          <t>maxHp</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L104" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N104" s="0" t="inlineStr">
         <is>
-          <t>最大血量</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="J105" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L105" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N105" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="J106" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L106" s="0" t="inlineStr">
@@ -2928,48 +2928,48 @@
       </c>
       <c r="N106" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="J107" s="0" t="inlineStr">
         <is>
-          <t>attackDamage</t>
+          <t>rotationSpeed</t>
         </is>
       </c>
       <c r="L107" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N107" s="0" t="inlineStr">
         <is>
-          <t>攻击伤害</t>
+          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="J108" s="0" t="inlineStr">
         <is>
-          <t>attackRange</t>
+          <t>attackDamage</t>
         </is>
       </c>
       <c r="L108" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N108" s="0" t="inlineStr">
         <is>
-          <t>攻击范围</t>
+          <t>攻击伤害</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="J109" s="0" t="inlineStr">
         <is>
-          <t>attackInterval</t>
+          <t>attackRange</t>
         </is>
       </c>
       <c r="L109" s="0" t="inlineStr">
@@ -2979,14 +2979,14 @@
       </c>
       <c r="N109" s="0" t="inlineStr">
         <is>
-          <t>攻击间隔</t>
+          <t>攻击范围</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="J110" s="0" t="inlineStr">
         <is>
-          <t>pathRefreshInterval</t>
+          <t>attackInterval</t>
         </is>
       </c>
       <c r="L110" s="0" t="inlineStr">
@@ -2996,82 +2996,82 @@
       </c>
       <c r="N110" s="0" t="inlineStr">
         <is>
-          <t>路径刷新间隔</t>
+          <t>攻击间隔</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="J111" s="0" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>pathRefreshInterval</t>
         </is>
       </c>
       <c r="L111" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N111" s="0" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>路径刷新间隔</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="J112" s="0" t="inlineStr">
         <is>
+          <t>prefab</t>
+        </is>
+      </c>
+      <c r="L112" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N112" s="0" t="inlineStr">
+        <is>
+          <t>预制体</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="J113" s="0" t="inlineStr">
+        <is>
           <t>chaseRange</t>
         </is>
       </c>
-      <c r="L112" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N112" s="0" t="inlineStr">
+      <c r="L113" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N113" s="0" t="inlineStr">
         <is>
           <t>仇恨范围（追击触发距离）</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="B113" s="0" t="inlineStr">
+    <row r="114">
+      <c r="B114" s="0" t="inlineStr">
         <is>
           <t>cfg.Wave</t>
         </is>
       </c>
-      <c r="G113" s="0" t="inlineStr">
+      <c r="G114" s="0" t="inlineStr">
         <is>
           <t>波次配置</t>
         </is>
       </c>
-      <c r="I113" s="0" t="inlineStr">
+      <c r="I114" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="J114" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L114" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N114" s="0" t="inlineStr">
-        <is>
-          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="J115" s="0" t="inlineStr">
         <is>
-          <t>levelId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L115" s="0" t="inlineStr">
@@ -3081,14 +3081,14 @@
       </c>
       <c r="N115" s="0" t="inlineStr">
         <is>
-          <t>关卡ID</t>
+          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="J116" s="0" t="inlineStr">
         <is>
-          <t>waveIndex</t>
+          <t>levelId</t>
         </is>
       </c>
       <c r="L116" s="0" t="inlineStr">
@@ -3098,14 +3098,14 @@
       </c>
       <c r="N116" s="0" t="inlineStr">
         <is>
-          <t>波次索引</t>
+          <t>关卡ID</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="J117" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>waveIndex</t>
         </is>
       </c>
       <c r="L117" s="0" t="inlineStr">
@@ -3115,14 +3115,14 @@
       </c>
       <c r="N117" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>波次索引</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="J118" s="0" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L118" s="0" t="inlineStr">
@@ -3132,82 +3132,82 @@
       </c>
       <c r="N118" s="0" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="J119" s="0" t="inlineStr">
         <is>
-          <t>spawnInterval</t>
+          <t>count</t>
         </is>
       </c>
       <c r="L119" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N119" s="0" t="inlineStr">
         <is>
-          <t>刷新间隔</t>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="J120" s="0" t="inlineStr">
         <is>
+          <t>spawnInterval</t>
+        </is>
+      </c>
+      <c r="L120" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N120" s="0" t="inlineStr">
+        <is>
+          <t>刷新间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="J121" s="0" t="inlineStr">
+        <is>
           <t>spawnRadius</t>
         </is>
       </c>
-      <c r="L120" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N120" s="0" t="inlineStr">
+      <c r="L121" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N121" s="0" t="inlineStr">
         <is>
           <t>刷新半径</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="B121" s="0" t="inlineStr">
+    <row r="122">
+      <c r="B122" s="0" t="inlineStr">
         <is>
           <t>cfg.Drop</t>
         </is>
       </c>
-      <c r="G121" s="0" t="inlineStr">
+      <c r="G122" s="0" t="inlineStr">
         <is>
           <t>掉落配置</t>
         </is>
       </c>
-      <c r="I121" s="0" t="inlineStr">
+      <c r="I122" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="J122" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L122" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N122" s="0" t="inlineStr">
-        <is>
-          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="J123" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L123" s="0" t="inlineStr">
@@ -3217,14 +3217,14 @@
       </c>
       <c r="N123" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="J124" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L124" s="0" t="inlineStr">
@@ -3234,14 +3234,14 @@
       </c>
       <c r="N124" s="0" t="inlineStr">
         <is>
-          <t>道具ID</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="J125" s="0" t="inlineStr">
         <is>
-          <t>dropRate</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L125" s="0" t="inlineStr">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="N125" s="0" t="inlineStr">
         <is>
-          <t>掉落概率(万分之一)</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="J126" s="0" t="inlineStr">
         <is>
-          <t>minCount</t>
+          <t>dropRate</t>
         </is>
       </c>
       <c r="L126" s="0" t="inlineStr">
@@ -3268,235 +3268,235 @@
       </c>
       <c r="N126" s="0" t="inlineStr">
         <is>
-          <t>最小数量</t>
+          <t>掉落概率(万分之一)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="J127" s="0" t="inlineStr">
         <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="L127" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N127" s="0" t="inlineStr">
+        <is>
+          <t>最小数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="J128" s="0" t="inlineStr">
+        <is>
           <t>maxCount</t>
         </is>
       </c>
-      <c r="L127" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N127" s="0" t="inlineStr">
+      <c r="L128" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N128" s="0" t="inlineStr">
         <is>
           <t>最大数量</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="B128" s="0" t="inlineStr">
+    <row r="129">
+      <c r="B129" s="0" t="inlineStr">
         <is>
           <t>cfg.Buff</t>
         </is>
       </c>
-      <c r="G128" s="0" t="inlineStr">
+      <c r="G129" s="0" t="inlineStr">
         <is>
           <t>Buff配置</t>
         </is>
       </c>
-      <c r="I128" s="0" t="inlineStr">
+      <c r="I129" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="J129" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L129" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N129" s="0" t="inlineStr">
-        <is>
-          <t>BuffID</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="J130" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L130" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N130" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>BuffID</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="J131" s="0" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L131" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N131" s="0" t="inlineStr">
         <is>
-          <t>持续时间</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="J132" s="0" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="L132" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N132" s="0" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>持续时间</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="J133" s="0" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="L133" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N133" s="0" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>效果类型</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="J134" s="0" t="inlineStr">
         <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L134" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N134" s="0" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="J135" s="0" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="L134" s="0" t="inlineStr">
+      <c r="L135" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N134" s="0" t="inlineStr">
+      <c r="N135" s="0" t="inlineStr">
         <is>
           <t>图标</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="B135" s="0" t="inlineStr">
+    <row r="136">
+      <c r="B136" s="0" t="inlineStr">
         <is>
           <t>cfg.Portal</t>
         </is>
       </c>
-      <c r="G135" s="0" t="inlineStr">
+      <c r="G136" s="0" t="inlineStr">
         <is>
           <t>传送门配置</t>
         </is>
       </c>
-      <c r="I135" s="0" t="inlineStr">
+      <c r="I136" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="J136" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L136" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N136" s="0" t="inlineStr">
-        <is>
-          <t>传送门ID</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="J137" s="0" t="inlineStr">
         <is>
-          <t>portalType</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L137" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N137" s="0" t="inlineStr">
         <is>
-          <t>传送门类型</t>
+          <t>传送门ID</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="J138" s="0" t="inlineStr">
         <is>
-          <t>targetLevelId</t>
+          <t>portalType</t>
         </is>
       </c>
       <c r="L138" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N138" s="0" t="inlineStr">
         <is>
-          <t>目标关卡ID</t>
+          <t>传送门类型</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="J139" s="0" t="inlineStr">
         <is>
-          <t>targetSceneName</t>
+          <t>targetLevelId</t>
         </is>
       </c>
       <c r="L139" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N139" s="0" t="inlineStr">
         <is>
-          <t>目标场景名</t>
+          <t>目标关卡ID</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="J140" s="0" t="inlineStr">
         <is>
-          <t>spawnCondition</t>
+          <t>targetSceneName</t>
         </is>
       </c>
       <c r="L140" s="0" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="N140" s="0" t="inlineStr">
         <is>
-          <t>出现条件</t>
+          <t>目标场景名</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="J141" s="0" t="inlineStr">
         <is>
-          <t>conditionParam</t>
+          <t>spawnCondition</t>
         </is>
       </c>
       <c r="L141" s="0" t="inlineStr">
@@ -3523,48 +3523,48 @@
       </c>
       <c r="N141" s="0" t="inlineStr">
         <is>
-          <t>条件参数</t>
+          <t>出现条件</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="J142" s="0" t="inlineStr">
         <is>
-          <t>keepPlayerState</t>
+          <t>conditionParam</t>
         </is>
       </c>
       <c r="L142" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N142" s="0" t="inlineStr">
         <is>
-          <t>保留玩家状态</t>
+          <t>条件参数</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="J143" s="0" t="inlineStr">
         <is>
-          <t>promptText</t>
+          <t>keepPlayerState</t>
         </is>
       </c>
       <c r="L143" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="N143" s="0" t="inlineStr">
         <is>
-          <t>提示文本</t>
+          <t>保留玩家状态</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="J144" s="0" t="inlineStr">
         <is>
-          <t>transitionType</t>
+          <t>promptText</t>
         </is>
       </c>
       <c r="L144" s="0" t="inlineStr">
@@ -3574,65 +3574,65 @@
       </c>
       <c r="N144" s="0" t="inlineStr">
         <is>
-          <t>转场类型</t>
+          <t>提示文本</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="J145" s="0" t="inlineStr">
         <is>
+          <t>transitionType</t>
+        </is>
+      </c>
+      <c r="L145" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N145" s="0" t="inlineStr">
+        <is>
+          <t>转场类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="J146" s="0" t="inlineStr">
+        <is>
           <t>transitionDuration</t>
         </is>
       </c>
-      <c r="L145" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N145" s="0" t="inlineStr">
+      <c r="L146" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N146" s="0" t="inlineStr">
         <is>
           <t>转场时长</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="B146" s="0" t="inlineStr">
+    <row r="147">
+      <c r="B147" s="0" t="inlineStr">
         <is>
           <t>cfg.InventoryConfig</t>
         </is>
       </c>
-      <c r="G146" s="0" t="inlineStr">
+      <c r="G147" s="0" t="inlineStr">
         <is>
           <t>背包容量配置</t>
         </is>
       </c>
-      <c r="I146" s="0" t="inlineStr">
+      <c r="I147" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="J147" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L147" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N147" s="0" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="J148" s="0" t="inlineStr">
         <is>
-          <t>tempBagCapacity</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L148" s="0" t="inlineStr">
@@ -3642,82 +3642,82 @@
       </c>
       <c r="N148" s="0" t="inlineStr">
         <is>
-          <t>临时背包槽位</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="J149" s="0" t="inlineStr">
         <is>
+          <t>tempBagCapacity</t>
+        </is>
+      </c>
+      <c r="L149" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N149" s="0" t="inlineStr">
+        <is>
+          <t>临时背包槽位</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="J150" s="0" t="inlineStr">
+        <is>
           <t>warehouseCapacity</t>
         </is>
       </c>
-      <c r="L149" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N149" s="0" t="inlineStr">
+      <c r="L150" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N150" s="0" t="inlineStr">
         <is>
           <t>仓库槽位</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="B150" s="0" t="inlineStr">
+    <row r="151">
+      <c r="B151" s="0" t="inlineStr">
         <is>
           <t>cfg.Camera</t>
         </is>
       </c>
-      <c r="G150" s="0" t="inlineStr">
+      <c r="G151" s="0" t="inlineStr">
         <is>
           <t>相机配置</t>
         </is>
       </c>
-      <c r="H150" s="0" t="inlineStr">
+      <c r="H151" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="J151" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L151" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N151" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="J152" s="0" t="inlineStr">
         <is>
-          <t>smoothTime</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L152" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N152" s="0" t="inlineStr">
         <is>
-          <t>相机平滑时间</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="J153" s="0" t="inlineStr">
         <is>
-          <t>defaultFov</t>
+          <t>smoothTime</t>
         </is>
       </c>
       <c r="L153" s="0" t="inlineStr">
@@ -3727,14 +3727,14 @@
       </c>
       <c r="N153" s="0" t="inlineStr">
         <is>
-          <t>默认FOV</t>
+          <t>相机平滑时间</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="J154" s="0" t="inlineStr">
         <is>
-          <t>fovSmoothTime</t>
+          <t>defaultFov</t>
         </is>
       </c>
       <c r="L154" s="0" t="inlineStr">
@@ -3744,14 +3744,14 @@
       </c>
       <c r="N154" s="0" t="inlineStr">
         <is>
-          <t>FOV平滑时间</t>
+          <t>默认FOV</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="J155" s="0" t="inlineStr">
         <is>
-          <t>shakeDamping</t>
+          <t>fovSmoothTime</t>
         </is>
       </c>
       <c r="L155" s="0" t="inlineStr">
@@ -3761,116 +3761,116 @@
       </c>
       <c r="N155" s="0" t="inlineStr">
         <is>
-          <t>震动衰减速度</t>
+          <t>FOV平滑时间</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="J156" s="0" t="inlineStr">
         <is>
-          <t>scopeRenderSize</t>
+          <t>shakeDamping</t>
         </is>
       </c>
       <c r="L156" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N156" s="0" t="inlineStr">
         <is>
-          <t>狙击镜渲染纹理尺寸</t>
+          <t>震动衰减速度</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="J157" s="0" t="inlineStr">
         <is>
-          <t>scopeCameraFov</t>
+          <t>scopeRenderSize</t>
         </is>
       </c>
       <c r="L157" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N157" s="0" t="inlineStr">
         <is>
-          <t>狙击镜相机FOV</t>
+          <t>狙击镜渲染纹理尺寸</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="J158" s="0" t="inlineStr">
         <is>
+          <t>scopeCameraFov</t>
+        </is>
+      </c>
+      <c r="L158" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N158" s="0" t="inlineStr">
+        <is>
+          <t>狙击镜相机FOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="J159" s="0" t="inlineStr">
+        <is>
           <t>defaultOrthographicSize</t>
         </is>
       </c>
-      <c r="L158" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N158" s="0" t="inlineStr">
+      <c r="L159" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N159" s="0" t="inlineStr">
         <is>
           <t>默认正交尺寸</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="B159" s="0" t="inlineStr">
+    <row r="160">
+      <c r="B160" s="0" t="inlineStr">
         <is>
           <t>cfg.Ballistic</t>
         </is>
       </c>
-      <c r="G159" s="0" t="inlineStr">
+      <c r="G160" s="0" t="inlineStr">
         <is>
           <t>弹道全局配置</t>
         </is>
       </c>
-      <c r="H159" s="0" t="inlineStr">
+      <c r="H160" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="J160" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L160" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N160" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="J161" s="0" t="inlineStr">
         <is>
-          <t>tracerRadius</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L161" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N161" s="0" t="inlineStr">
         <is>
-          <t>Tracer射线检测半径</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="J162" s="0" t="inlineStr">
         <is>
-          <t>tracerStartWidth</t>
+          <t>tracerRadius</t>
         </is>
       </c>
       <c r="L162" s="0" t="inlineStr">
@@ -3880,14 +3880,14 @@
       </c>
       <c r="N162" s="0" t="inlineStr">
         <is>
-          <t>Tracer起始宽度</t>
+          <t>Tracer射线检测半径</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="J163" s="0" t="inlineStr">
         <is>
-          <t>tracerEndWidth</t>
+          <t>tracerStartWidth</t>
         </is>
       </c>
       <c r="L163" s="0" t="inlineStr">
@@ -3897,14 +3897,14 @@
       </c>
       <c r="N163" s="0" t="inlineStr">
         <is>
-          <t>Tracer结束宽度</t>
+          <t>Tracer起始宽度</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="J164" s="0" t="inlineStr">
         <is>
-          <t>tracerTailLength</t>
+          <t>tracerEndWidth</t>
         </is>
       </c>
       <c r="L164" s="0" t="inlineStr">
@@ -3914,116 +3914,116 @@
       </c>
       <c r="N164" s="0" t="inlineStr">
         <is>
-          <t>Tracer尾迹长度</t>
+          <t>Tracer结束宽度</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="J165" s="0" t="inlineStr">
         <is>
-          <t>maxActiveTracers</t>
+          <t>tracerTailLength</t>
         </is>
       </c>
       <c r="L165" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N165" s="0" t="inlineStr">
         <is>
-          <t>最大同时存在Tracer数量</t>
+          <t>Tracer尾迹长度</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="J166" s="0" t="inlineStr">
         <is>
-          <t>hitLayers</t>
+          <t>maxActiveTracers</t>
         </is>
       </c>
       <c r="L166" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N166" s="0" t="inlineStr">
         <is>
-          <t>默认命中层级</t>
+          <t>最大同时存在Tracer数量</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="J167" s="0" t="inlineStr">
         <is>
-          <t>tracerStartColor</t>
+          <t>hitLayers</t>
         </is>
       </c>
       <c r="L167" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N167" s="0" t="inlineStr">
         <is>
-          <t>Tracer起始颜色</t>
+          <t>默认命中层级</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="J168" s="0" t="inlineStr">
         <is>
+          <t>tracerStartColor</t>
+        </is>
+      </c>
+      <c r="L168" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N168" s="0" t="inlineStr">
+        <is>
+          <t>Tracer起始颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="J169" s="0" t="inlineStr">
+        <is>
           <t>tracerEndColor</t>
         </is>
       </c>
-      <c r="L168" s="0" t="inlineStr">
+      <c r="L169" s="0" t="inlineStr">
         <is>
           <t>cfg.Color#sep=,</t>
         </is>
       </c>
-      <c r="N168" s="0" t="inlineStr">
+      <c r="N169" s="0" t="inlineStr">
         <is>
           <t>Tracer结束颜色</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="B169" s="0" t="inlineStr">
+    <row r="170">
+      <c r="B170" s="0" t="inlineStr">
         <is>
           <t>cfg.UiConfig</t>
         </is>
       </c>
-      <c r="G169" s="0" t="inlineStr">
+      <c r="G170" s="0" t="inlineStr">
         <is>
           <t>UI全局配置</t>
         </is>
       </c>
-      <c r="H169" s="0" t="inlineStr">
+      <c r="H170" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="J170" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L170" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N170" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="J171" s="0" t="inlineStr">
         <is>
-          <t>damageNumberPoolSize</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L171" s="0" t="inlineStr">
@@ -4033,31 +4033,31 @@
       </c>
       <c r="N171" s="0" t="inlineStr">
         <is>
-          <t>伤害数字对象池大小</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="J172" s="0" t="inlineStr">
         <is>
-          <t>damageNumberFadeDuration</t>
+          <t>damageNumberPoolSize</t>
         </is>
       </c>
       <c r="L172" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N172" s="0" t="inlineStr">
         <is>
-          <t>伤害数字渐隐时间</t>
+          <t>伤害数字对象池大小</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="J173" s="0" t="inlineStr">
         <is>
-          <t>damageNumberMoveOffset</t>
+          <t>damageNumberFadeDuration</t>
         </is>
       </c>
       <c r="L173" s="0" t="inlineStr">
@@ -4067,31 +4067,31 @@
       </c>
       <c r="N173" s="0" t="inlineStr">
         <is>
-          <t>伤害数字上浮偏移</t>
+          <t>伤害数字渐隐时间</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="J174" s="0" t="inlineStr">
         <is>
-          <t>damageNumberNormalColor</t>
+          <t>damageNumberMoveOffset</t>
         </is>
       </c>
       <c r="L174" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N174" s="0" t="inlineStr">
         <is>
-          <t>普通伤害数字颜色</t>
+          <t>伤害数字上浮偏移</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="J175" s="0" t="inlineStr">
         <is>
-          <t>damageNumberCriticalColor</t>
+          <t>damageNumberNormalColor</t>
         </is>
       </c>
       <c r="L175" s="0" t="inlineStr">
@@ -4101,31 +4101,31 @@
       </c>
       <c r="N175" s="0" t="inlineStr">
         <is>
-          <t>暴击伤害数字颜色</t>
+          <t>普通伤害数字颜色</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="J176" s="0" t="inlineStr">
         <is>
-          <t>damageNumberNormalFontSize</t>
+          <t>damageNumberCriticalColor</t>
         </is>
       </c>
       <c r="L176" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N176" s="0" t="inlineStr">
         <is>
-          <t>普通伤害数字字体大小</t>
+          <t>暴击伤害数字颜色</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="J177" s="0" t="inlineStr">
         <is>
-          <t>damageNumberCriticalFontSize</t>
+          <t>damageNumberNormalFontSize</t>
         </is>
       </c>
       <c r="L177" s="0" t="inlineStr">
@@ -4135,14 +4135,14 @@
       </c>
       <c r="N177" s="0" t="inlineStr">
         <is>
-          <t>暴击伤害数字字体大小</t>
+          <t>普通伤害数字字体大小</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="J178" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerPoolSize</t>
+          <t>damageNumberCriticalFontSize</t>
         </is>
       </c>
       <c r="L178" s="0" t="inlineStr">
@@ -4152,31 +4152,31 @@
       </c>
       <c r="N178" s="0" t="inlineStr">
         <is>
-          <t>命中标记对象池大小</t>
+          <t>暴击伤害数字字体大小</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="J179" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerDuration</t>
+          <t>hitMarkerPoolSize</t>
         </is>
       </c>
       <c r="L179" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N179" s="0" t="inlineStr">
         <is>
-          <t>命中标记显示时间</t>
+          <t>命中标记对象池大小</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="J180" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerSize</t>
+          <t>hitMarkerDuration</t>
         </is>
       </c>
       <c r="L180" s="0" t="inlineStr">
@@ -4186,31 +4186,31 @@
       </c>
       <c r="N180" s="0" t="inlineStr">
         <is>
-          <t>命中标记大小</t>
+          <t>命中标记显示时间</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="J181" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerNormalColor</t>
+          <t>hitMarkerSize</t>
         </is>
       </c>
       <c r="L181" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N181" s="0" t="inlineStr">
         <is>
-          <t>普通命中标记颜色</t>
+          <t>命中标记大小</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="J182" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerCriticalColor</t>
+          <t>hitMarkerNormalColor</t>
         </is>
       </c>
       <c r="L182" s="0" t="inlineStr">
@@ -4220,116 +4220,116 @@
       </c>
       <c r="N182" s="0" t="inlineStr">
         <is>
-          <t>暴击命中标记颜色</t>
+          <t>普通命中标记颜色</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="J183" s="0" t="inlineStr">
         <is>
-          <t>indicatorFadeSpeed</t>
+          <t>hitMarkerCriticalColor</t>
         </is>
       </c>
       <c r="L183" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N183" s="0" t="inlineStr">
         <is>
-          <t>受击指示器淡出速度</t>
+          <t>暴击命中标记颜色</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="J184" s="0" t="inlineStr">
         <is>
-          <t>indicatorColor</t>
+          <t>indicatorFadeSpeed</t>
         </is>
       </c>
       <c r="L184" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N184" s="0" t="inlineStr">
         <is>
-          <t>受击指示器颜色</t>
+          <t>受击指示器淡出速度</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="J185" s="0" t="inlineStr">
         <is>
+          <t>indicatorColor</t>
+        </is>
+      </c>
+      <c r="L185" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N185" s="0" t="inlineStr">
+        <is>
+          <t>受击指示器颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="J186" s="0" t="inlineStr">
+        <is>
           <t>loadingTextFormat</t>
         </is>
       </c>
-      <c r="L185" s="0" t="inlineStr">
+      <c r="L186" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N185" s="0" t="inlineStr">
+      <c r="N186" s="0" t="inlineStr">
         <is>
           <t>加载进度文本格式</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="B186" s="0" t="inlineStr">
+    <row r="187">
+      <c r="B187" s="0" t="inlineStr">
         <is>
           <t>cfg.Pickup</t>
         </is>
       </c>
-      <c r="G186" s="0" t="inlineStr">
+      <c r="G187" s="0" t="inlineStr">
         <is>
           <t>拾取物配置</t>
         </is>
       </c>
-      <c r="H186" s="0" t="inlineStr">
+      <c r="H187" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="J187" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L187" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N187" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="J188" s="0" t="inlineStr">
         <is>
-          <t>colliderRadius</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L188" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N188" s="0" t="inlineStr">
         <is>
-          <t>拾取物碰撞体半径</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="J189" s="0" t="inlineStr">
         <is>
-          <t>visualScale</t>
+          <t>colliderRadius</t>
         </is>
       </c>
       <c r="L189" s="0" t="inlineStr">
@@ -4339,82 +4339,82 @@
       </c>
       <c r="N189" s="0" t="inlineStr">
         <is>
-          <t>拾取物视觉缩放</t>
+          <t>拾取物碰撞体半径</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="J190" s="0" t="inlineStr">
         <is>
+          <t>visualScale</t>
+        </is>
+      </c>
+      <c r="L190" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N190" s="0" t="inlineStr">
+        <is>
+          <t>拾取物视觉缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="J191" s="0" t="inlineStr">
+        <is>
           <t>sortingOrder</t>
         </is>
       </c>
-      <c r="L190" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N190" s="0" t="inlineStr">
+      <c r="L191" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N191" s="0" t="inlineStr">
         <is>
           <t>拾取物渲染排序</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="B191" s="0" t="inlineStr">
+    <row r="192">
+      <c r="B192" s="0" t="inlineStr">
         <is>
           <t>cfg.Building</t>
         </is>
       </c>
-      <c r="G191" s="0" t="inlineStr">
+      <c r="G192" s="0" t="inlineStr">
         <is>
           <t>建筑配置</t>
         </is>
       </c>
-      <c r="I191" s="0" t="inlineStr">
+      <c r="I192" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="J192" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L192" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N192" s="0" t="inlineStr">
-        <is>
-          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="J193" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L193" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N193" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="J194" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L194" s="0" t="inlineStr">
@@ -4424,65 +4424,65 @@
       </c>
       <c r="N194" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="J195" s="0" t="inlineStr">
         <is>
-          <t>buildingType</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L195" s="0" t="inlineStr">
         <is>
-          <t>cfg.EBuildingType</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N195" s="0" t="inlineStr">
         <is>
-          <t>建筑类型</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="J196" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>buildingType</t>
         </is>
       </c>
       <c r="L196" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>cfg.EBuildingType</t>
         </is>
       </c>
       <c r="N196" s="0" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>建筑类型</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="J197" s="0" t="inlineStr">
         <is>
-          <t>maxLevel</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L197" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N197" s="0" t="inlineStr">
         <is>
-          <t>最大等级</t>
+          <t>图标</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="J198" s="0" t="inlineStr">
         <is>
-          <t>buildCostGold</t>
+          <t>maxLevel</t>
         </is>
       </c>
       <c r="L198" s="0" t="inlineStr">
@@ -4492,116 +4492,116 @@
       </c>
       <c r="N198" s="0" t="inlineStr">
         <is>
-          <t>建造金币</t>
+          <t>最大等级</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="J199" s="0" t="inlineStr">
         <is>
-          <t>buildCostItems</t>
+          <t>buildCostGold</t>
         </is>
       </c>
       <c r="L199" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N199" s="0" t="inlineStr">
         <is>
-          <t>建造材料</t>
+          <t>建造金币</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="J200" s="0" t="inlineStr">
         <is>
-          <t>buildTime</t>
+          <t>buildCostItems</t>
         </is>
       </c>
       <c r="L200" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N200" s="0" t="inlineStr">
         <is>
-          <t>建造耗时</t>
+          <t>建造材料</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="J201" s="0" t="inlineStr">
         <is>
-          <t>upgradeCostGold</t>
+          <t>buildTime</t>
         </is>
       </c>
       <c r="L201" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N201" s="0" t="inlineStr">
         <is>
-          <t>升级金币</t>
+          <t>建造耗时</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="J202" s="0" t="inlineStr">
         <is>
-          <t>upgradeCostItems</t>
+          <t>upgradeCostGold</t>
         </is>
       </c>
       <c r="L202" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N202" s="0" t="inlineStr">
         <is>
-          <t>升级材料</t>
+          <t>升级金币</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="J203" s="0" t="inlineStr">
         <is>
-          <t>upgradeTime</t>
+          <t>upgradeCostItems</t>
         </is>
       </c>
       <c r="L203" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N203" s="0" t="inlineStr">
         <is>
-          <t>升级耗时</t>
+          <t>升级材料</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="J204" s="0" t="inlineStr">
         <is>
-          <t>productionSlotCount</t>
+          <t>upgradeTime</t>
         </is>
       </c>
       <c r="L204" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N204" s="0" t="inlineStr">
         <is>
-          <t>生产槽位</t>
+          <t>升级耗时</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="J205" s="0" t="inlineStr">
         <is>
-          <t>unlockLevel</t>
+          <t>productionSlotCount</t>
         </is>
       </c>
       <c r="L205" s="0" t="inlineStr">
@@ -4611,184 +4611,184 @@
       </c>
       <c r="N205" s="0" t="inlineStr">
         <is>
-          <t>解锁等级</t>
+          <t>生产槽位</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="J206" s="0" t="inlineStr">
         <is>
+          <t>unlockLevel</t>
+        </is>
+      </c>
+      <c r="L206" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N206" s="0" t="inlineStr">
+        <is>
+          <t>解锁等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="J207" s="0" t="inlineStr">
+        <is>
           <t>footprintX</t>
         </is>
       </c>
-      <c r="L206" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N206" s="0" t="inlineStr">
+      <c r="L207" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N207" s="0" t="inlineStr">
         <is>
           <t>占地格数X(1m格)</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="J207" t="inlineStr">
+    <row r="208">
+      <c r="J208" s="0" t="inlineStr">
         <is>
           <t>maxCount</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr">
+      <c r="L208" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N208" s="0" t="inlineStr">
         <is>
           <t>数量上限-基础值(默认1)</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="J208" t="inlineStr">
+    <row r="209">
+      <c r="J209" s="0" t="inlineStr">
         <is>
           <t>maxCountPerPlayerLevel</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr">
+      <c r="L209" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N209" s="0" t="inlineStr">
         <is>
           <t>数量上限-玩家等级解锁:玩家每升1级上限+N(默认0)</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="J209" t="inlineStr">
+    <row r="210">
+      <c r="J210" s="0" t="inlineStr">
         <is>
           <t>maxCountUpgradeLevel</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N209" t="inlineStr">
+      <c r="L210" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N210" s="0" t="inlineStr">
         <is>
           <t>数量上限-升级解锁(默认方式):同类建筑每有1座达到该等级上限+1,0=不启用</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="J210" t="inlineStr">
+    <row r="211">
+      <c r="J211" s="0" t="inlineStr">
         <is>
           <t>maxCountSlotBaseCost</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr">
+      <c r="L211" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N211" s="0" t="inlineStr">
         <is>
           <t>数量上限-购买解锁:购买1个栏位的金币基础价,0=不可购买</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>maxCountSlotCostGrow</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>数量上限-购买解锁:每已购1个栏位价格+N(线性涨价)</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="J212" s="0" t="inlineStr">
         <is>
+          <t>maxCountSlotCostGrow</t>
+        </is>
+      </c>
+      <c r="L212" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N212" s="0" t="inlineStr">
+        <is>
+          <t>数量上限-购买解锁:每已购1个栏位价格+N(线性涨价)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="J213" s="0" t="inlineStr">
+        <is>
           <t>footprintZ</t>
         </is>
       </c>
-      <c r="L212" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N212" s="0" t="inlineStr">
+      <c r="L213" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N213" s="0" t="inlineStr">
         <is>
           <t>占地格数Z(1m格)</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="B213" s="0" t="inlineStr">
+    <row r="214">
+      <c r="B214" s="0" t="inlineStr">
         <is>
           <t>cfg.Production</t>
         </is>
       </c>
-      <c r="G213" s="0" t="inlineStr">
+      <c r="G214" s="0" t="inlineStr">
         <is>
           <t>生产配方</t>
         </is>
       </c>
-      <c r="I213" s="0" t="inlineStr">
+      <c r="I214" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="J214" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L214" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N214" s="0" t="inlineStr">
-        <is>
-          <t>配方ID</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="J215" s="0" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L215" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N215" s="0" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>配方ID</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="J216" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L216" s="0" t="inlineStr">
@@ -4798,31 +4798,31 @@
       </c>
       <c r="N216" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="J217" s="0" t="inlineStr">
         <is>
-          <t>buildingId</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L217" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N217" s="0" t="inlineStr">
         <is>
-          <t>建筑ID</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="J218" s="0" t="inlineStr">
         <is>
-          <t>levelRequired</t>
+          <t>buildingId</t>
         </is>
       </c>
       <c r="L218" s="0" t="inlineStr">
@@ -4832,48 +4832,48 @@
       </c>
       <c r="N218" s="0" t="inlineStr">
         <is>
-          <t>等级要求</t>
+          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="J219" s="0" t="inlineStr">
         <is>
-          <t>inputItems</t>
+          <t>levelRequired</t>
         </is>
       </c>
       <c r="L219" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N219" s="0" t="inlineStr">
         <is>
-          <t>输入材料</t>
+          <t>等级要求</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="J220" s="0" t="inlineStr">
         <is>
-          <t>outputItemId</t>
+          <t>inputItems</t>
         </is>
       </c>
       <c r="L220" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N220" s="0" t="inlineStr">
         <is>
-          <t>产出物品</t>
+          <t>输入材料</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="J221" s="0" t="inlineStr">
         <is>
-          <t>outputCount</t>
+          <t>outputItemId</t>
         </is>
       </c>
       <c r="L221" s="0" t="inlineStr">
@@ -4883,252 +4883,252 @@
       </c>
       <c r="N221" s="0" t="inlineStr">
         <is>
-          <t>产出数量</t>
+          <t>产出物品</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="J222" s="0" t="inlineStr">
         <is>
-          <t>productionTime</t>
+          <t>outputCount</t>
         </is>
       </c>
       <c r="L222" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N222" s="0" t="inlineStr">
         <is>
-          <t>生产耗时</t>
+          <t>产出数量</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="J223" s="0" t="inlineStr">
         <is>
+          <t>productionTime</t>
+        </is>
+      </c>
+      <c r="L223" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N223" s="0" t="inlineStr">
+        <is>
+          <t>生产耗时</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="J224" s="0" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="L223" s="0" t="inlineStr">
+      <c r="L224" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N223" s="0" t="inlineStr">
+      <c r="N224" s="0" t="inlineStr">
         <is>
           <t>图标</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="B224" s="0" t="inlineStr">
+    <row r="225">
+      <c r="B225" s="0" t="inlineStr">
         <is>
           <t>cfg.Order</t>
         </is>
       </c>
-      <c r="G224" s="0" t="inlineStr">
+      <c r="G225" s="0" t="inlineStr">
         <is>
           <t>订单配置</t>
         </is>
       </c>
-      <c r="I224" s="0" t="inlineStr">
+      <c r="I225" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="J225" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L225" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N225" s="0" t="inlineStr">
-        <is>
-          <t>订单ID</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="J226" s="0" t="inlineStr">
         <is>
-          <t>requiredItems</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L226" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N226" s="0" t="inlineStr">
         <is>
-          <t>需求物品</t>
+          <t>订单ID</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="J227" s="0" t="inlineStr">
         <is>
-          <t>rewardGold</t>
+          <t>requiredItems</t>
         </is>
       </c>
       <c r="L227" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N227" s="0" t="inlineStr">
         <is>
-          <t>奖励金币</t>
+          <t>需求物品</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="J228" s="0" t="inlineStr">
         <is>
-          <t>rewardItems</t>
+          <t>rewardGold</t>
         </is>
       </c>
       <c r="L228" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N228" s="0" t="inlineStr">
         <is>
-          <t>奖励物品</t>
+          <t>奖励金币</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="J229" s="0" t="inlineStr">
         <is>
-          <t>rewardExp</t>
+          <t>rewardItems</t>
         </is>
       </c>
       <c r="L229" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N229" s="0" t="inlineStr">
         <is>
-          <t>奖励经验</t>
+          <t>奖励物品</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="J230" s="0" t="inlineStr">
         <is>
-          <t>timeLimit</t>
+          <t>rewardExp</t>
         </is>
       </c>
       <c r="L230" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N230" s="0" t="inlineStr">
         <is>
-          <t>时限</t>
+          <t>奖励经验</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="J231" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>timeLimit</t>
         </is>
       </c>
       <c r="L231" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N231" s="0" t="inlineStr">
         <is>
-          <t>权重</t>
+          <t>时限</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="J232" s="0" t="inlineStr">
         <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L232" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N232" s="0" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="J233" s="0" t="inlineStr">
+        <is>
           <t>minPlayerLevel</t>
         </is>
       </c>
-      <c r="L232" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N232" s="0" t="inlineStr">
+      <c r="L233" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N233" s="0" t="inlineStr">
         <is>
           <t>最低等级</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="B233" s="0" t="inlineStr">
+    <row r="234">
+      <c r="B234" s="0" t="inlineStr">
         <is>
           <t>cfg.SimTimeConfig</t>
         </is>
       </c>
-      <c r="G233" s="0" t="inlineStr">
+      <c r="G234" s="0" t="inlineStr">
         <is>
           <t>经营时间配置</t>
         </is>
       </c>
-      <c r="I233" s="0" t="inlineStr">
+      <c r="I234" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="J234" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L234" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N234" s="0" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="J235" s="0" t="inlineStr">
         <is>
-          <t>baseSpeed</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L235" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N235" s="0" t="inlineStr">
         <is>
-          <t>基础速度</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="J236" s="0" t="inlineStr">
         <is>
-          <t>fastSpeed</t>
+          <t>baseSpeed</t>
         </is>
       </c>
       <c r="L236" s="0" t="inlineStr">
@@ -5138,14 +5138,14 @@
       </c>
       <c r="N236" s="0" t="inlineStr">
         <is>
-          <t>加速速度</t>
+          <t>基础速度</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="J237" s="0" t="inlineStr">
         <is>
-          <t>maxSpeed</t>
+          <t>fastSpeed</t>
         </is>
       </c>
       <c r="L237" s="0" t="inlineStr">
@@ -5155,14 +5155,14 @@
       </c>
       <c r="N237" s="0" t="inlineStr">
         <is>
-          <t>最大速度</t>
+          <t>加速速度</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="J238" s="0" t="inlineStr">
         <is>
-          <t>orderRefreshInterval</t>
+          <t>maxSpeed</t>
         </is>
       </c>
       <c r="L238" s="0" t="inlineStr">
@@ -5172,82 +5172,82 @@
       </c>
       <c r="N238" s="0" t="inlineStr">
         <is>
-          <t>订单刷新间隔</t>
+          <t>最大速度</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="J239" s="0" t="inlineStr">
         <is>
+          <t>orderRefreshInterval</t>
+        </is>
+      </c>
+      <c r="L239" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N239" s="0" t="inlineStr">
+        <is>
+          <t>订单刷新间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="J240" s="0" t="inlineStr">
+        <is>
           <t>maxOrderCount</t>
         </is>
       </c>
-      <c r="L239" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N239" s="0" t="inlineStr">
+      <c r="L240" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N240" s="0" t="inlineStr">
         <is>
           <t>最大订单数</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="B240" s="0" t="inlineStr">
+    <row r="241">
+      <c r="B241" s="0" t="inlineStr">
         <is>
           <t>cfg.Camera3D</t>
         </is>
       </c>
-      <c r="G240" s="0" t="inlineStr">
+      <c r="G241" s="0" t="inlineStr">
         <is>
           <t>3D摄像机配置</t>
         </is>
       </c>
-      <c r="I240" s="0" t="inlineStr">
+      <c r="I241" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="J241" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L241" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N241" s="0" t="inlineStr">
-        <is>
-          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="J242" s="0" t="inlineStr">
         <is>
-          <t>pitchAngle</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L242" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N242" s="0" t="inlineStr">
         <is>
-          <t>俯视角度</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="J243" s="0" t="inlineStr">
         <is>
-          <t>initialHeight</t>
+          <t>pitchAngle</t>
         </is>
       </c>
       <c r="L243" s="0" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="N243" s="0" t="inlineStr">
         <is>
-          <t>初始高度</t>
+          <t>俯视角度</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="J244" s="0" t="inlineStr">
         <is>
-          <t>initialDistance</t>
+          <t>initialHeight</t>
         </is>
       </c>
       <c r="L244" s="0" t="inlineStr">
@@ -5274,14 +5274,14 @@
       </c>
       <c r="N244" s="0" t="inlineStr">
         <is>
-          <t>初始距离</t>
+          <t>初始高度</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="J245" s="0" t="inlineStr">
         <is>
-          <t>fov</t>
+          <t>initialDistance</t>
         </is>
       </c>
       <c r="L245" s="0" t="inlineStr">
@@ -5291,14 +5291,14 @@
       </c>
       <c r="N245" s="0" t="inlineStr">
         <is>
-          <t>视场角</t>
+          <t>初始距离</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="J246" s="0" t="inlineStr">
         <is>
-          <t>minZoom</t>
+          <t>fov</t>
         </is>
       </c>
       <c r="L246" s="0" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="N246" s="0" t="inlineStr">
         <is>
-          <t>最小缩放</t>
+          <t>视场角</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="J247" s="0" t="inlineStr">
         <is>
-          <t>maxZoom</t>
+          <t>minZoom</t>
         </is>
       </c>
       <c r="L247" s="0" t="inlineStr">
@@ -5325,14 +5325,14 @@
       </c>
       <c r="N247" s="0" t="inlineStr">
         <is>
-          <t>最大缩放</t>
+          <t>最小缩放</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="J248" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>maxZoom</t>
         </is>
       </c>
       <c r="L248" s="0" t="inlineStr">
@@ -5342,14 +5342,14 @@
       </c>
       <c r="N248" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>最大缩放</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="J249" s="0" t="inlineStr">
         <is>
-          <t>zoomSpeed</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L249" s="0" t="inlineStr">
@@ -5359,14 +5359,14 @@
       </c>
       <c r="N249" s="0" t="inlineStr">
         <is>
-          <t>缩放速度</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="J250" s="0" t="inlineStr">
         <is>
-          <t>maxRotationAngle</t>
+          <t>zoomSpeed</t>
         </is>
       </c>
       <c r="L250" s="0" t="inlineStr">
@@ -5376,14 +5376,14 @@
       </c>
       <c r="N250" s="0" t="inlineStr">
         <is>
-          <t>最大旋转角度</t>
+          <t>缩放速度</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="J251" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>maxRotationAngle</t>
         </is>
       </c>
       <c r="L251" s="0" t="inlineStr">
@@ -5393,22 +5393,39 @@
       </c>
       <c r="N251" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>最大旋转角度</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="J252" s="0" t="inlineStr">
         <is>
+          <t>rotationSpeed</t>
+        </is>
+      </c>
+      <c r="L252" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N252" s="0" t="inlineStr">
+        <is>
+          <t>旋转速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="J253" s="0" t="inlineStr">
+        <is>
           <t>followSmoothTime</t>
         </is>
       </c>
-      <c r="L252" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N252" s="0" t="inlineStr">
+      <c r="L253" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N253" s="0" t="inlineStr">
         <is>
           <t>跟随平滑时间</t>
         </is>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1648,7 +1648,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>狙击镜FOV(0=无狙击镜)</t>
+          <t>瞄准镜FOV(0=无放大纯视觉镜窗,&gt;0=放大倍率FOV)</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P253"/>
+  <dimension ref="A1:P261"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -1636,17 +1636,17 @@
       </c>
     </row>
     <row r="31">
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="0" t="inlineStr">
         <is>
           <t>scopeFov</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
+      <c r="L31" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N31" s="0" t="inlineStr">
         <is>
           <t>瞄准镜FOV(0=无放大纯视觉镜窗,&gt;0=放大倍率FOV)</t>
         </is>
@@ -5428,6 +5428,95 @@
       <c r="N253" s="0" t="inlineStr">
         <is>
           <t>跟随平滑时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>cfg.LootContainer</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>容器掉落记录</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>containerId</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>itemId</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>maxCount</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P261"/>
+  <dimension ref="A1:P266"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -5432,91 +5432,161 @@
       </c>
     </row>
     <row r="255">
-      <c r="B255" t="inlineStr">
+      <c r="B255" s="0" t="inlineStr">
         <is>
           <t>cfg.LootContainer</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
+      <c r="G255" s="0" t="inlineStr">
         <is>
           <t>容器掉落记录</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr">
+      <c r="I255" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="J256" t="inlineStr">
+      <c r="J256" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr">
+      <c r="L256" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="J257" t="inlineStr">
+      <c r="J257" s="0" t="inlineStr">
         <is>
           <t>containerId</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
+      <c r="L257" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="J258" t="inlineStr">
+      <c r="J258" s="0" t="inlineStr">
         <is>
           <t>itemId</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr">
+      <c r="L258" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="J259" t="inlineStr">
+      <c r="J259" s="0" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr">
+      <c r="L259" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="J260" t="inlineStr">
+      <c r="J260" s="0" t="inlineStr">
         <is>
           <t>minCount</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr">
+      <c r="L260" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="J261" t="inlineStr">
+      <c r="J261" s="0" t="inlineStr">
         <is>
           <t>maxCount</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>int</t>
+      <c r="L261" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="262"/>
+    <row r="263">
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>cfg.Note</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>小纸条记录</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>纸条ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>正文(支持
+换行)</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P266"/>
+  <dimension ref="A1:P279"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="1" min="2" max="4"/>
@@ -2321,111 +2321,111 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="0" t="inlineStr">
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>rewardGold</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>通关奖励金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>rewardExp</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>通关奖励经验</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="0" t="inlineStr">
         <is>
           <t>cfg.Item</t>
         </is>
       </c>
-      <c r="G71" s="0" t="inlineStr">
+      <c r="G73" s="0" t="inlineStr">
         <is>
           <t>道具配置</t>
         </is>
       </c>
-      <c r="I71" s="0" t="inlineStr">
+      <c r="I73" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="J72" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L72" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N72" s="0" t="inlineStr">
-        <is>
-          <t>道具ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="J73" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L73" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N73" s="0" t="inlineStr">
-        <is>
-          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="J74" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L74" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N74" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="J75" s="0" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L75" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N75" s="0" t="inlineStr">
         <is>
-          <t>价格</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="J76" s="0" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L76" s="0" t="inlineStr">
         <is>
-          <t>cfg.EQuality</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N76" s="0" t="inlineStr">
         <is>
-          <t>品质</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="J77" s="0" t="inlineStr">
         <is>
-          <t>upgradeToItemId</t>
+          <t>price</t>
         </is>
       </c>
       <c r="L77" s="0" t="inlineStr">
@@ -2435,133 +2435,133 @@
       </c>
       <c r="N77" s="0" t="inlineStr">
         <is>
-          <t>升级目标道具ID</t>
+          <t>价格</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="J78" s="0" t="inlineStr">
         <is>
-          <t>expireTime</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="L78" s="0" t="inlineStr">
         <is>
-          <t>datetime?</t>
+          <t>cfg.EQuality</t>
         </is>
       </c>
       <c r="N78" s="0" t="inlineStr">
         <is>
-          <t>过期时间</t>
+          <t>品质</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="J79" s="0" t="inlineStr">
         <is>
-          <t>batchUseable</t>
+          <t>upgradeToItemId</t>
         </is>
       </c>
       <c r="L79" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N79" s="0" t="inlineStr">
         <is>
-          <t>是否可批量使用</t>
+          <t>升级目标道具ID</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="J80" s="0" t="inlineStr">
         <is>
-          <t>exchangeList</t>
+          <t>expireTime</t>
         </is>
       </c>
       <c r="L80" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>datetime?</t>
         </is>
       </c>
       <c r="N80" s="0" t="inlineStr">
         <is>
-          <t>兑换列表</t>
+          <t>过期时间</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="J81" s="0" t="inlineStr">
         <is>
-          <t>itemType</t>
+          <t>batchUseable</t>
         </is>
       </c>
       <c r="L81" s="0" t="inlineStr">
         <is>
-          <t>cfg.EItemType</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="N81" s="0" t="inlineStr">
         <is>
-          <t>道具类型</t>
+          <t>是否可批量使用</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="J82" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>exchangeList</t>
         </is>
       </c>
       <c r="L82" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N82" s="0" t="inlineStr">
         <is>
-          <t>图标资源地址</t>
+          <t>兑换列表</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="J83" s="0" t="inlineStr">
         <is>
-          <t>stackLimit</t>
+          <t>itemType</t>
         </is>
       </c>
       <c r="L83" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.EItemType</t>
         </is>
       </c>
       <c r="N83" s="0" t="inlineStr">
         <is>
-          <t>堆叠上限</t>
+          <t>道具类型</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Player</t>
-        </is>
-      </c>
-      <c r="G84" s="0" t="inlineStr">
-        <is>
-          <t>玩家属性</t>
-        </is>
-      </c>
-      <c r="I84" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J84" s="0" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="L84" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N84" s="0" t="inlineStr">
+        <is>
+          <t>图标资源地址</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="J85" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>stackLimit</t>
         </is>
       </c>
       <c r="L85" s="0" t="inlineStr">
@@ -2571,65 +2571,65 @@
       </c>
       <c r="N85" s="0" t="inlineStr">
         <is>
-          <t>配置ID</t>
+          <t>堆叠上限</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="J86" s="0" t="inlineStr">
-        <is>
-          <t>maxHp</t>
-        </is>
-      </c>
-      <c r="L86" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N86" s="0" t="inlineStr">
-        <is>
-          <t>最大血量</t>
+      <c r="B86" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Player</t>
+        </is>
+      </c>
+      <c r="G86" s="0" t="inlineStr">
+        <is>
+          <t>玩家属性</t>
+        </is>
+      </c>
+      <c r="I86" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="J87" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L87" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N87" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="J88" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L88" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N88" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="J89" s="0" t="inlineStr">
         <is>
-          <t>colliderRadius</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L89" s="0" t="inlineStr">
@@ -2639,31 +2639,31 @@
       </c>
       <c r="N89" s="0" t="inlineStr">
         <is>
-          <t>碰撞体半径</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="J90" s="0" t="inlineStr">
         <is>
-          <t>maxStamina</t>
+          <t>rotationSpeed</t>
         </is>
       </c>
       <c r="L90" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N90" s="0" t="inlineStr">
         <is>
-          <t>最大体力</t>
+          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="J91" s="0" t="inlineStr">
         <is>
-          <t>staminaRecoveryRate</t>
+          <t>colliderRadius</t>
         </is>
       </c>
       <c r="L91" s="0" t="inlineStr">
@@ -2673,14 +2673,14 @@
       </c>
       <c r="N91" s="0" t="inlineStr">
         <is>
-          <t>体力恢复速率</t>
+          <t>碰撞体半径</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="J92" s="0" t="inlineStr">
         <is>
-          <t>dodgeStaminaCost</t>
+          <t>maxStamina</t>
         </is>
       </c>
       <c r="L92" s="0" t="inlineStr">
@@ -2690,14 +2690,14 @@
       </c>
       <c r="N92" s="0" t="inlineStr">
         <is>
-          <t>闪避消耗体力</t>
+          <t>最大体力</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="J93" s="0" t="inlineStr">
         <is>
-          <t>dodgeSpeed</t>
+          <t>staminaRecoveryRate</t>
         </is>
       </c>
       <c r="L93" s="0" t="inlineStr">
@@ -2707,65 +2707,65 @@
       </c>
       <c r="N93" s="0" t="inlineStr">
         <is>
-          <t>闪避速度</t>
+          <t>体力恢复速率</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="J94" s="0" t="inlineStr">
         <is>
-          <t>dodgeDuration</t>
+          <t>dodgeStaminaCost</t>
         </is>
       </c>
       <c r="L94" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N94" s="0" t="inlineStr">
         <is>
-          <t>闪避持续时间</t>
+          <t>闪避消耗体力</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="J95" s="0" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>dodgeSpeed</t>
         </is>
       </c>
       <c r="L95" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N95" s="0" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>闪避速度</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="J96" s="0" t="inlineStr">
         <is>
-          <t>idleAnim</t>
+          <t>dodgeDuration</t>
         </is>
       </c>
       <c r="L96" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N96" s="0" t="inlineStr">
         <is>
-          <t>待机动画名</t>
+          <t>闪避持续时间</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="J97" s="0" t="inlineStr">
         <is>
-          <t>moveAnim</t>
+          <t>prefab</t>
         </is>
       </c>
       <c r="L97" s="0" t="inlineStr">
@@ -2775,14 +2775,14 @@
       </c>
       <c r="N97" s="0" t="inlineStr">
         <is>
-          <t>移动动画名</t>
+          <t>预制体</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="J98" s="0" t="inlineStr">
         <is>
-          <t>dodgeAnim</t>
+          <t>idleAnim</t>
         </is>
       </c>
       <c r="L98" s="0" t="inlineStr">
@@ -2792,14 +2792,14 @@
       </c>
       <c r="N98" s="0" t="inlineStr">
         <is>
-          <t>闪避动画名</t>
+          <t>待机动画名</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="J99" s="0" t="inlineStr">
         <is>
-          <t>reloadAnim</t>
+          <t>moveAnim</t>
         </is>
       </c>
       <c r="L99" s="0" t="inlineStr">
@@ -2809,31 +2809,31 @@
       </c>
       <c r="N99" s="0" t="inlineStr">
         <is>
-          <t>换弹动画名</t>
+          <t>移动动画名</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="J100" s="0" t="inlineStr">
         <is>
-          <t>weaponSwitchCooldown</t>
+          <t>dodgeAnim</t>
         </is>
       </c>
       <c r="L100" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N100" s="0" t="inlineStr">
         <is>
-          <t>武器切换冷却</t>
+          <t>闪避动画名</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="J101" s="0" t="inlineStr">
         <is>
-          <t>deadAnim</t>
+          <t>reloadAnim</t>
         </is>
       </c>
       <c r="L101" s="0" t="inlineStr">
@@ -2843,65 +2843,65 @@
       </c>
       <c r="N101" s="0" t="inlineStr">
         <is>
-          <t>死亡动画名</t>
+          <t>换弹动画名</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Enemy</t>
-        </is>
-      </c>
-      <c r="G102" s="0" t="inlineStr">
-        <is>
-          <t>敌人属性</t>
-        </is>
-      </c>
-      <c r="I102" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J102" s="0" t="inlineStr">
+        <is>
+          <t>weaponSwitchCooldown</t>
+        </is>
+      </c>
+      <c r="L102" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N102" s="0" t="inlineStr">
+        <is>
+          <t>武器切换冷却</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="J103" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>deadAnim</t>
         </is>
       </c>
       <c r="L103" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N103" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>死亡动画名</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="J104" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L104" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N104" s="0" t="inlineStr">
-        <is>
-          <t>名称</t>
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Enemy</t>
+        </is>
+      </c>
+      <c r="G104" s="0" t="inlineStr">
+        <is>
+          <t>敌人属性</t>
+        </is>
+      </c>
+      <c r="I104" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="J105" s="0" t="inlineStr">
         <is>
-          <t>maxHp</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L105" s="0" t="inlineStr">
@@ -2911,65 +2911,65 @@
       </c>
       <c r="N105" s="0" t="inlineStr">
         <is>
-          <t>最大血量</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="J106" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L106" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N106" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="J107" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>maxHp</t>
         </is>
       </c>
       <c r="L107" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N107" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>最大血量</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="J108" s="0" t="inlineStr">
         <is>
-          <t>attackDamage</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L108" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N108" s="0" t="inlineStr">
         <is>
-          <t>攻击伤害</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="J109" s="0" t="inlineStr">
         <is>
-          <t>attackRange</t>
+          <t>rotationSpeed</t>
         </is>
       </c>
       <c r="L109" s="0" t="inlineStr">
@@ -2979,31 +2979,31 @@
       </c>
       <c r="N109" s="0" t="inlineStr">
         <is>
-          <t>攻击范围</t>
+          <t>旋转速度</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="J110" s="0" t="inlineStr">
         <is>
-          <t>attackInterval</t>
+          <t>attackDamage</t>
         </is>
       </c>
       <c r="L110" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N110" s="0" t="inlineStr">
         <is>
-          <t>攻击间隔</t>
+          <t>攻击伤害</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="J111" s="0" t="inlineStr">
         <is>
-          <t>pathRefreshInterval</t>
+          <t>attackRange</t>
         </is>
       </c>
       <c r="L111" s="0" t="inlineStr">
@@ -3013,31 +3013,31 @@
       </c>
       <c r="N111" s="0" t="inlineStr">
         <is>
-          <t>路径刷新间隔</t>
+          <t>攻击范围</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="J112" s="0" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>attackInterval</t>
         </is>
       </c>
       <c r="L112" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N112" s="0" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>攻击间隔</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="J113" s="0" t="inlineStr">
         <is>
-          <t>chaseRange</t>
+          <t>pathRefreshInterval</t>
         </is>
       </c>
       <c r="L113" s="0" t="inlineStr">
@@ -3047,65 +3047,65 @@
       </c>
       <c r="N113" s="0" t="inlineStr">
         <is>
-          <t>仇恨范围（追击触发距离）</t>
+          <t>路径刷新间隔</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="B114" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Wave</t>
-        </is>
-      </c>
-      <c r="G114" s="0" t="inlineStr">
-        <is>
-          <t>波次配置</t>
-        </is>
-      </c>
-      <c r="I114" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J114" s="0" t="inlineStr">
+        <is>
+          <t>prefab</t>
+        </is>
+      </c>
+      <c r="L114" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N114" s="0" t="inlineStr">
+        <is>
+          <t>预制体</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="J115" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>chaseRange</t>
         </is>
       </c>
       <c r="L115" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N115" s="0" t="inlineStr">
         <is>
-          <t>波次ID</t>
+          <t>仇恨范围（追击触发距离）</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="J116" s="0" t="inlineStr">
-        <is>
-          <t>levelId</t>
-        </is>
-      </c>
-      <c r="L116" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N116" s="0" t="inlineStr">
-        <is>
-          <t>关卡ID</t>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Wave</t>
+        </is>
+      </c>
+      <c r="G116" s="0" t="inlineStr">
+        <is>
+          <t>波次配置</t>
+        </is>
+      </c>
+      <c r="I116" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="J117" s="0" t="inlineStr">
         <is>
-          <t>waveIndex</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L117" s="0" t="inlineStr">
@@ -3115,14 +3115,14 @@
       </c>
       <c r="N117" s="0" t="inlineStr">
         <is>
-          <t>波次索引</t>
+          <t>波次ID</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="J118" s="0" t="inlineStr">
         <is>
-          <t>enemyId</t>
+          <t>levelId</t>
         </is>
       </c>
       <c r="L118" s="0" t="inlineStr">
@@ -3132,14 +3132,14 @@
       </c>
       <c r="N118" s="0" t="inlineStr">
         <is>
-          <t>敌人ID</t>
+          <t>关卡ID</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="J119" s="0" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>waveIndex</t>
         </is>
       </c>
       <c r="L119" s="0" t="inlineStr">
@@ -3149,99 +3149,99 @@
       </c>
       <c r="N119" s="0" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>波次索引</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="J120" s="0" t="inlineStr">
         <is>
-          <t>spawnInterval</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L120" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N120" s="0" t="inlineStr">
         <is>
-          <t>刷新间隔</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="J121" s="0" t="inlineStr">
         <is>
-          <t>spawnRadius</t>
+          <t>count</t>
         </is>
       </c>
       <c r="L121" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N121" s="0" t="inlineStr">
         <is>
-          <t>刷新半径</t>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="B122" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Drop</t>
-        </is>
-      </c>
-      <c r="G122" s="0" t="inlineStr">
-        <is>
-          <t>掉落配置</t>
-        </is>
-      </c>
-      <c r="I122" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J122" s="0" t="inlineStr">
+        <is>
+          <t>spawnInterval</t>
+        </is>
+      </c>
+      <c r="L122" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N122" s="0" t="inlineStr">
+        <is>
+          <t>刷新间隔</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="J123" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>spawnRadius</t>
         </is>
       </c>
       <c r="L123" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N123" s="0" t="inlineStr">
         <is>
-          <t>掉落ID</t>
+          <t>刷新半径</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="J124" s="0" t="inlineStr">
-        <is>
-          <t>enemyId</t>
-        </is>
-      </c>
-      <c r="L124" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N124" s="0" t="inlineStr">
-        <is>
-          <t>敌人ID</t>
+      <c r="B124" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Drop</t>
+        </is>
+      </c>
+      <c r="G124" s="0" t="inlineStr">
+        <is>
+          <t>掉落配置</t>
+        </is>
+      </c>
+      <c r="I124" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="J125" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L125" s="0" t="inlineStr">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="N125" s="0" t="inlineStr">
         <is>
-          <t>道具ID</t>
+          <t>掉落ID</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="J126" s="0" t="inlineStr">
         <is>
-          <t>dropRate</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="L126" s="0" t="inlineStr">
@@ -3268,14 +3268,14 @@
       </c>
       <c r="N126" s="0" t="inlineStr">
         <is>
-          <t>掉落概率(万分之一)</t>
+          <t>敌人ID</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="J127" s="0" t="inlineStr">
         <is>
-          <t>minCount</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L127" s="0" t="inlineStr">
@@ -3285,14 +3285,14 @@
       </c>
       <c r="N127" s="0" t="inlineStr">
         <is>
-          <t>最小数量</t>
+          <t>道具ID</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="J128" s="0" t="inlineStr">
         <is>
-          <t>maxCount</t>
+          <t>dropRate</t>
         </is>
       </c>
       <c r="L128" s="0" t="inlineStr">
@@ -3302,31 +3302,31 @@
       </c>
       <c r="N128" s="0" t="inlineStr">
         <is>
-          <t>最大数量</t>
+          <t>掉落概率(万分之一)</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="B129" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Buff</t>
-        </is>
-      </c>
-      <c r="G129" s="0" t="inlineStr">
-        <is>
-          <t>Buff配置</t>
-        </is>
-      </c>
-      <c r="I129" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J129" s="0" t="inlineStr">
+        <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="L129" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N129" s="0" t="inlineStr">
+        <is>
+          <t>最小数量</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="J130" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>maxCount</t>
         </is>
       </c>
       <c r="L130" s="0" t="inlineStr">
@@ -3336,65 +3336,65 @@
       </c>
       <c r="N130" s="0" t="inlineStr">
         <is>
-          <t>BuffID</t>
+          <t>最大数量</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="J131" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L131" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N131" s="0" t="inlineStr">
-        <is>
-          <t>名称</t>
+      <c r="B131" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Buff</t>
+        </is>
+      </c>
+      <c r="G131" s="0" t="inlineStr">
+        <is>
+          <t>Buff配置</t>
+        </is>
+      </c>
+      <c r="I131" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="J132" s="0" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L132" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N132" s="0" t="inlineStr">
         <is>
-          <t>持续时间</t>
+          <t>BuffID</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="J133" s="0" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L133" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N133" s="0" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="J134" s="0" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="L134" s="0" t="inlineStr">
@@ -3404,82 +3404,82 @@
       </c>
       <c r="N134" s="0" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>持续时间</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="J135" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="L135" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N135" s="0" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>效果类型</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="B136" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Portal</t>
-        </is>
-      </c>
-      <c r="G136" s="0" t="inlineStr">
-        <is>
-          <t>传送门配置</t>
-        </is>
-      </c>
-      <c r="I136" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J136" s="0" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L136" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N136" s="0" t="inlineStr">
+        <is>
+          <t>数值</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="J137" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L137" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N137" s="0" t="inlineStr">
         <is>
-          <t>传送门ID</t>
+          <t>图标</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="J138" s="0" t="inlineStr">
-        <is>
-          <t>portalType</t>
-        </is>
-      </c>
-      <c r="L138" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N138" s="0" t="inlineStr">
-        <is>
-          <t>传送门类型</t>
+      <c r="B138" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Portal</t>
+        </is>
+      </c>
+      <c r="G138" s="0" t="inlineStr">
+        <is>
+          <t>传送门配置</t>
+        </is>
+      </c>
+      <c r="I138" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="J139" s="0" t="inlineStr">
         <is>
-          <t>targetLevelId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L139" s="0" t="inlineStr">
@@ -3489,14 +3489,14 @@
       </c>
       <c r="N139" s="0" t="inlineStr">
         <is>
-          <t>目标关卡ID</t>
+          <t>传送门ID</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="J140" s="0" t="inlineStr">
         <is>
-          <t>targetSceneName</t>
+          <t>portalType</t>
         </is>
       </c>
       <c r="L140" s="0" t="inlineStr">
@@ -3506,31 +3506,31 @@
       </c>
       <c r="N140" s="0" t="inlineStr">
         <is>
-          <t>目标场景名</t>
+          <t>传送门类型</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="J141" s="0" t="inlineStr">
         <is>
-          <t>spawnCondition</t>
+          <t>targetLevelId</t>
         </is>
       </c>
       <c r="L141" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N141" s="0" t="inlineStr">
         <is>
-          <t>出现条件</t>
+          <t>目标关卡ID</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="J142" s="0" t="inlineStr">
         <is>
-          <t>conditionParam</t>
+          <t>targetSceneName</t>
         </is>
       </c>
       <c r="L142" s="0" t="inlineStr">
@@ -3540,31 +3540,31 @@
       </c>
       <c r="N142" s="0" t="inlineStr">
         <is>
-          <t>条件参数</t>
+          <t>目标场景名</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="J143" s="0" t="inlineStr">
         <is>
-          <t>keepPlayerState</t>
+          <t>spawnCondition</t>
         </is>
       </c>
       <c r="L143" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N143" s="0" t="inlineStr">
         <is>
-          <t>保留玩家状态</t>
+          <t>出现条件</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="J144" s="0" t="inlineStr">
         <is>
-          <t>promptText</t>
+          <t>conditionParam</t>
         </is>
       </c>
       <c r="L144" s="0" t="inlineStr">
@@ -3574,99 +3574,99 @@
       </c>
       <c r="N144" s="0" t="inlineStr">
         <is>
-          <t>提示文本</t>
+          <t>条件参数</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="J145" s="0" t="inlineStr">
         <is>
-          <t>transitionType</t>
+          <t>keepPlayerState</t>
         </is>
       </c>
       <c r="L145" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="N145" s="0" t="inlineStr">
         <is>
-          <t>转场类型</t>
+          <t>保留玩家状态</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="J146" s="0" t="inlineStr">
         <is>
-          <t>transitionDuration</t>
+          <t>promptText</t>
         </is>
       </c>
       <c r="L146" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N146" s="0" t="inlineStr">
         <is>
-          <t>转场时长</t>
+          <t>提示文本</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="B147" s="0" t="inlineStr">
-        <is>
-          <t>cfg.InventoryConfig</t>
-        </is>
-      </c>
-      <c r="G147" s="0" t="inlineStr">
-        <is>
-          <t>背包容量配置</t>
-        </is>
-      </c>
-      <c r="I147" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J147" s="0" t="inlineStr">
+        <is>
+          <t>transitionType</t>
+        </is>
+      </c>
+      <c r="L147" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N147" s="0" t="inlineStr">
+        <is>
+          <t>转场类型</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="J148" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>transitionDuration</t>
         </is>
       </c>
       <c r="L148" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N148" s="0" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>转场时长</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="J149" s="0" t="inlineStr">
-        <is>
-          <t>tempBagCapacity</t>
-        </is>
-      </c>
-      <c r="L149" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N149" s="0" t="inlineStr">
-        <is>
-          <t>临时背包槽位</t>
+      <c r="B149" s="0" t="inlineStr">
+        <is>
+          <t>cfg.InventoryConfig</t>
+        </is>
+      </c>
+      <c r="G149" s="0" t="inlineStr">
+        <is>
+          <t>背包容量配置</t>
+        </is>
+      </c>
+      <c r="I149" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="J150" s="0" t="inlineStr">
         <is>
-          <t>warehouseCapacity</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L150" s="0" t="inlineStr">
@@ -3676,31 +3676,31 @@
       </c>
       <c r="N150" s="0" t="inlineStr">
         <is>
-          <t>仓库槽位</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="B151" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Camera</t>
-        </is>
-      </c>
-      <c r="G151" s="0" t="inlineStr">
-        <is>
-          <t>相机配置</t>
-        </is>
-      </c>
-      <c r="H151" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J151" s="0" t="inlineStr">
+        <is>
+          <t>tempBagCapacity</t>
+        </is>
+      </c>
+      <c r="L151" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N151" s="0" t="inlineStr">
+        <is>
+          <t>临时背包槽位</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="J152" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>warehouseCapacity</t>
         </is>
       </c>
       <c r="L152" s="0" t="inlineStr">
@@ -3710,48 +3710,48 @@
       </c>
       <c r="N152" s="0" t="inlineStr">
         <is>
-          <t>配置ID</t>
+          <t>仓库槽位</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="J153" s="0" t="inlineStr">
-        <is>
-          <t>smoothTime</t>
-        </is>
-      </c>
-      <c r="L153" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N153" s="0" t="inlineStr">
-        <is>
-          <t>相机平滑时间</t>
+      <c r="B153" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Camera</t>
+        </is>
+      </c>
+      <c r="G153" s="0" t="inlineStr">
+        <is>
+          <t>相机配置</t>
+        </is>
+      </c>
+      <c r="H153" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="J154" s="0" t="inlineStr">
         <is>
-          <t>defaultFov</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L154" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N154" s="0" t="inlineStr">
         <is>
-          <t>默认FOV</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="J155" s="0" t="inlineStr">
         <is>
-          <t>fovSmoothTime</t>
+          <t>smoothTime</t>
         </is>
       </c>
       <c r="L155" s="0" t="inlineStr">
@@ -3761,14 +3761,14 @@
       </c>
       <c r="N155" s="0" t="inlineStr">
         <is>
-          <t>FOV平滑时间</t>
+          <t>相机平滑时间</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="J156" s="0" t="inlineStr">
         <is>
-          <t>shakeDamping</t>
+          <t>defaultFov</t>
         </is>
       </c>
       <c r="L156" s="0" t="inlineStr">
@@ -3778,31 +3778,31 @@
       </c>
       <c r="N156" s="0" t="inlineStr">
         <is>
-          <t>震动衰减速度</t>
+          <t>默认FOV</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="J157" s="0" t="inlineStr">
         <is>
-          <t>scopeRenderSize</t>
+          <t>fovSmoothTime</t>
         </is>
       </c>
       <c r="L157" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N157" s="0" t="inlineStr">
         <is>
-          <t>狙击镜渲染纹理尺寸</t>
+          <t>FOV平滑时间</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="J158" s="0" t="inlineStr">
         <is>
-          <t>scopeCameraFov</t>
+          <t>shakeDamping</t>
         </is>
       </c>
       <c r="L158" s="0" t="inlineStr">
@@ -3812,99 +3812,99 @@
       </c>
       <c r="N158" s="0" t="inlineStr">
         <is>
-          <t>狙击镜相机FOV</t>
+          <t>震动衰减速度</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="J159" s="0" t="inlineStr">
         <is>
-          <t>defaultOrthographicSize</t>
+          <t>scopeRenderSize</t>
         </is>
       </c>
       <c r="L159" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N159" s="0" t="inlineStr">
         <is>
-          <t>默认正交尺寸</t>
+          <t>狙击镜渲染纹理尺寸</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="B160" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Ballistic</t>
-        </is>
-      </c>
-      <c r="G160" s="0" t="inlineStr">
-        <is>
-          <t>弹道全局配置</t>
-        </is>
-      </c>
-      <c r="H160" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J160" s="0" t="inlineStr">
+        <is>
+          <t>scopeCameraFov</t>
+        </is>
+      </c>
+      <c r="L160" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N160" s="0" t="inlineStr">
+        <is>
+          <t>狙击镜相机FOV</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="J161" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>defaultOrthographicSize</t>
         </is>
       </c>
       <c r="L161" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N161" s="0" t="inlineStr">
         <is>
-          <t>配置ID</t>
+          <t>默认正交尺寸</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="J162" s="0" t="inlineStr">
-        <is>
-          <t>tracerRadius</t>
-        </is>
-      </c>
-      <c r="L162" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N162" s="0" t="inlineStr">
-        <is>
-          <t>Tracer射线检测半径</t>
+      <c r="B162" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Ballistic</t>
+        </is>
+      </c>
+      <c r="G162" s="0" t="inlineStr">
+        <is>
+          <t>弹道全局配置</t>
+        </is>
+      </c>
+      <c r="H162" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="J163" s="0" t="inlineStr">
         <is>
-          <t>tracerStartWidth</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L163" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N163" s="0" t="inlineStr">
         <is>
-          <t>Tracer起始宽度</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="J164" s="0" t="inlineStr">
         <is>
-          <t>tracerEndWidth</t>
+          <t>tracerRadius</t>
         </is>
       </c>
       <c r="L164" s="0" t="inlineStr">
@@ -3914,14 +3914,14 @@
       </c>
       <c r="N164" s="0" t="inlineStr">
         <is>
-          <t>Tracer结束宽度</t>
+          <t>Tracer射线检测半径</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="J165" s="0" t="inlineStr">
         <is>
-          <t>tracerTailLength</t>
+          <t>tracerStartWidth</t>
         </is>
       </c>
       <c r="L165" s="0" t="inlineStr">
@@ -3931,235 +3931,235 @@
       </c>
       <c r="N165" s="0" t="inlineStr">
         <is>
-          <t>Tracer尾迹长度</t>
+          <t>Tracer起始宽度</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="J166" s="0" t="inlineStr">
         <is>
-          <t>maxActiveTracers</t>
+          <t>tracerEndWidth</t>
         </is>
       </c>
       <c r="L166" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N166" s="0" t="inlineStr">
         <is>
-          <t>最大同时存在Tracer数量</t>
+          <t>Tracer结束宽度</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="J167" s="0" t="inlineStr">
         <is>
-          <t>hitLayers</t>
+          <t>tracerTailLength</t>
         </is>
       </c>
       <c r="L167" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N167" s="0" t="inlineStr">
         <is>
-          <t>默认命中层级</t>
+          <t>Tracer尾迹长度</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="J168" s="0" t="inlineStr">
         <is>
-          <t>tracerStartColor</t>
+          <t>maxActiveTracers</t>
         </is>
       </c>
       <c r="L168" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N168" s="0" t="inlineStr">
         <is>
-          <t>Tracer起始颜色</t>
+          <t>最大同时存在Tracer数量</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="J169" s="0" t="inlineStr">
         <is>
-          <t>tracerEndColor</t>
+          <t>hitLayers</t>
         </is>
       </c>
       <c r="L169" s="0" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N169" s="0" t="inlineStr">
+        <is>
+          <t>默认命中层级</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="J170" s="0" t="inlineStr">
+        <is>
+          <t>tracerStartColor</t>
+        </is>
+      </c>
+      <c r="L170" s="0" t="inlineStr">
+        <is>
           <t>cfg.Color#sep=,</t>
         </is>
       </c>
-      <c r="N169" s="0" t="inlineStr">
-        <is>
-          <t>Tracer结束颜色</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="B170" s="0" t="inlineStr">
-        <is>
-          <t>cfg.UiConfig</t>
-        </is>
-      </c>
-      <c r="G170" s="0" t="inlineStr">
-        <is>
-          <t>UI全局配置</t>
-        </is>
-      </c>
-      <c r="H170" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="N170" s="0" t="inlineStr">
+        <is>
+          <t>Tracer起始颜色</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="J171" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>tracerEndColor</t>
         </is>
       </c>
       <c r="L171" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N171" s="0" t="inlineStr">
         <is>
-          <t>配置ID</t>
+          <t>Tracer结束颜色</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="J172" s="0" t="inlineStr">
-        <is>
-          <t>damageNumberPoolSize</t>
-        </is>
-      </c>
-      <c r="L172" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N172" s="0" t="inlineStr">
-        <is>
-          <t>伤害数字对象池大小</t>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t>cfg.UiConfig</t>
+        </is>
+      </c>
+      <c r="G172" s="0" t="inlineStr">
+        <is>
+          <t>UI全局配置</t>
+        </is>
+      </c>
+      <c r="H172" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="J173" s="0" t="inlineStr">
         <is>
-          <t>damageNumberFadeDuration</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L173" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N173" s="0" t="inlineStr">
         <is>
-          <t>伤害数字渐隐时间</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="J174" s="0" t="inlineStr">
         <is>
-          <t>damageNumberMoveOffset</t>
+          <t>damageNumberPoolSize</t>
         </is>
       </c>
       <c r="L174" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N174" s="0" t="inlineStr">
         <is>
-          <t>伤害数字上浮偏移</t>
+          <t>伤害数字对象池大小</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="J175" s="0" t="inlineStr">
         <is>
-          <t>damageNumberNormalColor</t>
+          <t>damageNumberFadeDuration</t>
         </is>
       </c>
       <c r="L175" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N175" s="0" t="inlineStr">
         <is>
-          <t>普通伤害数字颜色</t>
+          <t>伤害数字渐隐时间</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="J176" s="0" t="inlineStr">
         <is>
-          <t>damageNumberCriticalColor</t>
+          <t>damageNumberMoveOffset</t>
         </is>
       </c>
       <c r="L176" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N176" s="0" t="inlineStr">
         <is>
-          <t>暴击伤害数字颜色</t>
+          <t>伤害数字上浮偏移</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="J177" s="0" t="inlineStr">
         <is>
-          <t>damageNumberNormalFontSize</t>
+          <t>damageNumberNormalColor</t>
         </is>
       </c>
       <c r="L177" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N177" s="0" t="inlineStr">
         <is>
-          <t>普通伤害数字字体大小</t>
+          <t>普通伤害数字颜色</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="J178" s="0" t="inlineStr">
         <is>
-          <t>damageNumberCriticalFontSize</t>
+          <t>damageNumberCriticalColor</t>
         </is>
       </c>
       <c r="L178" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N178" s="0" t="inlineStr">
         <is>
-          <t>暴击伤害数字字体大小</t>
+          <t>暴击伤害数字颜色</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="J179" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerPoolSize</t>
+          <t>damageNumberNormalFontSize</t>
         </is>
       </c>
       <c r="L179" s="0" t="inlineStr">
@@ -4169,99 +4169,99 @@
       </c>
       <c r="N179" s="0" t="inlineStr">
         <is>
-          <t>命中标记对象池大小</t>
+          <t>普通伤害数字字体大小</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="J180" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerDuration</t>
+          <t>damageNumberCriticalFontSize</t>
         </is>
       </c>
       <c r="L180" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N180" s="0" t="inlineStr">
         <is>
-          <t>命中标记显示时间</t>
+          <t>暴击伤害数字字体大小</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="J181" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerSize</t>
+          <t>hitMarkerPoolSize</t>
         </is>
       </c>
       <c r="L181" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N181" s="0" t="inlineStr">
         <is>
-          <t>命中标记大小</t>
+          <t>命中标记对象池大小</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="J182" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerNormalColor</t>
+          <t>hitMarkerDuration</t>
         </is>
       </c>
       <c r="L182" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N182" s="0" t="inlineStr">
         <is>
-          <t>普通命中标记颜色</t>
+          <t>命中标记显示时间</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="J183" s="0" t="inlineStr">
         <is>
-          <t>hitMarkerCriticalColor</t>
+          <t>hitMarkerSize</t>
         </is>
       </c>
       <c r="L183" s="0" t="inlineStr">
         <is>
-          <t>cfg.Color#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N183" s="0" t="inlineStr">
         <is>
-          <t>暴击命中标记颜色</t>
+          <t>命中标记大小</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="J184" s="0" t="inlineStr">
         <is>
-          <t>indicatorFadeSpeed</t>
+          <t>hitMarkerNormalColor</t>
         </is>
       </c>
       <c r="L184" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>cfg.Color#sep=,</t>
         </is>
       </c>
       <c r="N184" s="0" t="inlineStr">
         <is>
-          <t>受击指示器淡出速度</t>
+          <t>普通命中标记颜色</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="J185" s="0" t="inlineStr">
         <is>
-          <t>indicatorColor</t>
+          <t>hitMarkerCriticalColor</t>
         </is>
       </c>
       <c r="L185" s="0" t="inlineStr">
@@ -4271,133 +4271,133 @@
       </c>
       <c r="N185" s="0" t="inlineStr">
         <is>
-          <t>受击指示器颜色</t>
+          <t>暴击命中标记颜色</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="J186" s="0" t="inlineStr">
         <is>
-          <t>loadingTextFormat</t>
+          <t>indicatorFadeSpeed</t>
         </is>
       </c>
       <c r="L186" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N186" s="0" t="inlineStr">
         <is>
-          <t>加载进度文本格式</t>
+          <t>受击指示器淡出速度</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="B187" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Pickup</t>
-        </is>
-      </c>
-      <c r="G187" s="0" t="inlineStr">
-        <is>
-          <t>拾取物配置</t>
-        </is>
-      </c>
-      <c r="H187" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J187" s="0" t="inlineStr">
+        <is>
+          <t>indicatorColor</t>
+        </is>
+      </c>
+      <c r="L187" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Color#sep=,</t>
+        </is>
+      </c>
+      <c r="N187" s="0" t="inlineStr">
+        <is>
+          <t>受击指示器颜色</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="J188" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>loadingTextFormat</t>
         </is>
       </c>
       <c r="L188" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N188" s="0" t="inlineStr">
         <is>
-          <t>配置ID</t>
+          <t>加载进度文本格式</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="J189" s="0" t="inlineStr">
-        <is>
-          <t>colliderRadius</t>
-        </is>
-      </c>
-      <c r="L189" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N189" s="0" t="inlineStr">
-        <is>
-          <t>拾取物碰撞体半径</t>
+      <c r="B189" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Pickup</t>
+        </is>
+      </c>
+      <c r="G189" s="0" t="inlineStr">
+        <is>
+          <t>拾取物配置</t>
+        </is>
+      </c>
+      <c r="H189" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="J190" s="0" t="inlineStr">
         <is>
-          <t>visualScale</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L190" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N190" s="0" t="inlineStr">
         <is>
-          <t>拾取物视觉缩放</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="J191" s="0" t="inlineStr">
         <is>
-          <t>sortingOrder</t>
+          <t>colliderRadius</t>
         </is>
       </c>
       <c r="L191" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N191" s="0" t="inlineStr">
         <is>
-          <t>拾取物渲染排序</t>
+          <t>拾取物碰撞体半径</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="B192" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Building</t>
-        </is>
-      </c>
-      <c r="G192" s="0" t="inlineStr">
-        <is>
-          <t>建筑配置</t>
-        </is>
-      </c>
-      <c r="I192" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J192" s="0" t="inlineStr">
+        <is>
+          <t>visualScale</t>
+        </is>
+      </c>
+      <c r="L192" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N192" s="0" t="inlineStr">
+        <is>
+          <t>拾取物视觉缩放</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="J193" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>sortingOrder</t>
         </is>
       </c>
       <c r="L193" s="0" t="inlineStr">
@@ -4407,65 +4407,65 @@
       </c>
       <c r="N193" s="0" t="inlineStr">
         <is>
-          <t>建筑ID</t>
+          <t>拾取物渲染排序</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="J194" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L194" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N194" s="0" t="inlineStr">
-        <is>
-          <t>名称</t>
+      <c r="B194" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Building</t>
+        </is>
+      </c>
+      <c r="G194" s="0" t="inlineStr">
+        <is>
+          <t>建筑配置</t>
+        </is>
+      </c>
+      <c r="I194" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="J195" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L195" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N195" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="J196" s="0" t="inlineStr">
         <is>
-          <t>buildingType</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L196" s="0" t="inlineStr">
         <is>
-          <t>cfg.EBuildingType</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N196" s="0" t="inlineStr">
         <is>
-          <t>建筑类型</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="J197" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L197" s="0" t="inlineStr">
@@ -4475,167 +4475,167 @@
       </c>
       <c r="N197" s="0" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="J198" s="0" t="inlineStr">
         <is>
-          <t>maxLevel</t>
+          <t>buildingType</t>
         </is>
       </c>
       <c r="L198" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>cfg.EBuildingType</t>
         </is>
       </c>
       <c r="N198" s="0" t="inlineStr">
         <is>
-          <t>最大等级</t>
+          <t>建筑类型</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="J199" s="0" t="inlineStr">
         <is>
-          <t>buildCostGold</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L199" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N199" s="0" t="inlineStr">
         <is>
-          <t>建造金币</t>
+          <t>图标</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="J200" s="0" t="inlineStr">
         <is>
-          <t>buildCostItems</t>
+          <t>maxLevel</t>
         </is>
       </c>
       <c r="L200" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N200" s="0" t="inlineStr">
         <is>
-          <t>建造材料</t>
+          <t>最大等级</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="J201" s="0" t="inlineStr">
         <is>
-          <t>buildTime</t>
+          <t>buildCostGold</t>
         </is>
       </c>
       <c r="L201" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N201" s="0" t="inlineStr">
         <is>
-          <t>建造耗时</t>
+          <t>建造金币</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="J202" s="0" t="inlineStr">
         <is>
-          <t>upgradeCostGold</t>
+          <t>buildCostItems</t>
         </is>
       </c>
       <c r="L202" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N202" s="0" t="inlineStr">
         <is>
-          <t>升级金币</t>
+          <t>建造材料</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="J203" s="0" t="inlineStr">
         <is>
-          <t>upgradeCostItems</t>
+          <t>buildTime</t>
         </is>
       </c>
       <c r="L203" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N203" s="0" t="inlineStr">
         <is>
-          <t>升级材料</t>
+          <t>建造耗时</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="J204" s="0" t="inlineStr">
         <is>
-          <t>upgradeTime</t>
+          <t>upgradeCostGold</t>
         </is>
       </c>
       <c r="L204" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N204" s="0" t="inlineStr">
         <is>
-          <t>升级耗时</t>
+          <t>升级金币</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="J205" s="0" t="inlineStr">
         <is>
-          <t>productionSlotCount</t>
+          <t>upgradeCostItems</t>
         </is>
       </c>
       <c r="L205" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N205" s="0" t="inlineStr">
         <is>
-          <t>生产槽位</t>
+          <t>升级材料</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="J206" s="0" t="inlineStr">
         <is>
-          <t>unlockLevel</t>
+          <t>upgradeTime</t>
         </is>
       </c>
       <c r="L206" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N206" s="0" t="inlineStr">
         <is>
-          <t>解锁等级</t>
+          <t>升级耗时</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="J207" s="0" t="inlineStr">
         <is>
-          <t>footprintX</t>
+          <t>productionSlotCount</t>
         </is>
       </c>
       <c r="L207" s="0" t="inlineStr">
@@ -4645,14 +4645,14 @@
       </c>
       <c r="N207" s="0" t="inlineStr">
         <is>
-          <t>占地格数X(1m格)</t>
+          <t>生产槽位</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="J208" s="0" t="inlineStr">
         <is>
-          <t>maxCount</t>
+          <t>unlockLevel</t>
         </is>
       </c>
       <c r="L208" s="0" t="inlineStr">
@@ -4662,14 +4662,14 @@
       </c>
       <c r="N208" s="0" t="inlineStr">
         <is>
-          <t>数量上限-基础值(默认1)</t>
+          <t>解锁等级</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="J209" s="0" t="inlineStr">
         <is>
-          <t>maxCountPerPlayerLevel</t>
+          <t>footprintX</t>
         </is>
       </c>
       <c r="L209" s="0" t="inlineStr">
@@ -4679,14 +4679,14 @@
       </c>
       <c r="N209" s="0" t="inlineStr">
         <is>
-          <t>数量上限-玩家等级解锁:玩家每升1级上限+N(默认0)</t>
+          <t>占地格数X(1m格)</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="J210" s="0" t="inlineStr">
         <is>
-          <t>maxCountUpgradeLevel</t>
+          <t>maxCount</t>
         </is>
       </c>
       <c r="L210" s="0" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="N210" s="0" t="inlineStr">
         <is>
-          <t>数量上限-升级解锁(默认方式):同类建筑每有1座达到该等级上限+1,0=不启用</t>
+          <t>数量上限-基础值(默认1)</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="J211" s="0" t="inlineStr">
         <is>
-          <t>maxCountSlotBaseCost</t>
+          <t>maxCountPerPlayerLevel</t>
         </is>
       </c>
       <c r="L211" s="0" t="inlineStr">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="N211" s="0" t="inlineStr">
         <is>
-          <t>数量上限-购买解锁:购买1个栏位的金币基础价,0=不可购买</t>
+          <t>数量上限-玩家等级解锁:玩家每升1级上限+N(默认0)</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="J212" s="0" t="inlineStr">
         <is>
-          <t>maxCountSlotCostGrow</t>
+          <t>maxCountUpgradeLevel</t>
         </is>
       </c>
       <c r="L212" s="0" t="inlineStr">
@@ -4730,14 +4730,14 @@
       </c>
       <c r="N212" s="0" t="inlineStr">
         <is>
-          <t>数量上限-购买解锁:每已购1个栏位价格+N(线性涨价)</t>
+          <t>数量上限-升级解锁(默认方式):同类建筑每有1座达到该等级上限+1,0=不启用</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="J213" s="0" t="inlineStr">
         <is>
-          <t>footprintZ</t>
+          <t>maxCountSlotBaseCost</t>
         </is>
       </c>
       <c r="L213" s="0" t="inlineStr">
@@ -4747,31 +4747,31 @@
       </c>
       <c r="N213" s="0" t="inlineStr">
         <is>
-          <t>占地格数Z(1m格)</t>
+          <t>数量上限-购买解锁:购买1个栏位的金币基础价,0=不可购买</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="B214" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Production</t>
-        </is>
-      </c>
-      <c r="G214" s="0" t="inlineStr">
-        <is>
-          <t>生产配方</t>
-        </is>
-      </c>
-      <c r="I214" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J214" s="0" t="inlineStr">
+        <is>
+          <t>maxCountSlotCostGrow</t>
+        </is>
+      </c>
+      <c r="L214" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N214" s="0" t="inlineStr">
+        <is>
+          <t>数量上限-购买解锁:每已购1个栏位价格+N(线性涨价)</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="J215" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>footprintZ</t>
         </is>
       </c>
       <c r="L215" s="0" t="inlineStr">
@@ -4781,99 +4781,99 @@
       </c>
       <c r="N215" s="0" t="inlineStr">
         <is>
-          <t>配方ID</t>
+          <t>占地格数Z(1m格)</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="J216" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L216" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N216" s="0" t="inlineStr">
-        <is>
-          <t>名称</t>
+      <c r="B216" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Production</t>
+        </is>
+      </c>
+      <c r="G216" s="0" t="inlineStr">
+        <is>
+          <t>生产配方</t>
+        </is>
+      </c>
+      <c r="I216" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="J217" s="0" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L217" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N217" s="0" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>配方ID</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="J218" s="0" t="inlineStr">
         <is>
-          <t>buildingId</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L218" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N218" s="0" t="inlineStr">
         <is>
-          <t>建筑ID</t>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="J219" s="0" t="inlineStr">
         <is>
-          <t>levelRequired</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="L219" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N219" s="0" t="inlineStr">
         <is>
-          <t>等级要求</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="J220" s="0" t="inlineStr">
         <is>
-          <t>inputItems</t>
+          <t>buildingId</t>
         </is>
       </c>
       <c r="L220" s="0" t="inlineStr">
         <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N220" s="0" t="inlineStr">
         <is>
-          <t>输入材料</t>
+          <t>建筑ID</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="J221" s="0" t="inlineStr">
         <is>
-          <t>outputItemId</t>
+          <t>levelRequired</t>
         </is>
       </c>
       <c r="L221" s="0" t="inlineStr">
@@ -4883,116 +4883,116 @@
       </c>
       <c r="N221" s="0" t="inlineStr">
         <is>
-          <t>产出物品</t>
+          <t>等级要求</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="J222" s="0" t="inlineStr">
         <is>
-          <t>outputCount</t>
+          <t>inputItems</t>
         </is>
       </c>
       <c r="L222" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N222" s="0" t="inlineStr">
         <is>
-          <t>产出数量</t>
+          <t>输入材料</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="J223" s="0" t="inlineStr">
         <is>
-          <t>productionTime</t>
+          <t>outputItemId</t>
         </is>
       </c>
       <c r="L223" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N223" s="0" t="inlineStr">
         <is>
-          <t>生产耗时</t>
+          <t>产出物品</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="J224" s="0" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>outputCount</t>
         </is>
       </c>
       <c r="L224" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N224" s="0" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>产出数量</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="B225" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Order</t>
-        </is>
-      </c>
-      <c r="G225" s="0" t="inlineStr">
-        <is>
-          <t>订单配置</t>
-        </is>
-      </c>
-      <c r="I225" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J225" s="0" t="inlineStr">
+        <is>
+          <t>productionTime</t>
+        </is>
+      </c>
+      <c r="L225" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N225" s="0" t="inlineStr">
+        <is>
+          <t>生产耗时</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="J226" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="L226" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N226" s="0" t="inlineStr">
         <is>
-          <t>订单ID</t>
+          <t>图标</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="J227" s="0" t="inlineStr">
-        <is>
-          <t>requiredItems</t>
-        </is>
-      </c>
-      <c r="L227" s="0" t="inlineStr">
-        <is>
-          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
-        </is>
-      </c>
-      <c r="N227" s="0" t="inlineStr">
-        <is>
-          <t>需求物品</t>
+      <c r="B227" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Order</t>
+        </is>
+      </c>
+      <c r="G227" s="0" t="inlineStr">
+        <is>
+          <t>订单配置</t>
+        </is>
+      </c>
+      <c r="I227" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="J228" s="0" t="inlineStr">
         <is>
-          <t>rewardGold</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L228" s="0" t="inlineStr">
@@ -5002,14 +5002,14 @@
       </c>
       <c r="N228" s="0" t="inlineStr">
         <is>
-          <t>奖励金币</t>
+          <t>订单ID</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="J229" s="0" t="inlineStr">
         <is>
-          <t>rewardItems</t>
+          <t>requiredItems</t>
         </is>
       </c>
       <c r="L229" s="0" t="inlineStr">
@@ -5019,14 +5019,14 @@
       </c>
       <c r="N229" s="0" t="inlineStr">
         <is>
-          <t>奖励物品</t>
+          <t>需求物品</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="J230" s="0" t="inlineStr">
         <is>
-          <t>rewardExp</t>
+          <t>rewardGold</t>
         </is>
       </c>
       <c r="L230" s="0" t="inlineStr">
@@ -5036,31 +5036,31 @@
       </c>
       <c r="N230" s="0" t="inlineStr">
         <is>
-          <t>奖励经验</t>
+          <t>奖励金币</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="J231" s="0" t="inlineStr">
         <is>
-          <t>timeLimit</t>
+          <t>rewardItems</t>
         </is>
       </c>
       <c r="L231" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>(list#sep=;),cfg.ItemExchange#sep=,</t>
         </is>
       </c>
       <c r="N231" s="0" t="inlineStr">
         <is>
-          <t>时限</t>
+          <t>奖励物品</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="J232" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>rewardExp</t>
         </is>
       </c>
       <c r="L232" s="0" t="inlineStr">
@@ -5070,48 +5070,48 @@
       </c>
       <c r="N232" s="0" t="inlineStr">
         <is>
-          <t>权重</t>
+          <t>奖励经验</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="J233" s="0" t="inlineStr">
         <is>
-          <t>minPlayerLevel</t>
+          <t>timeLimit</t>
         </is>
       </c>
       <c r="L233" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N233" s="0" t="inlineStr">
         <is>
-          <t>最低等级</t>
+          <t>时限</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="B234" s="0" t="inlineStr">
-        <is>
-          <t>cfg.SimTimeConfig</t>
-        </is>
-      </c>
-      <c r="G234" s="0" t="inlineStr">
-        <is>
-          <t>经营时间配置</t>
-        </is>
-      </c>
-      <c r="I234" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J234" s="0" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L234" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N234" s="0" t="inlineStr">
+        <is>
+          <t>权重</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="J235" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>minPlayerLevel</t>
         </is>
       </c>
       <c r="L235" s="0" t="inlineStr">
@@ -5121,48 +5121,48 @@
       </c>
       <c r="N235" s="0" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>最低等级</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="J236" s="0" t="inlineStr">
-        <is>
-          <t>baseSpeed</t>
-        </is>
-      </c>
-      <c r="L236" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N236" s="0" t="inlineStr">
-        <is>
-          <t>基础速度</t>
+      <c r="B236" s="0" t="inlineStr">
+        <is>
+          <t>cfg.SimTimeConfig</t>
+        </is>
+      </c>
+      <c r="G236" s="0" t="inlineStr">
+        <is>
+          <t>经营时间配置</t>
+        </is>
+      </c>
+      <c r="I236" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="J237" s="0" t="inlineStr">
         <is>
-          <t>fastSpeed</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L237" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N237" s="0" t="inlineStr">
         <is>
-          <t>加速速度</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="J238" s="0" t="inlineStr">
         <is>
-          <t>maxSpeed</t>
+          <t>baseSpeed</t>
         </is>
       </c>
       <c r="L238" s="0" t="inlineStr">
@@ -5172,14 +5172,14 @@
       </c>
       <c r="N238" s="0" t="inlineStr">
         <is>
-          <t>最大速度</t>
+          <t>基础速度</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="J239" s="0" t="inlineStr">
         <is>
-          <t>orderRefreshInterval</t>
+          <t>fastSpeed</t>
         </is>
       </c>
       <c r="L239" s="0" t="inlineStr">
@@ -5189,48 +5189,48 @@
       </c>
       <c r="N239" s="0" t="inlineStr">
         <is>
-          <t>订单刷新间隔</t>
+          <t>加速速度</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="J240" s="0" t="inlineStr">
         <is>
-          <t>maxOrderCount</t>
+          <t>maxSpeed</t>
         </is>
       </c>
       <c r="L240" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N240" s="0" t="inlineStr">
         <is>
-          <t>最大订单数</t>
+          <t>最大速度</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="B241" s="0" t="inlineStr">
-        <is>
-          <t>cfg.Camera3D</t>
-        </is>
-      </c>
-      <c r="G241" s="0" t="inlineStr">
-        <is>
-          <t>3D摄像机配置</t>
-        </is>
-      </c>
-      <c r="I241" s="0" t="inlineStr">
-        <is>
-          <t>c</t>
+      <c r="J241" s="0" t="inlineStr">
+        <is>
+          <t>orderRefreshInterval</t>
+        </is>
+      </c>
+      <c r="L241" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N241" s="0" t="inlineStr">
+        <is>
+          <t>订单刷新间隔</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="J242" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>maxOrderCount</t>
         </is>
       </c>
       <c r="L242" s="0" t="inlineStr">
@@ -5240,48 +5240,48 @@
       </c>
       <c r="N242" s="0" t="inlineStr">
         <is>
-          <t>配置ID</t>
+          <t>最大订单数</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="J243" s="0" t="inlineStr">
-        <is>
-          <t>pitchAngle</t>
-        </is>
-      </c>
-      <c r="L243" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N243" s="0" t="inlineStr">
-        <is>
-          <t>俯视角度</t>
+      <c r="B243" s="0" t="inlineStr">
+        <is>
+          <t>cfg.Camera3D</t>
+        </is>
+      </c>
+      <c r="G243" s="0" t="inlineStr">
+        <is>
+          <t>3D摄像机配置</t>
+        </is>
+      </c>
+      <c r="I243" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="J244" s="0" t="inlineStr">
         <is>
-          <t>initialHeight</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L244" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N244" s="0" t="inlineStr">
         <is>
-          <t>初始高度</t>
+          <t>配置ID</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="J245" s="0" t="inlineStr">
         <is>
-          <t>initialDistance</t>
+          <t>pitchAngle</t>
         </is>
       </c>
       <c r="L245" s="0" t="inlineStr">
@@ -5291,14 +5291,14 @@
       </c>
       <c r="N245" s="0" t="inlineStr">
         <is>
-          <t>初始距离</t>
+          <t>俯视角度</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="J246" s="0" t="inlineStr">
         <is>
-          <t>fov</t>
+          <t>initialHeight</t>
         </is>
       </c>
       <c r="L246" s="0" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="N246" s="0" t="inlineStr">
         <is>
-          <t>视场角</t>
+          <t>初始高度</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="J247" s="0" t="inlineStr">
         <is>
-          <t>minZoom</t>
+          <t>initialDistance</t>
         </is>
       </c>
       <c r="L247" s="0" t="inlineStr">
@@ -5325,14 +5325,14 @@
       </c>
       <c r="N247" s="0" t="inlineStr">
         <is>
-          <t>最小缩放</t>
+          <t>初始距离</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="J248" s="0" t="inlineStr">
         <is>
-          <t>maxZoom</t>
+          <t>fov</t>
         </is>
       </c>
       <c r="L248" s="0" t="inlineStr">
@@ -5342,14 +5342,14 @@
       </c>
       <c r="N248" s="0" t="inlineStr">
         <is>
-          <t>最大缩放</t>
+          <t>视场角</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="J249" s="0" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>minZoom</t>
         </is>
       </c>
       <c r="L249" s="0" t="inlineStr">
@@ -5359,14 +5359,14 @@
       </c>
       <c r="N249" s="0" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>最小缩放</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="J250" s="0" t="inlineStr">
         <is>
-          <t>zoomSpeed</t>
+          <t>maxZoom</t>
         </is>
       </c>
       <c r="L250" s="0" t="inlineStr">
@@ -5376,14 +5376,14 @@
       </c>
       <c r="N250" s="0" t="inlineStr">
         <is>
-          <t>缩放速度</t>
+          <t>最大缩放</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="J251" s="0" t="inlineStr">
         <is>
-          <t>maxRotationAngle</t>
+          <t>moveSpeed</t>
         </is>
       </c>
       <c r="L251" s="0" t="inlineStr">
@@ -5393,14 +5393,14 @@
       </c>
       <c r="N251" s="0" t="inlineStr">
         <is>
-          <t>最大旋转角度</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="J252" s="0" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>zoomSpeed</t>
         </is>
       </c>
       <c r="L252" s="0" t="inlineStr">
@@ -5410,72 +5410,83 @@
       </c>
       <c r="N252" s="0" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>缩放速度</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="J253" s="0" t="inlineStr">
         <is>
+          <t>maxRotationAngle</t>
+        </is>
+      </c>
+      <c r="L253" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N253" s="0" t="inlineStr">
+        <is>
+          <t>最大旋转角度</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="J254" s="0" t="inlineStr">
+        <is>
+          <t>rotationSpeed</t>
+        </is>
+      </c>
+      <c r="L254" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N254" s="0" t="inlineStr">
+        <is>
+          <t>旋转速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="J255" s="0" t="inlineStr">
+        <is>
           <t>followSmoothTime</t>
         </is>
       </c>
-      <c r="L253" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N253" s="0" t="inlineStr">
+      <c r="L255" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N255" s="0" t="inlineStr">
         <is>
           <t>跟随平滑时间</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="B255" s="0" t="inlineStr">
+    <row r="256"/>
+    <row r="257">
+      <c r="B257" s="0" t="inlineStr">
         <is>
           <t>cfg.LootContainer</t>
         </is>
       </c>
-      <c r="G255" s="0" t="inlineStr">
+      <c r="G257" s="0" t="inlineStr">
         <is>
           <t>容器掉落记录</t>
         </is>
       </c>
-      <c r="I255" s="0" t="inlineStr">
+      <c r="I257" s="0" t="inlineStr">
         <is>
           <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="J256" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L256" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="J257" s="0" t="inlineStr">
-        <is>
-          <t>containerId</t>
-        </is>
-      </c>
-      <c r="L257" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="J258" s="0" t="inlineStr">
         <is>
-          <t>itemId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L258" s="0" t="inlineStr">
@@ -5487,7 +5498,7 @@
     <row r="259">
       <c r="J259" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>containerId</t>
         </is>
       </c>
       <c r="L259" s="0" t="inlineStr">
@@ -5499,7 +5510,7 @@
     <row r="260">
       <c r="J260" s="0" t="inlineStr">
         <is>
-          <t>minCount</t>
+          <t>itemId</t>
         </is>
       </c>
       <c r="L260" s="0" t="inlineStr">
@@ -5511,82 +5522,293 @@
     <row r="261">
       <c r="J261" s="0" t="inlineStr">
         <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L261" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="J262" s="0" t="inlineStr">
+        <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="L262" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="J263" s="0" t="inlineStr">
+        <is>
           <t>maxCount</t>
         </is>
       </c>
-      <c r="L261" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="262"/>
-    <row r="263">
-      <c r="B263" t="inlineStr">
+      <c r="L263" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="264"/>
+    <row r="265">
+      <c r="B265" s="0" t="inlineStr">
         <is>
           <t>cfg.Note</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
+      <c r="G265" s="0" t="inlineStr">
         <is>
           <t>小纸条记录</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr">
+      <c r="I265" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="J264" t="inlineStr">
+    <row r="266">
+      <c r="J266" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N264" t="inlineStr">
+      <c r="L266" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N266" s="0" t="inlineStr">
         <is>
           <t>纸条ID</t>
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="J265" t="inlineStr">
+    <row r="267">
+      <c r="J267" s="0" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr">
+      <c r="L267" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N265" t="inlineStr">
+      <c r="N267" s="0" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="J266" t="inlineStr">
+    <row r="268">
+      <c r="J268" s="0" t="inlineStr">
         <is>
           <t>content</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr">
+      <c r="L268" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N266" t="inlineStr">
+      <c r="N268" s="0" t="inlineStr">
         <is>
           <t>正文(支持
 换行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>cfg.PlayerLevel</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>玩家等级经验表</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>expToNext</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>升到下一级所需经验</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>cfg.Unlock</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>内容解锁表</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>解锁ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>contentType</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>cfg.UnlockContentType</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>内容类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>targetId</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>目标ID（关卡/武器）</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>requirePlayerLevel</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>要求玩家等级(0=无)</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>requireCompleteLevelId</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>要求通关关卡ID(0=无)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>costGold</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>解锁花费金币(0=免费)</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
